--- a/docs/WFMHub Report Design Reference.xlsx
+++ b/docs/WFMHub Report Design Reference.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="118">
   <si>
     <t>WFMHUB REPORT SYSTEM</t>
   </si>
@@ -25,7 +25,7 @@
     <t>UPDATED</t>
   </si>
   <si>
-    <t>WFMHUB-DESIGN 1.0.0 · approved visual contract</t>
+    <t>WFMHUB-DESIGN 2.0.0 · approved visual contract</t>
   </si>
   <si>
     <t>TOKENS</t>
@@ -103,10 +103,13 @@
     <t>No AI branding, decorative visuals, guessed target, or hidden KPI arithmetic.</t>
   </si>
   <si>
-    <t>PCS PERFORMANCE</t>
-  </si>
-  <si>
-    <t>Illustrative layout only · governed data replaces every example</t>
+    <t>PCS OPERATIONS</t>
+  </si>
+  <si>
+    <t>WFMHUB  |  ANASS ASSRI</t>
+  </si>
+  <si>
+    <t>DATA FRESH</t>
   </si>
   <si>
     <t>PERIOD</t>
@@ -124,280 +127,244 @@
     <t>TEAM LEADER</t>
   </si>
   <si>
-    <t>RESULTS filter</t>
-  </si>
-  <si>
     <t>AGENT</t>
   </si>
   <si>
-    <t>CURRENT MTD PCS</t>
-  </si>
-  <si>
-    <t>4.54</t>
-  </si>
-  <si>
-    <t>Weighted valid Q1</t>
+    <t>CURRENT PCS</t>
   </si>
   <si>
     <t>PARTICIPATION</t>
   </si>
   <si>
-    <t>26.8%</t>
-  </si>
-  <si>
-    <t>Q1 nonblank / status 1</t>
-  </si>
-  <si>
-    <t>PRIOR MTD PCS</t>
-  </si>
-  <si>
-    <t>4.42</t>
-  </si>
-  <si>
-    <t>Same days</t>
+    <t>PRIOR PCS</t>
   </si>
   <si>
     <t>CHANGE</t>
   </si>
   <si>
-    <t>+0.12</t>
-  </si>
-  <si>
-    <t>Current minus prior</t>
-  </si>
-  <si>
-    <t>PCS BY LOB · DAILY TREND · LOB PERFORMANCE TABLE</t>
-  </si>
-  <si>
-    <t>Prior MTD</t>
-  </si>
-  <si>
-    <t>Participation</t>
-  </si>
-  <si>
-    <t>Responses</t>
-  </si>
-  <si>
-    <t>Sample</t>
-  </si>
-  <si>
     <t>RSA NL</t>
   </si>
   <si>
-    <t>28.1%</t>
-  </si>
-  <si>
-    <t>OK</t>
-  </si>
-  <si>
     <t>RSA BE</t>
   </si>
   <si>
-    <t>24.7%</t>
-  </si>
-  <si>
     <t>FORD NL</t>
   </si>
   <si>
-    <t>28.9%</t>
+    <t>OEM</t>
+  </si>
+  <si>
+    <t>TEAM PERFORMANCE &amp; ACTIONS</t>
+  </si>
+  <si>
+    <t>PCS AGENTS</t>
+  </si>
+  <si>
+    <t>COACHING DUE</t>
+  </si>
+  <si>
+    <t>Sophie Martin</t>
+  </si>
+  <si>
+    <t>Karim Belkacem</t>
+  </si>
+  <si>
+    <t>Elena Rossi</t>
+  </si>
+  <si>
+    <t>Daniel Weber</t>
+  </si>
+  <si>
+    <t>RTM DAILY CONTROL</t>
+  </si>
+  <si>
+    <t>Combined service, attendance pulse and exact call actions</t>
+  </si>
+  <si>
+    <t>DATE</t>
+  </si>
+  <si>
+    <t>08 Sep 2026</t>
+  </si>
+  <si>
+    <t>SNAPSHOT</t>
+  </si>
+  <si>
+    <t>Through 17:59</t>
+  </si>
+  <si>
+    <t>All operational</t>
+  </si>
+  <si>
+    <t>ATTENDANCE</t>
+  </si>
+  <si>
+    <t>17:45</t>
+  </si>
+  <si>
+    <t>LOBS ON TARGET</t>
+  </si>
+  <si>
+    <t>3 / 4</t>
+  </si>
+  <si>
+    <t>Configured target</t>
+  </si>
+  <si>
+    <t>DEMAND VARIANCE</t>
+  </si>
+  <si>
+    <t>+84</t>
+  </si>
+  <si>
+    <t>Actual minus forecast</t>
+  </si>
+  <si>
+    <t>NO SHOW HC</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>Evidence proven</t>
+  </si>
+  <si>
+    <t>CALL NOW</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>Exact lists by LOB</t>
+  </si>
+  <si>
+    <t>SERVICE LEVEL BY LOB · LINKED OPERATIONAL TABLE</t>
+  </si>
+  <si>
+    <t>TSL</t>
+  </si>
+  <si>
+    <t>Target</t>
+  </si>
+  <si>
+    <t>Actual</t>
+  </si>
+  <si>
+    <t>Forecast</t>
+  </si>
+  <si>
+    <t>Variance</t>
+  </si>
+  <si>
+    <t>No Show</t>
+  </si>
+  <si>
+    <t>Call Now</t>
+  </si>
+  <si>
+    <t>89.9%</t>
+  </si>
+  <si>
+    <t>80.0%</t>
+  </si>
+  <si>
+    <t>85.8%</t>
+  </si>
+  <si>
+    <t>97.3%</t>
+  </si>
+  <si>
+    <t>94.9%</t>
+  </si>
+  <si>
+    <t>Examples are visual only. Calculations, targets and LOBs always come from WFMHub authorities.</t>
+  </si>
+  <si>
+    <t>ATTENDANCE REVIEW</t>
+  </si>
+  <si>
+    <t>Completed-day schedule-versus-observed decisions</t>
+  </si>
+  <si>
+    <t>01–07 Sep 2026</t>
+  </si>
+  <si>
+    <t>COMPLETED</t>
+  </si>
+  <si>
+    <t>Through 07 Sep</t>
+  </si>
+  <si>
+    <t>EVIDENCE</t>
+  </si>
+  <si>
+    <t>Agent Status + LILO</t>
+  </si>
+  <si>
+    <t>DECISION</t>
+  </si>
+  <si>
+    <t>REVIEW BOARD</t>
+  </si>
+  <si>
+    <t>REVIEW GAPS</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>Exact intervals</t>
+  </si>
+  <si>
+    <t>GAP HOURS</t>
+  </si>
+  <si>
+    <t>7.4</t>
+  </si>
+  <si>
+    <t>Exact minutes / 60</t>
+  </si>
+  <si>
+    <t>OPEN DECISIONS</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>Awaiting review</t>
+  </si>
+  <si>
+    <t>MISSING EVIDENCE</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Never treated as zero</t>
+  </si>
+  <si>
+    <t>BY-LOB ACTION SUMMARY · SCHEDULE ABOVE ACTUAL</t>
+  </si>
+  <si>
+    <t>Exact Gaps</t>
+  </si>
+  <si>
+    <t>Gap Hours</t>
+  </si>
+  <si>
+    <t>Agents</t>
+  </si>
+  <si>
+    <t>Open</t>
+  </si>
+  <si>
+    <t>Approved</t>
+  </si>
+  <si>
+    <t>Dismissed</t>
   </si>
   <si>
     <t>OEM FR</t>
-  </si>
-  <si>
-    <t>26.1%</t>
-  </si>
-  <si>
-    <t>Examples are visual only. Calculations, targets and LOBs always come from WFMHub authorities.</t>
-  </si>
-  <si>
-    <t>RTM DAILY CONTROL</t>
-  </si>
-  <si>
-    <t>Combined service, attendance pulse and exact call actions</t>
-  </si>
-  <si>
-    <t>DATE</t>
-  </si>
-  <si>
-    <t>08 Sep 2026</t>
-  </si>
-  <si>
-    <t>SNAPSHOT</t>
-  </si>
-  <si>
-    <t>Through 17:59</t>
-  </si>
-  <si>
-    <t>All operational</t>
-  </si>
-  <si>
-    <t>ATTENDANCE</t>
-  </si>
-  <si>
-    <t>17:45</t>
-  </si>
-  <si>
-    <t>LOBS ON TARGET</t>
-  </si>
-  <si>
-    <t>3 / 4</t>
-  </si>
-  <si>
-    <t>Configured target</t>
-  </si>
-  <si>
-    <t>DEMAND VARIANCE</t>
-  </si>
-  <si>
-    <t>+84</t>
-  </si>
-  <si>
-    <t>Actual minus forecast</t>
-  </si>
-  <si>
-    <t>NO SHOW HC</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>Evidence proven</t>
-  </si>
-  <si>
-    <t>CALL NOW</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>Exact lists by LOB</t>
-  </si>
-  <si>
-    <t>SERVICE LEVEL BY LOB · LINKED OPERATIONAL TABLE</t>
-  </si>
-  <si>
-    <t>TSL</t>
-  </si>
-  <si>
-    <t>Target</t>
-  </si>
-  <si>
-    <t>Actual</t>
-  </si>
-  <si>
-    <t>Forecast</t>
-  </si>
-  <si>
-    <t>Variance</t>
-  </si>
-  <si>
-    <t>No Show</t>
-  </si>
-  <si>
-    <t>Call Now</t>
-  </si>
-  <si>
-    <t>89.9%</t>
-  </si>
-  <si>
-    <t>80.0%</t>
-  </si>
-  <si>
-    <t>85.8%</t>
-  </si>
-  <si>
-    <t>97.3%</t>
-  </si>
-  <si>
-    <t>OEM</t>
-  </si>
-  <si>
-    <t>94.9%</t>
-  </si>
-  <si>
-    <t>ATTENDANCE REVIEW</t>
-  </si>
-  <si>
-    <t>Completed-day schedule-versus-observed decisions</t>
-  </si>
-  <si>
-    <t>01–07 Sep 2026</t>
-  </si>
-  <si>
-    <t>COMPLETED</t>
-  </si>
-  <si>
-    <t>Through 07 Sep</t>
-  </si>
-  <si>
-    <t>EVIDENCE</t>
-  </si>
-  <si>
-    <t>Agent Status + LILO</t>
-  </si>
-  <si>
-    <t>DECISION</t>
-  </si>
-  <si>
-    <t>REVIEW BOARD</t>
-  </si>
-  <si>
-    <t>REVIEW GAPS</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>Exact intervals</t>
-  </si>
-  <si>
-    <t>GAP HOURS</t>
-  </si>
-  <si>
-    <t>7.4</t>
-  </si>
-  <si>
-    <t>Exact minutes / 60</t>
-  </si>
-  <si>
-    <t>OPEN DECISIONS</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>Awaiting review</t>
-  </si>
-  <si>
-    <t>MISSING EVIDENCE</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>Never treated as zero</t>
-  </si>
-  <si>
-    <t>BY-LOB ACTION SUMMARY · SCHEDULE ABOVE ACTUAL</t>
-  </si>
-  <si>
-    <t>Exact Gaps</t>
-  </si>
-  <si>
-    <t>Gap Hours</t>
-  </si>
-  <si>
-    <t>Agents</t>
-  </si>
-  <si>
-    <t>Open</t>
-  </si>
-  <si>
-    <t>Approved</t>
-  </si>
-  <si>
-    <t>Dismissed</t>
   </si>
   <si>
     <t>Editable decision example</t>
@@ -410,7 +377,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="14">
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="0.00"/>
+    <numFmt numFmtId="165" formatCode="0%"/>
+    <numFmt numFmtId="166" formatCode="#,##0"/>
+    <numFmt numFmtId="167" formatCode="+0.00;-0.00;0.00"/>
+  </numFmts>
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -466,6 +439,81 @@
     </font>
     <font>
       <b/>
+      <sz val="22"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Display"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFDDE7EE"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF0B1F33"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0B1F33"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF0B1F33"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="34"/>
+      <color rgb="FF007C83"/>
+      <name val="Aptos Display"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="34"/>
+      <color rgb="FFD6A84B"/>
+      <name val="Aptos Display"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Display"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0B1F33"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF1F7A53"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFB42318"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
       <sz val="8"/>
       <color rgb="FF536474"/>
       <name val="Aptos"/>
@@ -505,7 +553,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -544,12 +592,36 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFD6A84B"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCEAF2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDE7E5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDF3E8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFE3F0FA"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -590,11 +662,46 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD8E0E6"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD8E0E6"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD8E0E6"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD8E0E6"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD8E0E6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFD8E0E6"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD8E0E6"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -611,22 +718,79 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="13" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="14" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="16" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="17" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="18" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -634,6 +798,631 @@
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="1" baseline="0">
+                <a:solidFill>
+                  <a:srgbClr val="0B1F33"/>
+                </a:solidFill>
+                <a:latin typeface="Aptos Display"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="1" baseline="0">
+                <a:solidFill>
+                  <a:srgbClr val="0B1F33"/>
+                </a:solidFill>
+                <a:latin typeface="Aptos Display"/>
+              </a:rPr>
+              <a:t>PCS BY LOB</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+    </c:title>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Current period</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="007C83"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0.00" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>PCS!$AD$2:$AD$5</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>RSA NL</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>RSA BE</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>FORD NL</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>OEM</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>PCS!$AE$2:$AE$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>4.62</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.38</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4.71</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4.55</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Prior comparable</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="536474"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0.00" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>PCS!$AD$2:$AD$5</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>RSA NL</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>RSA BE</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>FORD NL</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>OEM</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>PCS!$AF$2:$AF$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>4.51</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.31</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4.66</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4.48</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:axId val="50010001"/>
+        <c:axId val="50010002"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="50010001"/>
+        <c:scaling>
+          <c:orientation val="maxMin"/>
+        </c:scaling>
+        <c:axPos val="l"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" baseline="0">
+                <a:solidFill>
+                  <a:srgbClr val="0B1F33"/>
+                </a:solidFill>
+                <a:latin typeface="Aptos"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="50010002"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="50010002"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="5"/>
+          <c:min val="1"/>
+        </c:scaling>
+        <c:axPos val="t"/>
+        <c:majorGridlines/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="50010001"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+        <c:majorUnit val="1"/>
+      </c:valAx>
+      <c:spPr>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="536474"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="FFFFFF"/>
+    </a:solidFill>
+    <a:ln w="12700">
+      <a:solidFill>
+        <a:srgbClr val="D8E0E6"/>
+      </a:solidFill>
+    </a:ln>
+  </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="1" baseline="0">
+                <a:solidFill>
+                  <a:srgbClr val="0B1F33"/>
+                </a:solidFill>
+                <a:latin typeface="Aptos Display"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="1" baseline="0">
+                <a:solidFill>
+                  <a:srgbClr val="0B1F33"/>
+                </a:solidFill>
+                <a:latin typeface="Aptos Display"/>
+              </a:rPr>
+              <a:t>DAILY PCS TREND</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+    </c:title>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Current period</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="007C83"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>PCS!$AH$2:$AH$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>PCS!$AI$2:$AI$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>4.25</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.29</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4.33</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4.37</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4.41</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4.45</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4.49</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4.53</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Prior comparable</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="536474"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>PCS!$AH$2:$AH$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>PCS!$AJ$2:$AJ$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>4.18</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.215</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4.25</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4.285</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4.319999999999999</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4.355</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4.39</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4.425</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:marker val="1"/>
+        <c:axId val="50020001"/>
+        <c:axId val="50020002"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="50020001"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr val="D8E0E6"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="800" baseline="0">
+                <a:solidFill>
+                  <a:srgbClr val="536474"/>
+                </a:solidFill>
+                <a:latin typeface="Aptos"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="50020002"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="50020002"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="5"/>
+          <c:min val="2"/>
+        </c:scaling>
+        <c:axPos val="l"/>
+        <c:majorGridlines/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="50020001"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+        <c:majorUnit val="0.5"/>
+      </c:valAx>
+      <c:spPr>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="536474"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="FFFFFF"/>
+    </a:solidFill>
+    <a:ln w="12700">
+      <a:solidFill>
+        <a:srgbClr val="D8E0E6"/>
+      </a:solidFill>
+    </a:ln>
+  </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1183,327 +1972,787 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <tabColor rgb="FFD6A84B"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N25"/>
+  <dimension ref="A1:AJ32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="14" width="12.7109375" customWidth="1"/>
+    <col min="1" max="28" width="7.42578125" style="8" customWidth="1"/>
+    <col min="30" max="36" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="34" customHeight="1">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:36" ht="42" customHeight="1">
+      <c r="A1" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="2" t="s">
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="9"/>
+      <c r="Q1" s="9"/>
+      <c r="R1" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="S1" s="10"/>
+      <c r="T1" s="10"/>
+      <c r="U1" s="10"/>
+      <c r="V1" s="10"/>
+      <c r="W1" s="10"/>
+      <c r="X1" s="10"/>
+      <c r="Y1" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z1" s="11"/>
+      <c r="AA1" s="11"/>
+      <c r="AB1" s="11"/>
+    </row>
+    <row r="2" spans="1:36" ht="39" customHeight="1">
+      <c r="A2" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" s="12"/>
+      <c r="C2" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="I2" s="12"/>
+      <c r="J2" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="K2" s="13"/>
+      <c r="L2" s="13"/>
+      <c r="M2" s="13"/>
+      <c r="N2" s="13"/>
+      <c r="O2" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="P2" s="12"/>
+      <c r="Q2" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="R2" s="13"/>
+      <c r="S2" s="13"/>
+      <c r="T2" s="13"/>
+      <c r="U2" s="13"/>
+      <c r="V2" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="W2" s="12"/>
+      <c r="X2" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y2" s="13"/>
+      <c r="Z2" s="13"/>
+      <c r="AA2" s="13"/>
+      <c r="AB2" s="13"/>
+      <c r="AD2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AE2">
+        <v>4.62</v>
+      </c>
+      <c r="AF2">
+        <v>4.51</v>
+      </c>
+      <c r="AH2">
         <v>1</v>
       </c>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-    </row>
-    <row r="2" spans="1:14" ht="21" customHeight="1">
-      <c r="A2" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
-      <c r="N2" s="3"/>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="F4" s="9"/>
-      <c r="G4" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="H4" s="9" t="s">
+      <c r="AI2">
+        <v>4.25</v>
+      </c>
+      <c r="AJ2">
+        <v>4.18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:36" s="8" customFormat="1" ht="7.5" customHeight="1">
+      <c r="AD3" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="AE3" s="8">
+        <v>4.38</v>
+      </c>
+      <c r="AF3" s="8">
+        <v>4.31</v>
+      </c>
+      <c r="AH3" s="8">
+        <v>2</v>
+      </c>
+      <c r="AI3" s="8">
+        <v>4.29</v>
+      </c>
+      <c r="AJ3" s="8">
+        <v>4.215</v>
+      </c>
+    </row>
+    <row r="4" spans="1:36" ht="5.25" customHeight="1">
+      <c r="A4" s="14"/>
+      <c r="B4" s="14"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="15"/>
+      <c r="I4" s="15"/>
+      <c r="J4" s="15"/>
+      <c r="K4" s="15"/>
+      <c r="L4" s="15"/>
+      <c r="M4" s="15"/>
+      <c r="N4" s="15"/>
+      <c r="O4" s="14"/>
+      <c r="P4" s="14"/>
+      <c r="Q4" s="14"/>
+      <c r="R4" s="14"/>
+      <c r="S4" s="14"/>
+      <c r="T4" s="14"/>
+      <c r="U4" s="14"/>
+      <c r="V4" s="15"/>
+      <c r="W4" s="15"/>
+      <c r="X4" s="15"/>
+      <c r="Y4" s="15"/>
+      <c r="Z4" s="15"/>
+      <c r="AA4" s="15"/>
+      <c r="AB4" s="15"/>
+      <c r="AD4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE4">
+        <v>4.71</v>
+      </c>
+      <c r="AF4">
+        <v>4.66</v>
+      </c>
+      <c r="AH4">
+        <v>3</v>
+      </c>
+      <c r="AI4">
+        <v>4.33</v>
+      </c>
+      <c r="AJ4">
+        <v>4.25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:36" ht="27" customHeight="1">
+      <c r="A5" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" s="16"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="I5" s="16"/>
+      <c r="J5" s="16"/>
+      <c r="K5" s="16"/>
+      <c r="L5" s="16"/>
+      <c r="M5" s="16"/>
+      <c r="N5" s="16"/>
+      <c r="O5" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="P5" s="16"/>
+      <c r="Q5" s="16"/>
+      <c r="R5" s="16"/>
+      <c r="S5" s="16"/>
+      <c r="T5" s="16"/>
+      <c r="U5" s="16"/>
+      <c r="V5" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="W5" s="16"/>
+      <c r="X5" s="16"/>
+      <c r="Y5" s="16"/>
+      <c r="Z5" s="16"/>
+      <c r="AA5" s="16"/>
+      <c r="AB5" s="16"/>
+      <c r="AD5" t="s">
+        <v>44</v>
+      </c>
+      <c r="AE5">
+        <v>4.55</v>
+      </c>
+      <c r="AF5">
+        <v>4.48</v>
+      </c>
+      <c r="AH5">
+        <v>4</v>
+      </c>
+      <c r="AI5">
+        <v>4.37</v>
+      </c>
+      <c r="AJ5">
+        <v>4.285</v>
+      </c>
+    </row>
+    <row r="6" spans="1:36" ht="72" customHeight="1">
+      <c r="A6" s="17">
+        <v>4.54</v>
+      </c>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="18">
+        <v>0.268</v>
+      </c>
+      <c r="I6" s="18"/>
+      <c r="J6" s="18"/>
+      <c r="K6" s="18"/>
+      <c r="L6" s="18"/>
+      <c r="M6" s="18"/>
+      <c r="N6" s="18"/>
+      <c r="O6" s="17">
+        <v>4.42</v>
+      </c>
+      <c r="P6" s="17"/>
+      <c r="Q6" s="17"/>
+      <c r="R6" s="17"/>
+      <c r="S6" s="17"/>
+      <c r="T6" s="17"/>
+      <c r="U6" s="17"/>
+      <c r="V6" s="17">
+        <v>0.12</v>
+      </c>
+      <c r="W6" s="17"/>
+      <c r="X6" s="17"/>
+      <c r="Y6" s="17"/>
+      <c r="Z6" s="17"/>
+      <c r="AA6" s="17"/>
+      <c r="AB6" s="17"/>
+      <c r="AH6">
+        <v>5</v>
+      </c>
+      <c r="AI6">
+        <v>4.41</v>
+      </c>
+      <c r="AJ6">
+        <v>4.319999999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:36" s="8" customFormat="1" ht="7.5" customHeight="1">
+      <c r="AH7" s="8">
+        <v>6</v>
+      </c>
+      <c r="AI7" s="8">
+        <v>4.45</v>
+      </c>
+      <c r="AJ7" s="8">
+        <v>4.355</v>
+      </c>
+    </row>
+    <row r="8" spans="1:36" s="8" customFormat="1" ht="16.5" customHeight="1">
+      <c r="AH8" s="8">
+        <v>7</v>
+      </c>
+      <c r="AI8" s="8">
+        <v>4.49</v>
+      </c>
+      <c r="AJ8" s="8">
+        <v>4.39</v>
+      </c>
+    </row>
+    <row r="9" spans="1:36" s="8" customFormat="1" ht="16.5" customHeight="1">
+      <c r="AH9" s="8">
+        <v>8</v>
+      </c>
+      <c r="AI9" s="8">
+        <v>4.53</v>
+      </c>
+      <c r="AJ9" s="8">
+        <v>4.425</v>
+      </c>
+    </row>
+    <row r="10" spans="1:36" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="11" spans="1:36" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="12" spans="1:36" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="13" spans="1:36" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="14" spans="1:36" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="15" spans="1:36" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="16" spans="1:36" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="17" spans="1:28" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="18" spans="1:28" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="19" spans="1:28" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="20" spans="1:28" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="21" spans="1:28" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="22" spans="1:28" s="8" customFormat="1" ht="7.5" customHeight="1"/>
+    <row r="23" spans="1:28" ht="25.5" customHeight="1">
+      <c r="A23" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="B23" s="19"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="19"/>
+      <c r="F23" s="19"/>
+      <c r="G23" s="19"/>
+      <c r="H23" s="19"/>
+      <c r="I23" s="19"/>
+      <c r="J23" s="19"/>
+      <c r="K23" s="19"/>
+      <c r="L23" s="19"/>
+      <c r="M23" s="19"/>
+      <c r="N23" s="19"/>
+      <c r="O23" s="19"/>
+    </row>
+    <row r="24" spans="1:28" ht="22.5" customHeight="1">
+      <c r="A24" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="I4" s="9"/>
-      <c r="J4" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="K4" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="L4" s="9"/>
-      <c r="M4" s="9"/>
-      <c r="N4" s="9"/>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6" s="10" t="s">
+      <c r="B24" s="20"/>
+      <c r="C24" s="20"/>
+      <c r="D24" s="20"/>
+      <c r="E24" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="F24" s="20"/>
+      <c r="G24" s="20"/>
+      <c r="H24" s="20"/>
+      <c r="I24" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="J24" s="20"/>
+      <c r="K24" s="20"/>
+      <c r="L24" s="20"/>
+      <c r="M24" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
-      <c r="E6" s="10" t="s">
+      <c r="N24" s="20"/>
+      <c r="O24" s="20"/>
+      <c r="P24" s="20"/>
+      <c r="Q24" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="R24" s="20"/>
+      <c r="S24" s="20"/>
+      <c r="T24" s="20"/>
+      <c r="U24" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="I6" s="10"/>
-      <c r="J6" s="10"/>
-      <c r="L6" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="M6" s="10"/>
-      <c r="N6" s="10"/>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="A7" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="B7" s="11"/>
-      <c r="C7" s="11"/>
-      <c r="E7" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="F7" s="11"/>
-      <c r="G7" s="11"/>
-      <c r="H7" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="I7" s="11"/>
-      <c r="J7" s="11"/>
-      <c r="L7" s="11" t="s">
+      <c r="V24" s="20"/>
+      <c r="W24" s="20"/>
+      <c r="X24" s="20"/>
+      <c r="Y24" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="M7" s="11"/>
-      <c r="N7" s="11"/>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" s="11"/>
-      <c r="B8" s="11"/>
-      <c r="C8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
-      <c r="J8" s="11"/>
-      <c r="L8" s="11"/>
-      <c r="M8" s="11"/>
-      <c r="N8" s="11"/>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="B9" s="12"/>
-      <c r="C9" s="12"/>
-      <c r="E9" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="I9" s="12"/>
-      <c r="J9" s="12"/>
-      <c r="L9" s="12" t="s">
+      <c r="Z24" s="20"/>
+      <c r="AA24" s="20"/>
+      <c r="AB24" s="20"/>
+    </row>
+    <row r="25" spans="1:28" ht="19.5" customHeight="1">
+      <c r="A25" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="M9" s="12"/>
-      <c r="N9" s="12"/>
-    </row>
-    <row r="11" spans="1:14">
-      <c r="A11" s="4" t="s">
+      <c r="B25" s="21"/>
+      <c r="C25" s="21"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="22">
+        <v>12</v>
+      </c>
+      <c r="F25" s="22"/>
+      <c r="G25" s="22"/>
+      <c r="H25" s="22"/>
+      <c r="I25" s="23">
+        <v>0.29</v>
+      </c>
+      <c r="J25" s="23"/>
+      <c r="K25" s="23"/>
+      <c r="L25" s="23"/>
+      <c r="M25" s="24">
+        <v>4.62</v>
+      </c>
+      <c r="N25" s="24"/>
+      <c r="O25" s="24"/>
+      <c r="P25" s="24"/>
+      <c r="Q25" s="24">
+        <v>4.51</v>
+      </c>
+      <c r="R25" s="24"/>
+      <c r="S25" s="24"/>
+      <c r="T25" s="24"/>
+      <c r="U25" s="25">
+        <v>0.11</v>
+      </c>
+      <c r="V25" s="25"/>
+      <c r="W25" s="25"/>
+      <c r="X25" s="25"/>
+      <c r="Y25" s="26">
+        <v>2</v>
+      </c>
+      <c r="Z25" s="26"/>
+      <c r="AA25" s="26"/>
+      <c r="AB25" s="26"/>
+    </row>
+    <row r="26" spans="1:28" ht="19.5" customHeight="1">
+      <c r="A26" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4"/>
-      <c r="J11" s="4"/>
-      <c r="K11" s="4"/>
-      <c r="L11" s="4"/>
-      <c r="M11" s="4"/>
-      <c r="N11" s="4"/>
-    </row>
-    <row r="13" spans="1:14">
-      <c r="A13" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13" s="5" t="s">
+      <c r="B26" s="21"/>
+      <c r="C26" s="21"/>
+      <c r="D26" s="21"/>
+      <c r="E26" s="22">
+        <v>10</v>
+      </c>
+      <c r="F26" s="22"/>
+      <c r="G26" s="22"/>
+      <c r="H26" s="22"/>
+      <c r="I26" s="23">
+        <v>0.25</v>
+      </c>
+      <c r="J26" s="23"/>
+      <c r="K26" s="23"/>
+      <c r="L26" s="23"/>
+      <c r="M26" s="24">
+        <v>3.92</v>
+      </c>
+      <c r="N26" s="24"/>
+      <c r="O26" s="24"/>
+      <c r="P26" s="24"/>
+      <c r="Q26" s="24">
+        <v>4.08</v>
+      </c>
+      <c r="R26" s="24"/>
+      <c r="S26" s="24"/>
+      <c r="T26" s="24"/>
+      <c r="U26" s="27">
+        <v>-0.16</v>
+      </c>
+      <c r="V26" s="27"/>
+      <c r="W26" s="27"/>
+      <c r="X26" s="27"/>
+      <c r="Y26" s="26">
+        <v>5</v>
+      </c>
+      <c r="Z26" s="26"/>
+      <c r="AA26" s="26"/>
+      <c r="AB26" s="26"/>
+    </row>
+    <row r="27" spans="1:28" ht="19.5" customHeight="1">
+      <c r="A27" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="B27" s="21"/>
+      <c r="C27" s="21"/>
+      <c r="D27" s="21"/>
+      <c r="E27" s="22">
+        <v>11</v>
+      </c>
+      <c r="F27" s="22"/>
+      <c r="G27" s="22"/>
+      <c r="H27" s="22"/>
+      <c r="I27" s="23">
+        <v>0.27</v>
+      </c>
+      <c r="J27" s="23"/>
+      <c r="K27" s="23"/>
+      <c r="L27" s="23"/>
+      <c r="M27" s="24">
+        <v>4.38</v>
+      </c>
+      <c r="N27" s="24"/>
+      <c r="O27" s="24"/>
+      <c r="P27" s="24"/>
+      <c r="Q27" s="24">
+        <v>4.31</v>
+      </c>
+      <c r="R27" s="24"/>
+      <c r="S27" s="24"/>
+      <c r="T27" s="24"/>
+      <c r="U27" s="25">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="V27" s="25"/>
+      <c r="W27" s="25"/>
+      <c r="X27" s="25"/>
+      <c r="Y27" s="26">
+        <v>1</v>
+      </c>
+      <c r="Z27" s="26"/>
+      <c r="AA27" s="26"/>
+      <c r="AB27" s="26"/>
+    </row>
+    <row r="28" spans="1:28" ht="19.5" customHeight="1">
+      <c r="A28" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="E13" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
-      <c r="A14" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B14" s="6">
-        <v>4.62</v>
-      </c>
-      <c r="C14" s="6">
-        <v>4.51</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="E14" s="6">
-        <v>412</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
-      <c r="A15" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="B15" s="6">
-        <v>4.38</v>
-      </c>
-      <c r="C15" s="6">
-        <v>4.31</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="E15" s="6">
-        <v>286</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14">
-      <c r="A16" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="B16" s="6">
+      <c r="B28" s="21"/>
+      <c r="C28" s="21"/>
+      <c r="D28" s="21"/>
+      <c r="E28" s="22">
+        <v>9</v>
+      </c>
+      <c r="F28" s="22"/>
+      <c r="G28" s="22"/>
+      <c r="H28" s="22"/>
+      <c r="I28" s="23">
+        <v>0.31</v>
+      </c>
+      <c r="J28" s="23"/>
+      <c r="K28" s="23"/>
+      <c r="L28" s="23"/>
+      <c r="M28" s="24">
         <v>4.71</v>
       </c>
-      <c r="C16" s="6">
+      <c r="N28" s="24"/>
+      <c r="O28" s="24"/>
+      <c r="P28" s="24"/>
+      <c r="Q28" s="24">
         <v>4.66</v>
       </c>
-      <c r="D16" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="E16" s="6">
-        <v>398</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14">
-      <c r="A17" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="B17" s="6">
-        <v>4.55</v>
-      </c>
-      <c r="C17" s="6">
-        <v>4.48</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="E17" s="6">
-        <v>312</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14">
-      <c r="A25" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
-      <c r="G25" s="7"/>
-      <c r="H25" s="7"/>
-      <c r="I25" s="7"/>
-      <c r="J25" s="7"/>
-      <c r="K25" s="7"/>
-      <c r="L25" s="7"/>
-      <c r="M25" s="7"/>
-      <c r="N25" s="7"/>
+      <c r="R28" s="24"/>
+      <c r="S28" s="24"/>
+      <c r="T28" s="24"/>
+      <c r="U28" s="25">
+        <v>0.05</v>
+      </c>
+      <c r="V28" s="25"/>
+      <c r="W28" s="25"/>
+      <c r="X28" s="25"/>
+      <c r="Y28" s="28">
+        <v>0</v>
+      </c>
+      <c r="Z28" s="28"/>
+      <c r="AA28" s="28"/>
+      <c r="AB28" s="28"/>
+    </row>
+    <row r="29" spans="1:28" ht="19.5" customHeight="1">
+      <c r="A29" s="21"/>
+      <c r="B29" s="21"/>
+      <c r="C29" s="21"/>
+      <c r="D29" s="21"/>
+      <c r="E29" s="22"/>
+      <c r="F29" s="22"/>
+      <c r="G29" s="22"/>
+      <c r="H29" s="22"/>
+      <c r="I29" s="23"/>
+      <c r="J29" s="23"/>
+      <c r="K29" s="23"/>
+      <c r="L29" s="23"/>
+      <c r="M29" s="24"/>
+      <c r="N29" s="24"/>
+      <c r="O29" s="24"/>
+      <c r="P29" s="24"/>
+      <c r="Q29" s="24"/>
+      <c r="R29" s="24"/>
+      <c r="S29" s="24"/>
+      <c r="T29" s="24"/>
+      <c r="U29" s="27"/>
+      <c r="V29" s="27"/>
+      <c r="W29" s="27"/>
+      <c r="X29" s="27"/>
+      <c r="Y29" s="28"/>
+      <c r="Z29" s="28"/>
+      <c r="AA29" s="28"/>
+      <c r="AB29" s="28"/>
+    </row>
+    <row r="30" spans="1:28" ht="19.5" customHeight="1">
+      <c r="A30" s="21"/>
+      <c r="B30" s="21"/>
+      <c r="C30" s="21"/>
+      <c r="D30" s="21"/>
+      <c r="E30" s="22"/>
+      <c r="F30" s="22"/>
+      <c r="G30" s="22"/>
+      <c r="H30" s="22"/>
+      <c r="I30" s="23"/>
+      <c r="J30" s="23"/>
+      <c r="K30" s="23"/>
+      <c r="L30" s="23"/>
+      <c r="M30" s="24"/>
+      <c r="N30" s="24"/>
+      <c r="O30" s="24"/>
+      <c r="P30" s="24"/>
+      <c r="Q30" s="24"/>
+      <c r="R30" s="24"/>
+      <c r="S30" s="24"/>
+      <c r="T30" s="24"/>
+      <c r="U30" s="27"/>
+      <c r="V30" s="27"/>
+      <c r="W30" s="27"/>
+      <c r="X30" s="27"/>
+      <c r="Y30" s="28"/>
+      <c r="Z30" s="28"/>
+      <c r="AA30" s="28"/>
+      <c r="AB30" s="28"/>
+    </row>
+    <row r="31" spans="1:28" ht="19.5" customHeight="1">
+      <c r="A31" s="21"/>
+      <c r="B31" s="21"/>
+      <c r="C31" s="21"/>
+      <c r="D31" s="21"/>
+      <c r="E31" s="22"/>
+      <c r="F31" s="22"/>
+      <c r="G31" s="22"/>
+      <c r="H31" s="22"/>
+      <c r="I31" s="23"/>
+      <c r="J31" s="23"/>
+      <c r="K31" s="23"/>
+      <c r="L31" s="23"/>
+      <c r="M31" s="24"/>
+      <c r="N31" s="24"/>
+      <c r="O31" s="24"/>
+      <c r="P31" s="24"/>
+      <c r="Q31" s="24"/>
+      <c r="R31" s="24"/>
+      <c r="S31" s="24"/>
+      <c r="T31" s="24"/>
+      <c r="U31" s="27"/>
+      <c r="V31" s="27"/>
+      <c r="W31" s="27"/>
+      <c r="X31" s="27"/>
+      <c r="Y31" s="28"/>
+      <c r="Z31" s="28"/>
+      <c r="AA31" s="28"/>
+      <c r="AB31" s="28"/>
+    </row>
+    <row r="32" spans="1:28" ht="19.5" customHeight="1">
+      <c r="A32" s="21"/>
+      <c r="B32" s="21"/>
+      <c r="C32" s="21"/>
+      <c r="D32" s="21"/>
+      <c r="E32" s="22"/>
+      <c r="F32" s="22"/>
+      <c r="G32" s="22"/>
+      <c r="H32" s="22"/>
+      <c r="I32" s="23"/>
+      <c r="J32" s="23"/>
+      <c r="K32" s="23"/>
+      <c r="L32" s="23"/>
+      <c r="M32" s="24"/>
+      <c r="N32" s="24"/>
+      <c r="O32" s="24"/>
+      <c r="P32" s="24"/>
+      <c r="Q32" s="24"/>
+      <c r="R32" s="24"/>
+      <c r="S32" s="24"/>
+      <c r="T32" s="24"/>
+      <c r="U32" s="27"/>
+      <c r="V32" s="27"/>
+      <c r="W32" s="27"/>
+      <c r="X32" s="27"/>
+      <c r="Y32" s="28"/>
+      <c r="Z32" s="28"/>
+      <c r="AA32" s="28"/>
+      <c r="AB32" s="28"/>
     </row>
   </sheetData>
-  <mergeCells count="21">
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="L1:N1"/>
-    <mergeCell ref="A2:N2"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="K4:N4"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A7:C8"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="E6:G6"/>
-    <mergeCell ref="E7:G8"/>
-    <mergeCell ref="E9:G9"/>
-    <mergeCell ref="H6:J6"/>
-    <mergeCell ref="H7:J8"/>
-    <mergeCell ref="H9:J9"/>
-    <mergeCell ref="L6:N6"/>
-    <mergeCell ref="L7:N8"/>
-    <mergeCell ref="L9:N9"/>
-    <mergeCell ref="A11:N11"/>
-    <mergeCell ref="A25:N25"/>
+  <mergeCells count="87">
+    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="R1:X1"/>
+    <mergeCell ref="Y1:AB1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="J2:N2"/>
+    <mergeCell ref="O2:P2"/>
+    <mergeCell ref="Q2:U2"/>
+    <mergeCell ref="V2:W2"/>
+    <mergeCell ref="X2:AB2"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="H4:N4"/>
+    <mergeCell ref="H5:N5"/>
+    <mergeCell ref="H6:N6"/>
+    <mergeCell ref="O4:U4"/>
+    <mergeCell ref="O5:U5"/>
+    <mergeCell ref="O6:U6"/>
+    <mergeCell ref="V4:AB4"/>
+    <mergeCell ref="V5:AB5"/>
+    <mergeCell ref="V6:AB6"/>
+    <mergeCell ref="A23:O23"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="E24:H24"/>
+    <mergeCell ref="I24:L24"/>
+    <mergeCell ref="M24:P24"/>
+    <mergeCell ref="Q24:T24"/>
+    <mergeCell ref="U24:X24"/>
+    <mergeCell ref="Y24:AB24"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="E25:H25"/>
+    <mergeCell ref="I25:L25"/>
+    <mergeCell ref="M25:P25"/>
+    <mergeCell ref="Q25:T25"/>
+    <mergeCell ref="U25:X25"/>
+    <mergeCell ref="Y25:AB25"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="E26:H26"/>
+    <mergeCell ref="I26:L26"/>
+    <mergeCell ref="M26:P26"/>
+    <mergeCell ref="Q26:T26"/>
+    <mergeCell ref="U26:X26"/>
+    <mergeCell ref="Y26:AB26"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="E27:H27"/>
+    <mergeCell ref="I27:L27"/>
+    <mergeCell ref="M27:P27"/>
+    <mergeCell ref="Q27:T27"/>
+    <mergeCell ref="U27:X27"/>
+    <mergeCell ref="Y27:AB27"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="E28:H28"/>
+    <mergeCell ref="I28:L28"/>
+    <mergeCell ref="M28:P28"/>
+    <mergeCell ref="Q28:T28"/>
+    <mergeCell ref="U28:X28"/>
+    <mergeCell ref="Y28:AB28"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="E29:H29"/>
+    <mergeCell ref="I29:L29"/>
+    <mergeCell ref="M29:P29"/>
+    <mergeCell ref="Q29:T29"/>
+    <mergeCell ref="U29:X29"/>
+    <mergeCell ref="Y29:AB29"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="E30:H30"/>
+    <mergeCell ref="I30:L30"/>
+    <mergeCell ref="M30:P30"/>
+    <mergeCell ref="Q30:T30"/>
+    <mergeCell ref="U30:X30"/>
+    <mergeCell ref="Y30:AB30"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="E31:H31"/>
+    <mergeCell ref="I31:L31"/>
+    <mergeCell ref="M31:P31"/>
+    <mergeCell ref="Q31:T31"/>
+    <mergeCell ref="U31:X31"/>
+    <mergeCell ref="Y31:AB31"/>
+    <mergeCell ref="A32:D32"/>
+    <mergeCell ref="E32:H32"/>
+    <mergeCell ref="I32:L32"/>
+    <mergeCell ref="M32:P32"/>
+    <mergeCell ref="Q32:T32"/>
+    <mergeCell ref="U32:X32"/>
+    <mergeCell ref="Y32:AB32"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.15" right="0.15" top="0.2" bottom="0.2" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape"/>
   <headerFooter>
     <oddFooter>&amp;LPrepared by Anass ASSRI | WFM&amp;CDesign reference&amp;RConfidential</oddFooter>
   </headerFooter>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1520,7 +2769,7 @@
   <sheetData>
     <row r="1" spans="1:14" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1540,7 +2789,7 @@
     </row>
     <row r="2" spans="1:14" ht="21" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -1557,120 +2806,120 @@
       <c r="N2" s="3"/>
     </row>
     <row r="4" spans="1:14">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="29" t="s">
+        <v>54</v>
+      </c>
+      <c r="B4" s="30" t="s">
+        <v>55</v>
+      </c>
+      <c r="C4" s="30"/>
+      <c r="D4" s="29" t="s">
+        <v>56</v>
+      </c>
+      <c r="E4" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="F4" s="30"/>
+      <c r="G4" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="H4" s="30" t="s">
+        <v>58</v>
+      </c>
+      <c r="I4" s="30"/>
+      <c r="J4" s="29" t="s">
+        <v>59</v>
+      </c>
+      <c r="K4" s="30" t="s">
+        <v>60</v>
+      </c>
+      <c r="L4" s="30"/>
+      <c r="M4" s="30"/>
+      <c r="N4" s="30"/>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="B6" s="31"/>
+      <c r="C6" s="31"/>
+      <c r="E6" s="31" t="s">
+        <v>64</v>
+      </c>
+      <c r="F6" s="31"/>
+      <c r="G6" s="31"/>
+      <c r="H6" s="31" t="s">
+        <v>67</v>
+      </c>
+      <c r="I6" s="31"/>
+      <c r="J6" s="31"/>
+      <c r="L6" s="31" t="s">
+        <v>70</v>
+      </c>
+      <c r="M6" s="31"/>
+      <c r="N6" s="31"/>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" s="32" t="s">
+        <v>62</v>
+      </c>
+      <c r="B7" s="32"/>
+      <c r="C7" s="32"/>
+      <c r="E7" s="32" t="s">
+        <v>65</v>
+      </c>
+      <c r="F7" s="32"/>
+      <c r="G7" s="32"/>
+      <c r="H7" s="32" t="s">
+        <v>68</v>
+      </c>
+      <c r="I7" s="32"/>
+      <c r="J7" s="32"/>
+      <c r="L7" s="32" t="s">
+        <v>71</v>
+      </c>
+      <c r="M7" s="32"/>
+      <c r="N7" s="32"/>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="32"/>
+      <c r="B8" s="32"/>
+      <c r="C8" s="32"/>
+      <c r="E8" s="32"/>
+      <c r="F8" s="32"/>
+      <c r="G8" s="32"/>
+      <c r="H8" s="32"/>
+      <c r="I8" s="32"/>
+      <c r="J8" s="32"/>
+      <c r="L8" s="32"/>
+      <c r="M8" s="32"/>
+      <c r="N8" s="32"/>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" s="33" t="s">
+        <v>63</v>
+      </c>
+      <c r="B9" s="33"/>
+      <c r="C9" s="33"/>
+      <c r="E9" s="33" t="s">
         <v>66</v>
       </c>
-      <c r="B4" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="E4" s="9" t="s">
+      <c r="F9" s="33"/>
+      <c r="G9" s="33"/>
+      <c r="H9" s="33" t="s">
         <v>69</v>
       </c>
-      <c r="F4" s="9"/>
-      <c r="G4" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="H4" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="I4" s="9"/>
-      <c r="J4" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="K4" s="9" t="s">
+      <c r="I9" s="33"/>
+      <c r="J9" s="33"/>
+      <c r="L9" s="33" t="s">
         <v>72</v>
       </c>
-      <c r="L4" s="9"/>
-      <c r="M4" s="9"/>
-      <c r="N4" s="9"/>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
-      <c r="E6" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="I6" s="10"/>
-      <c r="J6" s="10"/>
-      <c r="L6" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="M6" s="10"/>
-      <c r="N6" s="10"/>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="A7" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="B7" s="11"/>
-      <c r="C7" s="11"/>
-      <c r="E7" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="F7" s="11"/>
-      <c r="G7" s="11"/>
-      <c r="H7" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="I7" s="11"/>
-      <c r="J7" s="11"/>
-      <c r="L7" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="M7" s="11"/>
-      <c r="N7" s="11"/>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" s="11"/>
-      <c r="B8" s="11"/>
-      <c r="C8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
-      <c r="J8" s="11"/>
-      <c r="L8" s="11"/>
-      <c r="M8" s="11"/>
-      <c r="N8" s="11"/>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="B9" s="12"/>
-      <c r="C9" s="12"/>
-      <c r="E9" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="I9" s="12"/>
-      <c r="J9" s="12"/>
-      <c r="L9" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="M9" s="12"/>
-      <c r="N9" s="12"/>
+      <c r="M9" s="33"/>
+      <c r="N9" s="33"/>
     </row>
     <row r="11" spans="1:14">
       <c r="A11" s="4" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
@@ -1688,39 +2937,39 @@
     </row>
     <row r="13" spans="1:14">
       <c r="A13" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
     </row>
     <row r="14" spans="1:14">
       <c r="A14" s="6" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="D14" s="6">
         <v>840</v>
@@ -1740,13 +2989,13 @@
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="6" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="D15" s="6">
         <v>530</v>
@@ -1766,13 +3015,13 @@
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="6" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="D16" s="6">
         <v>320</v>
@@ -1792,13 +3041,13 @@
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="6" t="s">
-        <v>97</v>
+        <v>44</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="D17" s="6">
         <v>410</v>
@@ -1818,7 +3067,7 @@
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="7" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
@@ -1878,7 +3127,7 @@
   <sheetData>
     <row r="1" spans="1:14" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1898,7 +3147,7 @@
     </row>
     <row r="2" spans="1:14" ht="21" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -1915,120 +3164,120 @@
       <c r="N2" s="3"/>
     </row>
     <row r="4" spans="1:14">
-      <c r="A4" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="B4" s="9" t="s">
+      <c r="A4" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="C4" s="30"/>
+      <c r="D4" s="29" t="s">
+        <v>90</v>
+      </c>
+      <c r="E4" s="30" t="s">
+        <v>91</v>
+      </c>
+      <c r="F4" s="30"/>
+      <c r="G4" s="29" t="s">
+        <v>92</v>
+      </c>
+      <c r="H4" s="30" t="s">
+        <v>93</v>
+      </c>
+      <c r="I4" s="30"/>
+      <c r="J4" s="29" t="s">
+        <v>94</v>
+      </c>
+      <c r="K4" s="30" t="s">
+        <v>95</v>
+      </c>
+      <c r="L4" s="30"/>
+      <c r="M4" s="30"/>
+      <c r="N4" s="30"/>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" s="31" t="s">
+        <v>96</v>
+      </c>
+      <c r="B6" s="31"/>
+      <c r="C6" s="31"/>
+      <c r="E6" s="31" t="s">
+        <v>99</v>
+      </c>
+      <c r="F6" s="31"/>
+      <c r="G6" s="31"/>
+      <c r="H6" s="31" t="s">
+        <v>102</v>
+      </c>
+      <c r="I6" s="31"/>
+      <c r="J6" s="31"/>
+      <c r="L6" s="31" t="s">
+        <v>105</v>
+      </c>
+      <c r="M6" s="31"/>
+      <c r="N6" s="31"/>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" s="32" t="s">
+        <v>97</v>
+      </c>
+      <c r="B7" s="32"/>
+      <c r="C7" s="32"/>
+      <c r="E7" s="32" t="s">
+        <v>100</v>
+      </c>
+      <c r="F7" s="32"/>
+      <c r="G7" s="32"/>
+      <c r="H7" s="32" t="s">
+        <v>103</v>
+      </c>
+      <c r="I7" s="32"/>
+      <c r="J7" s="32"/>
+      <c r="L7" s="32" t="s">
+        <v>106</v>
+      </c>
+      <c r="M7" s="32"/>
+      <c r="N7" s="32"/>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="32"/>
+      <c r="B8" s="32"/>
+      <c r="C8" s="32"/>
+      <c r="E8" s="32"/>
+      <c r="F8" s="32"/>
+      <c r="G8" s="32"/>
+      <c r="H8" s="32"/>
+      <c r="I8" s="32"/>
+      <c r="J8" s="32"/>
+      <c r="L8" s="32"/>
+      <c r="M8" s="32"/>
+      <c r="N8" s="32"/>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="B9" s="33"/>
+      <c r="C9" s="33"/>
+      <c r="E9" s="33" t="s">
         <v>101</v>
       </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="F4" s="9"/>
-      <c r="G4" s="8" t="s">
+      <c r="F9" s="33"/>
+      <c r="G9" s="33"/>
+      <c r="H9" s="33" t="s">
         <v>104</v>
       </c>
-      <c r="H4" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="I4" s="9"/>
-      <c r="J4" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="K4" s="9" t="s">
+      <c r="I9" s="33"/>
+      <c r="J9" s="33"/>
+      <c r="L9" s="33" t="s">
         <v>107</v>
       </c>
-      <c r="L4" s="9"/>
-      <c r="M4" s="9"/>
-      <c r="N4" s="9"/>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
-      <c r="E6" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="I6" s="10"/>
-      <c r="J6" s="10"/>
-      <c r="L6" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="M6" s="10"/>
-      <c r="N6" s="10"/>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="A7" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="B7" s="11"/>
-      <c r="C7" s="11"/>
-      <c r="E7" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="F7" s="11"/>
-      <c r="G7" s="11"/>
-      <c r="H7" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="I7" s="11"/>
-      <c r="J7" s="11"/>
-      <c r="L7" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="M7" s="11"/>
-      <c r="N7" s="11"/>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" s="11"/>
-      <c r="B8" s="11"/>
-      <c r="C8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
-      <c r="J8" s="11"/>
-      <c r="L8" s="11"/>
-      <c r="M8" s="11"/>
-      <c r="N8" s="11"/>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="B9" s="12"/>
-      <c r="C9" s="12"/>
-      <c r="E9" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="12" t="s">
-        <v>116</v>
-      </c>
-      <c r="I9" s="12"/>
-      <c r="J9" s="12"/>
-      <c r="L9" s="12" t="s">
-        <v>119</v>
-      </c>
-      <c r="M9" s="12"/>
-      <c r="N9" s="12"/>
+      <c r="M9" s="33"/>
+      <c r="N9" s="33"/>
     </row>
     <row r="11" spans="1:14">
       <c r="A11" s="4" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
@@ -2046,30 +3295,30 @@
     </row>
     <row r="13" spans="1:14">
       <c r="A13" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
     </row>
     <row r="14" spans="1:14">
       <c r="A14" s="6" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="B14" s="6">
         <v>6</v>
@@ -2092,7 +3341,7 @@
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="6" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="B15" s="6">
         <v>5</v>
@@ -2115,7 +3364,7 @@
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="6" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="B16" s="6">
         <v>4</v>
@@ -2138,7 +3387,7 @@
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="6" t="s">
-        <v>61</v>
+        <v>115</v>
       </c>
       <c r="B17" s="6">
         <v>3</v>
@@ -2161,20 +3410,20 @@
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="4" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="B21" s="13" t="s">
-        <v>124</v>
+        <v>117</v>
+      </c>
+      <c r="B21" s="34" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="7" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>

--- a/docs/WFMHub Report Design Reference.xlsx
+++ b/docs/WFMHub Report Design Reference.xlsx
@@ -11,13 +11,178 @@
     <sheet name="PCS" sheetId="2" r:id="rId2"/>
     <sheet name="RTM" sheetId="3" r:id="rId3"/>
     <sheet name="ATTENDANCE" sheetId="4" r:id="rId4"/>
+    <sheet name="STAFFING" sheetId="5" r:id="rId5"/>
+    <sheet name="REALISATIONS" sheetId="6" r:id="rId6"/>
+    <sheet name="ABSENCE" sheetId="7" r:id="rId7"/>
+    <sheet name="BONUS" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Anass ASSRI</author>
+  </authors>
+  <commentList>
+    <comment ref="Y1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Illustrative values only; production reports use governed data.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Anass ASSRI</author>
+  </authors>
+  <commentList>
+    <comment ref="Y1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Illustrative values only; production reports use governed data.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Anass ASSRI</author>
+  </authors>
+  <commentList>
+    <comment ref="Y1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Illustrative values only; production reports use governed data.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Anass ASSRI</author>
+  </authors>
+  <commentList>
+    <comment ref="Y1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Illustrative values only; production reports use governed data.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Anass ASSRI</author>
+  </authors>
+  <commentList>
+    <comment ref="Y1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Illustrative values only; production reports use governed data.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments6.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Anass ASSRI</author>
+  </authors>
+  <commentList>
+    <comment ref="Y1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Illustrative values only; production reports use governed data.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments7.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Anass ASSRI</author>
+  </authors>
+  <commentList>
+    <comment ref="Y1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Illustrative values only; production reports use governed data.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="186">
   <si>
     <t>WFMHUB REPORT SYSTEM</t>
   </si>
@@ -25,7 +190,7 @@
     <t>UPDATED</t>
   </si>
   <si>
-    <t>WFMHUB-DESIGN 2.0.0 · approved visual contract</t>
+    <t>WFMHUB-DESIGN 2.1.0 · approved visual contract</t>
   </si>
   <si>
     <t>TOKENS</t>
@@ -109,7 +274,7 @@
     <t>WFMHUB  |  ANASS ASSRI</t>
   </si>
   <si>
-    <t>DATA FRESH</t>
+    <t>REFERENCE</t>
   </si>
   <si>
     <t>PERIOD</t>
@@ -142,6 +307,9 @@
     <t>CHANGE</t>
   </si>
   <si>
+    <t>Category</t>
+  </si>
+  <si>
     <t>RSA NL</t>
   </si>
   <si>
@@ -154,6 +322,27 @@
     <t>OEM</t>
   </si>
   <si>
+    <t>Current</t>
+  </si>
+  <si>
+    <t>Prior</t>
+  </si>
+  <si>
+    <t>01</t>
+  </si>
+  <si>
+    <t>02</t>
+  </si>
+  <si>
+    <t>03</t>
+  </si>
+  <si>
+    <t>04</t>
+  </si>
+  <si>
+    <t>05</t>
+  </si>
+  <si>
     <t>TEAM PERFORMANCE &amp; ACTIONS</t>
   </si>
   <si>
@@ -169,18 +358,9 @@
     <t>Karim Belkacem</t>
   </si>
   <si>
-    <t>Elena Rossi</t>
-  </si>
-  <si>
-    <t>Daniel Weber</t>
-  </si>
-  <si>
     <t>RTM DAILY CONTROL</t>
   </si>
   <si>
-    <t>Combined service, attendance pulse and exact call actions</t>
-  </si>
-  <si>
     <t>DATE</t>
   </si>
   <si>
@@ -193,54 +373,30 @@
     <t>Through 17:59</t>
   </si>
   <si>
-    <t>All operational</t>
+    <t>All 4</t>
   </si>
   <si>
     <t>ATTENDANCE</t>
   </si>
   <si>
-    <t>17:45</t>
+    <t>17:55</t>
   </si>
   <si>
     <t>LOBS ON TARGET</t>
   </si>
   <si>
-    <t>3 / 4</t>
-  </si>
-  <si>
-    <t>Configured target</t>
+    <t>4 / 4</t>
   </si>
   <si>
     <t>DEMAND VARIANCE</t>
   </si>
   <si>
-    <t>+84</t>
-  </si>
-  <si>
-    <t>Actual minus forecast</t>
-  </si>
-  <si>
     <t>NO SHOW HC</t>
   </si>
   <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>Evidence proven</t>
-  </si>
-  <si>
     <t>CALL NOW</t>
   </si>
   <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>Exact lists by LOB</t>
-  </si>
-  <si>
-    <t>SERVICE LEVEL BY LOB · LINKED OPERATIONAL TABLE</t>
-  </si>
-  <si>
     <t>TSL</t>
   </si>
   <si>
@@ -253,39 +409,24 @@
     <t>Forecast</t>
   </si>
   <si>
-    <t>Variance</t>
-  </si>
-  <si>
-    <t>No Show</t>
-  </si>
-  <si>
-    <t>Call Now</t>
-  </si>
-  <si>
-    <t>89.9%</t>
-  </si>
-  <si>
-    <t>80.0%</t>
-  </si>
-  <si>
-    <t>85.8%</t>
-  </si>
-  <si>
-    <t>97.3%</t>
-  </si>
-  <si>
-    <t>94.9%</t>
-  </si>
-  <si>
-    <t>Examples are visual only. Calculations, targets and LOBs always come from WFMHub authorities.</t>
+    <t>LOB SERVICE &amp; ATTENDANCE ACTIONS</t>
+  </si>
+  <si>
+    <t>VAR CALLS</t>
+  </si>
+  <si>
+    <t>NO SHOW</t>
+  </si>
+  <si>
+    <t>LATE</t>
+  </si>
+  <si>
+    <t>EARLY LEAVE</t>
   </si>
   <si>
     <t>ATTENDANCE REVIEW</t>
   </si>
   <si>
-    <t>Completed-day schedule-versus-observed decisions</t>
-  </si>
-  <si>
     <t>01–07 Sep 2026</t>
   </si>
   <si>
@@ -298,61 +439,28 @@
     <t>EVIDENCE</t>
   </si>
   <si>
-    <t>Agent Status + LILO</t>
+    <t>Status + LILO</t>
   </si>
   <si>
     <t>DECISION</t>
   </si>
   <si>
-    <t>REVIEW BOARD</t>
+    <t>Review board</t>
   </si>
   <si>
     <t>REVIEW GAPS</t>
   </si>
   <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>Exact intervals</t>
-  </si>
-  <si>
     <t>GAP HOURS</t>
   </si>
   <si>
-    <t>7.4</t>
-  </si>
-  <si>
-    <t>Exact minutes / 60</t>
-  </si>
-  <si>
     <t>OPEN DECISIONS</t>
   </si>
   <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>Awaiting review</t>
-  </si>
-  <si>
     <t>MISSING EVIDENCE</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>Never treated as zero</t>
-  </si>
-  <si>
-    <t>BY-LOB ACTION SUMMARY · SCHEDULE ABOVE ACTUAL</t>
-  </si>
-  <si>
-    <t>Exact Gaps</t>
-  </si>
-  <si>
-    <t>Gap Hours</t>
-  </si>
-  <si>
-    <t>Agents</t>
+    <t>Gap hours</t>
   </si>
   <si>
     <t>Open</t>
@@ -364,26 +472,288 @@
     <t>Dismissed</t>
   </si>
   <si>
-    <t>OEM FR</t>
-  </si>
-  <si>
-    <t>Editable decision example</t>
-  </si>
-  <si>
-    <t>Decision Status</t>
+    <t>Missing</t>
+  </si>
+  <si>
+    <t>Cases</t>
+  </si>
+  <si>
+    <t>BY-LOB REVIEW ACTIONS</t>
+  </si>
+  <si>
+    <t>EXACT GAPS</t>
+  </si>
+  <si>
+    <t>AGENTS</t>
+  </si>
+  <si>
+    <t>OPEN</t>
+  </si>
+  <si>
+    <t>APPROVED</t>
+  </si>
+  <si>
+    <t>DISMISSED</t>
+  </si>
+  <si>
+    <t>STAFFING &amp; COVERAGE</t>
+  </si>
+  <si>
+    <t>Current + 4 weeks</t>
+  </si>
+  <si>
+    <t>MODE</t>
+  </si>
+  <si>
+    <t>Future plan</t>
+  </si>
+  <si>
+    <t>LANGUAGE</t>
+  </si>
+  <si>
+    <t>PEAK GAP FTE</t>
+  </si>
+  <si>
+    <t>FUTURE GAP HOURS</t>
+  </si>
+  <si>
+    <t>FORECAST COVERAGE</t>
+  </si>
+  <si>
+    <t>PTO / AWAY IMPACT</t>
+  </si>
+  <si>
+    <t>Required</t>
+  </si>
+  <si>
+    <t>Net scheduled</t>
+  </si>
+  <si>
+    <t>Mon</t>
+  </si>
+  <si>
+    <t>Tue</t>
+  </si>
+  <si>
+    <t>Wed</t>
+  </si>
+  <si>
+    <t>Thu</t>
+  </si>
+  <si>
+    <t>Fri</t>
+  </si>
+  <si>
+    <t>Gap FTE</t>
+  </si>
+  <si>
+    <t>PRIORITIZED CAPACITY ACTIONS</t>
+  </si>
+  <si>
+    <t>INTERVAL</t>
+  </si>
+  <si>
+    <t>LOB / LANGUAGE</t>
+  </si>
+  <si>
+    <t>REQUIRED FTE</t>
+  </si>
+  <si>
+    <t>NET / OBSERVED</t>
+  </si>
+  <si>
+    <t>GAP FTE</t>
+  </si>
+  <si>
+    <t>STATE</t>
+  </si>
+  <si>
+    <t>09 Sep 10:00</t>
+  </si>
+  <si>
+    <t>RSA BE / FR-NL</t>
+  </si>
+  <si>
+    <t>Future</t>
+  </si>
+  <si>
+    <t>FUTURE GAP</t>
+  </si>
+  <si>
+    <t>REALISATIONS</t>
+  </si>
+  <si>
+    <t>All mapped</t>
+  </si>
+  <si>
+    <t>GRAIN</t>
+  </si>
+  <si>
+    <t>Daily</t>
+  </si>
+  <si>
+    <t>DATA STATE</t>
+  </si>
+  <si>
+    <t>Reviewed</t>
+  </si>
+  <si>
+    <t>ACTUAL VOLUME</t>
+  </si>
+  <si>
+    <t>FORECAST ATTAINMENT</t>
+  </si>
+  <si>
+    <t>ROUTED RATE</t>
+  </si>
+  <si>
+    <t>WEIGHTED AHT</t>
+  </si>
+  <si>
+    <t>Service level</t>
+  </si>
+  <si>
+    <t>LOB REALISATION SUMMARY</t>
+  </si>
+  <si>
+    <t>ACTUAL</t>
+  </si>
+  <si>
+    <t>FORECAST</t>
+  </si>
+  <si>
+    <t>ATTAINMENT</t>
+  </si>
+  <si>
+    <t>SERVICE LEVEL</t>
+  </si>
+  <si>
+    <t>ABSENCE %</t>
+  </si>
+  <si>
+    <t>READY</t>
+  </si>
+  <si>
+    <t>ABSENTEEISM &amp; SHRINKAGE</t>
+  </si>
+  <si>
+    <t>ABSENCE RATE</t>
+  </si>
+  <si>
+    <t>SHRINKAGE RATE</t>
+  </si>
+  <si>
+    <t>FINALIZED COVERAGE</t>
+  </si>
+  <si>
+    <t>REVIEW CASES</t>
+  </si>
+  <si>
+    <t>Absence</t>
+  </si>
+  <si>
+    <t>Shrinkage</t>
+  </si>
+  <si>
+    <t>PRIORITIZED ABSENCE REVIEW CASES</t>
+  </si>
+  <si>
+    <t>RESULT STATUS</t>
+  </si>
+  <si>
+    <t>ABSENCE H</t>
+  </si>
+  <si>
+    <t>ACTION STATUS</t>
+  </si>
+  <si>
+    <t>07 Sep</t>
+  </si>
+  <si>
+    <t>Amina El Idrissi</t>
+  </si>
+  <si>
+    <t>ABSENCE RECORDED</t>
+  </si>
+  <si>
+    <t>Pending</t>
+  </si>
+  <si>
+    <t>BONUS MANAGEMENT</t>
+  </si>
+  <si>
+    <t>2026-08</t>
+  </si>
+  <si>
+    <t>POPULATION</t>
+  </si>
+  <si>
+    <t>TEAM LEAD</t>
+  </si>
+  <si>
+    <t>TOTAL PAYOUT</t>
+  </si>
+  <si>
+    <t>PAID AGENTS</t>
+  </si>
+  <si>
+    <t>AVG PAID PAYOUT</t>
+  </si>
+  <si>
+    <t>REVIEW ITEMS</t>
+  </si>
+  <si>
+    <t>RSA</t>
+  </si>
+  <si>
+    <t>FORD</t>
+  </si>
+  <si>
+    <t>Total payout</t>
+  </si>
+  <si>
+    <t>AHT</t>
+  </si>
+  <si>
+    <t>Productivity</t>
+  </si>
+  <si>
+    <t>PCS</t>
+  </si>
+  <si>
+    <t>QM</t>
+  </si>
+  <si>
+    <t>Abs%</t>
+  </si>
+  <si>
+    <t>Attainment</t>
+  </si>
+  <si>
+    <t>POPULATION PAYOUT SUMMARY</t>
+  </si>
+  <si>
+    <t>PAYOUT RATE</t>
+  </si>
+  <si>
+    <t>AVG ACHIEVEMENT</t>
+  </si>
+  <si>
+    <t>REVIEW</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="0.00"/>
     <numFmt numFmtId="165" formatCode="0%"/>
     <numFmt numFmtId="166" formatCode="#,##0"/>
     <numFmt numFmtId="167" formatCode="+0.00;-0.00;0.00"/>
+    <numFmt numFmtId="168" formatCode="#,##0.00"/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -453,6 +823,13 @@
     </font>
     <font>
       <b/>
+      <sz val="10"/>
+      <color rgb="FF0B1F33"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
       <sz val="9"/>
       <color rgb="FF0B1F33"/>
       <name val="Aptos"/>
@@ -460,13 +837,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF0B1F33"/>
-      <name val="Aptos"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
       <color rgb="FF0B1F33"/>
       <name val="Aptos"/>
       <family val="2"/>
@@ -514,42 +884,22 @@
     </font>
     <font>
       <b/>
-      <sz val="8"/>
-      <color rgb="FF536474"/>
-      <name val="Aptos"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF1F2933"/>
-      <name val="Aptos"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FF536474"/>
-      <name val="Aptos"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="20"/>
+      <sz val="24"/>
       <color rgb="FF0B1F33"/>
       <name val="Aptos Display"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="8"/>
-      <color rgb="FF536474"/>
-      <name val="Aptos"/>
+      <b/>
+      <sz val="30"/>
+      <color rgb="FF007C83"/>
+      <name val="Aptos Display"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color rgb="FF0563C1"/>
-      <name val="Aptos"/>
+      <sz val="8"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -586,6 +936,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFF1CC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -611,12 +967,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFDDF3E8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3F0FA"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -701,7 +1051,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -725,72 +1075,68 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="13" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="14" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="166" fontId="16" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="16" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="16" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="16" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="17" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="17" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="18" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="18" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="13" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="20" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="16" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -841,7 +1187,7 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:v>Current period</c:v>
+            <c:v>Current</c:v>
           </c:tx>
           <c:spPr>
             <a:solidFill>
@@ -852,7 +1198,7 @@
             </a:ln>
           </c:spPr>
           <c:dLbls>
-            <c:numFmt formatCode="0.00" sourceLinked="0"/>
+            <c:numFmt formatCode="0.0" sourceLinked="0"/>
             <c:showVal val="1"/>
           </c:dLbls>
           <c:cat>
@@ -901,7 +1247,7 @@
           <c:idx val="1"/>
           <c:order val="1"/>
           <c:tx>
-            <c:v>Prior comparable</c:v>
+            <c:v>Prior</c:v>
           </c:tx>
           <c:spPr>
             <a:solidFill>
@@ -912,7 +1258,7 @@
             </a:ln>
           </c:spPr>
           <c:dLbls>
-            <c:numFmt formatCode="0.00" sourceLinked="0"/>
+            <c:numFmt formatCode="0.0" sourceLinked="0"/>
             <c:showVal val="1"/>
           </c:dLbls>
           <c:cat>
@@ -992,17 +1338,22 @@
         <c:axId val="50010002"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="5"/>
-          <c:min val="1"/>
         </c:scaling>
         <c:axPos val="t"/>
-        <c:majorGridlines/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr val="D8E0E6"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50010001"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
-        <c:majorUnit val="1"/>
       </c:valAx>
       <c:spPr>
         <a:solidFill>
@@ -1032,7 +1383,1204 @@
         </a:p>
       </c:txPr>
     </c:legend>
-    <c:plotVisOnly val="1"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="FFFFFF"/>
+    </a:solidFill>
+    <a:ln w="12700">
+      <a:solidFill>
+        <a:srgbClr val="D8E0E6"/>
+      </a:solidFill>
+    </a:ln>
+  </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="1" baseline="0">
+                <a:solidFill>
+                  <a:srgbClr val="0B1F33"/>
+                </a:solidFill>
+                <a:latin typeface="Aptos Display"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="1" baseline="0">
+                <a:solidFill>
+                  <a:srgbClr val="0B1F33"/>
+                </a:solidFill>
+                <a:latin typeface="Aptos Display"/>
+              </a:rPr>
+              <a:t>SERVICE LEVEL VS TARGET</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+    </c:title>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Service level</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="007C83"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0%" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>REALISATIONS!$AJ$2:$AJ$5</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>RSA NL</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>RSA BE</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>FORD NL</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>OEM</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>REALISATIONS!$AK$2:$AK$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.899</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.858</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.973</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.949</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Target</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="536474"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0%" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>REALISATIONS!$AJ$2:$AJ$5</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>RSA NL</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>RSA BE</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>FORD NL</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>OEM</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>REALISATIONS!$AL$2:$AL$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.8</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:axId val="50100001"/>
+        <c:axId val="50100002"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="50100001"/>
+        <c:scaling>
+          <c:orientation val="maxMin"/>
+        </c:scaling>
+        <c:axPos val="l"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" baseline="0">
+                <a:solidFill>
+                  <a:srgbClr val="0B1F33"/>
+                </a:solidFill>
+                <a:latin typeface="Aptos"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="50100002"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="50100002"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="1"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:axPos val="t"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr val="D8E0E6"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0%" sourceLinked="0"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="50100001"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="536474"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="FFFFFF"/>
+    </a:solidFill>
+    <a:ln w="12700">
+      <a:solidFill>
+        <a:srgbClr val="D8E0E6"/>
+      </a:solidFill>
+    </a:ln>
+  </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="1" baseline="0">
+                <a:solidFill>
+                  <a:srgbClr val="0B1F33"/>
+                </a:solidFill>
+                <a:latin typeface="Aptos Display"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="1" baseline="0">
+                <a:solidFill>
+                  <a:srgbClr val="0B1F33"/>
+                </a:solidFill>
+                <a:latin typeface="Aptos Display"/>
+              </a:rPr>
+              <a:t>ABSENCE &amp; SHRINKAGE BY LOB</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+    </c:title>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Absence</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="B42318"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0%" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>ABSENCE!$AD$2:$AD$5</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>RSA NL</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>RSA BE</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>FORD NL</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>OEM</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>ABSENCE!$AE$2:$AE$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.041</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.052</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.033</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.046</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Shrinkage</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="007C83"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0%" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>ABSENCE!$AD$2:$AD$5</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>RSA NL</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>RSA BE</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>FORD NL</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>OEM</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>ABSENCE!$AF$2:$AF$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.118</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.129</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.104</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.123</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:axId val="50110001"/>
+        <c:axId val="50110002"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="50110001"/>
+        <c:scaling>
+          <c:orientation val="maxMin"/>
+        </c:scaling>
+        <c:axPos val="l"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" baseline="0">
+                <a:solidFill>
+                  <a:srgbClr val="0B1F33"/>
+                </a:solidFill>
+                <a:latin typeface="Aptos"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="50110002"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="50110002"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:axPos val="t"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr val="D8E0E6"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0%" sourceLinked="0"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="50110001"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="536474"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="FFFFFF"/>
+    </a:solidFill>
+    <a:ln w="12700">
+      <a:solidFill>
+        <a:srgbClr val="D8E0E6"/>
+      </a:solidFill>
+    </a:ln>
+  </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="1" baseline="0">
+                <a:solidFill>
+                  <a:srgbClr val="0B1F33"/>
+                </a:solidFill>
+                <a:latin typeface="Aptos Display"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="1" baseline="0">
+                <a:solidFill>
+                  <a:srgbClr val="0B1F33"/>
+                </a:solidFill>
+                <a:latin typeface="Aptos Display"/>
+              </a:rPr>
+              <a:t>DAILY ABSENCE &amp; SHRINKAGE HOURS</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+    </c:title>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Absence</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="B42318"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="4"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="B42318"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:srgbClr val="B42318"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>ABSENCE!$AJ$2:$AJ$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>01</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>02</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>03</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>04</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>05</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>ABSENCE!$AK$2:$AK$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>42</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>35</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Shrinkage</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="007C83"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="4"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="007C83"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:srgbClr val="007C83"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>ABSENCE!$AJ$2:$AJ$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>01</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>02</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>03</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>04</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>05</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>ABSENCE!$AL$2:$AL$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>72</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>68</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>81</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>77</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>74</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:marker val="1"/>
+        <c:axId val="50120001"/>
+        <c:axId val="50120002"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="50120001"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:tickLblPos val="low"/>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="800" baseline="0">
+                <a:solidFill>
+                  <a:srgbClr val="536474"/>
+                </a:solidFill>
+                <a:latin typeface="Aptos"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="50120002"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="50120002"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr val="D8E0E6"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="50120001"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="536474"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="FFFFFF"/>
+    </a:solidFill>
+    <a:ln w="12700">
+      <a:solidFill>
+        <a:srgbClr val="D8E0E6"/>
+      </a:solidFill>
+    </a:ln>
+  </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart13.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="1" baseline="0">
+                <a:solidFill>
+                  <a:srgbClr val="0B1F33"/>
+                </a:solidFill>
+                <a:latin typeface="Aptos Display"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="1" baseline="0">
+                <a:solidFill>
+                  <a:srgbClr val="0B1F33"/>
+                </a:solidFill>
+                <a:latin typeface="Aptos Display"/>
+              </a:rPr>
+              <a:t>PAYOUT BY POPULATION</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+    </c:title>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Total payout</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="D6A84B"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0.0" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>BONUS!$AD$2:$AD$4</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>RSA</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>FORD</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>OEM</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>BONUS!$AE$2:$AE$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>92100</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>54120</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>38300</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:axId val="50130001"/>
+        <c:axId val="50130002"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="50130001"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="b"/>
+        <c:tickLblPos val="low"/>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="800" baseline="0">
+                <a:solidFill>
+                  <a:srgbClr val="536474"/>
+                </a:solidFill>
+                <a:latin typeface="Aptos"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="50130002"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="50130002"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr val="D8E0E6"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="50130001"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="536474"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="FFFFFF"/>
+    </a:solidFill>
+    <a:ln w="12700">
+      <a:solidFill>
+        <a:srgbClr val="D8E0E6"/>
+      </a:solidFill>
+    </a:ln>
+  </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart14.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="1" baseline="0">
+                <a:solidFill>
+                  <a:srgbClr val="0B1F33"/>
+                </a:solidFill>
+                <a:latin typeface="Aptos Display"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="1" baseline="0">
+                <a:solidFill>
+                  <a:srgbClr val="0B1F33"/>
+                </a:solidFill>
+                <a:latin typeface="Aptos Display"/>
+              </a:rPr>
+              <a:t>KPI ATTAINMENT</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+    </c:title>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Attainment</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="007C83"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0%" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>BONUS!$AJ$2:$AJ$6</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>AHT</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Productivity</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>PCS</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>QM</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Abs%</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>BONUS!$AK$2:$AK$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.82</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.76</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.6899999999999999</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.88</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.73</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:axId val="50140001"/>
+        <c:axId val="50140002"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="50140001"/>
+        <c:scaling>
+          <c:orientation val="maxMin"/>
+        </c:scaling>
+        <c:axPos val="l"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" baseline="0">
+                <a:solidFill>
+                  <a:srgbClr val="0B1F33"/>
+                </a:solidFill>
+                <a:latin typeface="Aptos"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="50140002"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="50140002"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="1"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:axPos val="t"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr val="D8E0E6"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0%" sourceLinked="0"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="50140001"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="536474"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1092,7 +2640,7 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:v>Current period</c:v>
+            <c:v>Current</c:v>
           </c:tx>
           <c:spPr>
             <a:ln w="28575">
@@ -1102,70 +2650,63 @@
             </a:ln>
           </c:spPr>
           <c:marker>
-            <c:symbol val="none"/>
+            <c:symbol val="circle"/>
+            <c:size val="4"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="007C83"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:srgbClr val="007C83"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>PCS!$AH$2:$AH$9</c:f>
+              <c:f>PCS!$AJ$2:$AJ$6</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>01</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2</c:v>
+                  <c:v>02</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3</c:v>
+                  <c:v>03</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4</c:v>
+                  <c:v>04</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>8</c:v>
+                  <c:v>05</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>PCS!$AI$2:$AI$9</c:f>
+              <c:f>PCS!$AK$2:$AK$6</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>4.25</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4.29</c:v>
+                  <c:v>4.32</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4.33</c:v>
+                  <c:v>4.39</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4.37</c:v>
+                  <c:v>4.48</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4.41</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>4.45</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>4.49</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>4.53</c:v>
+                  <c:v>4.54</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1175,7 +2716,7 @@
           <c:idx val="1"/>
           <c:order val="1"/>
           <c:tx>
-            <c:v>Prior comparable</c:v>
+            <c:v>Prior</c:v>
           </c:tx>
           <c:spPr>
             <a:ln w="28575">
@@ -1185,70 +2726,63 @@
             </a:ln>
           </c:spPr>
           <c:marker>
-            <c:symbol val="none"/>
+            <c:symbol val="circle"/>
+            <c:size val="4"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="536474"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:srgbClr val="536474"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>PCS!$AH$2:$AH$9</c:f>
+              <c:f>PCS!$AJ$2:$AJ$6</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>01</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2</c:v>
+                  <c:v>02</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3</c:v>
+                  <c:v>03</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4</c:v>
+                  <c:v>04</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>8</c:v>
+                  <c:v>05</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>PCS!$AJ$2:$AJ$9</c:f>
+              <c:f>PCS!$AL$2:$AL$6</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>4.18</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4.215</c:v>
+                  <c:v>4.27</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4.25</c:v>
+                  <c:v>4.31</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4.285</c:v>
+                  <c:v>4.38</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4.319999999999999</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>4.355</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>4.39</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>4.425</c:v>
+                  <c:v>4.42</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1264,17 +2798,8 @@
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:srgbClr val="D8E0E6"/>
-              </a:solidFill>
-            </a:ln>
-          </c:spPr>
-        </c:majorGridlines>
         <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:tickLblPos val="nextTo"/>
+        <c:tickLblPos val="low"/>
         <c:txPr>
           <a:bodyPr/>
           <a:lstStyle/>
@@ -1300,17 +2825,22 @@
         <c:axId val="50020002"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="5"/>
-          <c:min val="2"/>
         </c:scaling>
         <c:axPos val="l"/>
-        <c:majorGridlines/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr val="D8E0E6"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50020001"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
-        <c:majorUnit val="0.5"/>
       </c:valAx>
       <c:spPr>
         <a:solidFill>
@@ -1340,7 +2870,1635 @@
         </a:p>
       </c:txPr>
     </c:legend>
-    <c:plotVisOnly val="1"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="FFFFFF"/>
+    </a:solidFill>
+    <a:ln w="12700">
+      <a:solidFill>
+        <a:srgbClr val="D8E0E6"/>
+      </a:solidFill>
+    </a:ln>
+  </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="1" baseline="0">
+                <a:solidFill>
+                  <a:srgbClr val="0B1F33"/>
+                </a:solidFill>
+                <a:latin typeface="Aptos Display"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="1" baseline="0">
+                <a:solidFill>
+                  <a:srgbClr val="0B1F33"/>
+                </a:solidFill>
+                <a:latin typeface="Aptos Display"/>
+              </a:rPr>
+              <a:t>SERVICE LEVEL BY LOB</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+    </c:title>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>TSL</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="007C83"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0%" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>RTM!$AD$2:$AD$5</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>RSA NL</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>RSA BE</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>FORD NL</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>OEM</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>RTM!$AE$2:$AE$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.899</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.858</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.973</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.949</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Target</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="536474"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0%" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>RTM!$AD$2:$AD$5</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>RSA NL</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>RSA BE</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>FORD NL</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>OEM</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>RTM!$AF$2:$AF$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.8</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:axId val="50030001"/>
+        <c:axId val="50030002"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="50030001"/>
+        <c:scaling>
+          <c:orientation val="maxMin"/>
+        </c:scaling>
+        <c:axPos val="l"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" baseline="0">
+                <a:solidFill>
+                  <a:srgbClr val="0B1F33"/>
+                </a:solidFill>
+                <a:latin typeface="Aptos"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="50030002"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="50030002"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="1"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:axPos val="t"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr val="D8E0E6"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0%" sourceLinked="0"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="50030001"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="536474"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="FFFFFF"/>
+    </a:solidFill>
+    <a:ln w="12700">
+      <a:solidFill>
+        <a:srgbClr val="D8E0E6"/>
+      </a:solidFill>
+    </a:ln>
+  </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="1" baseline="0">
+                <a:solidFill>
+                  <a:srgbClr val="0B1F33"/>
+                </a:solidFill>
+                <a:latin typeface="Aptos Display"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="1" baseline="0">
+                <a:solidFill>
+                  <a:srgbClr val="0B1F33"/>
+                </a:solidFill>
+                <a:latin typeface="Aptos Display"/>
+              </a:rPr>
+              <a:t>ACTUAL VS FORECAST</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+    </c:title>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Actual</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="007C83"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0.0" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>RTM!$AJ$2:$AJ$5</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>RSA NL</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>RSA BE</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>FORD NL</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>OEM</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>RTM!$AK$2:$AK$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>840</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>530</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>320</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>410</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Forecast</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="536474"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0.0" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>RTM!$AJ$2:$AJ$5</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>RSA NL</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>RSA BE</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>FORD NL</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>OEM</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>RTM!$AL$2:$AL$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>810</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>552</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>300</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>354</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:axId val="50040001"/>
+        <c:axId val="50040002"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="50040001"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="b"/>
+        <c:tickLblPos val="low"/>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="800" baseline="0">
+                <a:solidFill>
+                  <a:srgbClr val="536474"/>
+                </a:solidFill>
+                <a:latin typeface="Aptos"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="50040002"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="50040002"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr val="D8E0E6"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="50040001"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="536474"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="FFFFFF"/>
+    </a:solidFill>
+    <a:ln w="12700">
+      <a:solidFill>
+        <a:srgbClr val="D8E0E6"/>
+      </a:solidFill>
+    </a:ln>
+  </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="1" baseline="0">
+                <a:solidFill>
+                  <a:srgbClr val="0B1F33"/>
+                </a:solidFill>
+                <a:latin typeface="Aptos Display"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="1" baseline="0">
+                <a:solidFill>
+                  <a:srgbClr val="0B1F33"/>
+                </a:solidFill>
+                <a:latin typeface="Aptos Display"/>
+              </a:rPr>
+              <a:t>GAP HOURS BY LOB</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+    </c:title>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Gap hours</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="007C83"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0.0" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>ATTENDANCE!$AD$2:$AD$5</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>RSA NL</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>RSA BE</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>FORD NL</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>OEM</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>ATTENDANCE!$AE$2:$AE$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>2.8</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.6</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.9</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:axId val="50050001"/>
+        <c:axId val="50050002"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="50050001"/>
+        <c:scaling>
+          <c:orientation val="maxMin"/>
+        </c:scaling>
+        <c:axPos val="l"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" baseline="0">
+                <a:solidFill>
+                  <a:srgbClr val="0B1F33"/>
+                </a:solidFill>
+                <a:latin typeface="Aptos"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="50050002"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="50050002"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="t"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr val="D8E0E6"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="50050001"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="536474"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="FFFFFF"/>
+    </a:solidFill>
+    <a:ln w="12700">
+      <a:solidFill>
+        <a:srgbClr val="D8E0E6"/>
+      </a:solidFill>
+    </a:ln>
+  </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="1" baseline="0">
+                <a:solidFill>
+                  <a:srgbClr val="0B1F33"/>
+                </a:solidFill>
+                <a:latin typeface="Aptos Display"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="1" baseline="0">
+                <a:solidFill>
+                  <a:srgbClr val="0B1F33"/>
+                </a:solidFill>
+                <a:latin typeface="Aptos Display"/>
+              </a:rPr>
+              <a:t>DECISION STATUS</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+    </c:title>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Cases</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="007C83"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0.0" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>ATTENDANCE!$AJ$2:$AJ$5</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Open</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Approved</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Dismissed</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Missing</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>ATTENDANCE!$AK$2:$AK$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:axId val="50060001"/>
+        <c:axId val="50060002"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="50060001"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="b"/>
+        <c:tickLblPos val="low"/>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="800" baseline="0">
+                <a:solidFill>
+                  <a:srgbClr val="536474"/>
+                </a:solidFill>
+                <a:latin typeface="Aptos"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="50060002"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="50060002"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr val="D8E0E6"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="50060001"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="536474"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="FFFFFF"/>
+    </a:solidFill>
+    <a:ln w="12700">
+      <a:solidFill>
+        <a:srgbClr val="D8E0E6"/>
+      </a:solidFill>
+    </a:ln>
+  </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="1" baseline="0">
+                <a:solidFill>
+                  <a:srgbClr val="0B1F33"/>
+                </a:solidFill>
+                <a:latin typeface="Aptos Display"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="1" baseline="0">
+                <a:solidFill>
+                  <a:srgbClr val="0B1F33"/>
+                </a:solidFill>
+                <a:latin typeface="Aptos Display"/>
+              </a:rPr>
+              <a:t>REQUIRED VS NET SCHEDULED HOURS</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+    </c:title>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Required</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="007C83"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0.0" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>STAFFING!$AD$2:$AD$5</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>RSA NL</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>RSA BE</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>FORD NL</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>OEM</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>STAFFING!$AE$2:$AE$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>420</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>310</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>245</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>280</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Net scheduled</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="536474"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0.0" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>STAFFING!$AD$2:$AD$5</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>RSA NL</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>RSA BE</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>FORD NL</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>OEM</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>STAFFING!$AF$2:$AF$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>401</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>298</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>251</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>260</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:axId val="50070001"/>
+        <c:axId val="50070002"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="50070001"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="b"/>
+        <c:tickLblPos val="low"/>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="800" baseline="0">
+                <a:solidFill>
+                  <a:srgbClr val="536474"/>
+                </a:solidFill>
+                <a:latin typeface="Aptos"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="50070002"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="50070002"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr val="D8E0E6"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="50070001"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="536474"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="FFFFFF"/>
+    </a:solidFill>
+    <a:ln w="12700">
+      <a:solidFill>
+        <a:srgbClr val="D8E0E6"/>
+      </a:solidFill>
+    </a:ln>
+  </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="1" baseline="0">
+                <a:solidFill>
+                  <a:srgbClr val="0B1F33"/>
+                </a:solidFill>
+                <a:latin typeface="Aptos Display"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="1" baseline="0">
+                <a:solidFill>
+                  <a:srgbClr val="0B1F33"/>
+                </a:solidFill>
+                <a:latin typeface="Aptos Display"/>
+              </a:rPr>
+              <a:t>PEAK GAP BY DAY</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+    </c:title>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Gap FTE</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575">
+              <a:solidFill>
+                <a:srgbClr val="B42318"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="4"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="B42318"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:srgbClr val="B42318"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>STAFFING!$AJ$2:$AJ$6</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Mon</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Tue</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Wed</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Thu</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Fri</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>STAFFING!$AK$2:$AK$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>2.1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.8</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3.9</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:marker val="1"/>
+        <c:axId val="50080001"/>
+        <c:axId val="50080002"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="50080001"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="b"/>
+        <c:tickLblPos val="low"/>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="800" baseline="0">
+                <a:solidFill>
+                  <a:srgbClr val="536474"/>
+                </a:solidFill>
+                <a:latin typeface="Aptos"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="50080002"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="50080002"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr val="D8E0E6"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="50080001"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="536474"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="FFFFFF"/>
+    </a:solidFill>
+    <a:ln w="12700">
+      <a:solidFill>
+        <a:srgbClr val="D8E0E6"/>
+      </a:solidFill>
+    </a:ln>
+  </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="1" baseline="0">
+                <a:solidFill>
+                  <a:srgbClr val="0B1F33"/>
+                </a:solidFill>
+                <a:latin typeface="Aptos Display"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="1" baseline="0">
+                <a:solidFill>
+                  <a:srgbClr val="0B1F33"/>
+                </a:solidFill>
+                <a:latin typeface="Aptos Display"/>
+              </a:rPr>
+              <a:t>ACTUAL VS FORECAST BY LOB</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+    </c:title>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Actual</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="007C83"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0.0" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>REALISATIONS!$AD$2:$AD$5</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>RSA NL</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>RSA BE</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>FORD NL</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>OEM</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>REALISATIONS!$AE$2:$AE$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>18400</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>12150</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8830</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>10240</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Forecast</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="536474"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:dLbls>
+            <c:numFmt formatCode="0.0" sourceLinked="0"/>
+            <c:showVal val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>REALISATIONS!$AD$2:$AD$5</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>RSA NL</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>RSA BE</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>FORD NL</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>OEM</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>REALISATIONS!$AF$2:$AF$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>17950</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>12600</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8460</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9980</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:axId val="50090001"/>
+        <c:axId val="50090002"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="50090001"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="b"/>
+        <c:tickLblPos val="low"/>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="800" baseline="0">
+                <a:solidFill>
+                  <a:srgbClr val="536474"/>
+                </a:solidFill>
+                <a:latin typeface="Aptos"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="50090002"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="50090002"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr val="D8E0E6"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="50090001"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="536474"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1361,6 +4519,396 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
@@ -1974,14 +5522,14 @@
     <tabColor rgb="FFD6A84B"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AJ32"/>
+  <dimension ref="A1:AL32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="28" width="7.42578125" style="8" customWidth="1"/>
-    <col min="30" max="36" width="0" hidden="1" customWidth="1"/>
+    <col min="30" max="38" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="42" customHeight="1">
+    <row r="1" spans="1:38" ht="42" customHeight="1">
       <c r="A1" s="9" t="s">
         <v>28</v>
       </c>
@@ -2016,8 +5564,26 @@
       <c r="Z1" s="11"/>
       <c r="AA1" s="11"/>
       <c r="AB1" s="11"/>
-    </row>
-    <row r="2" spans="1:36" ht="39" customHeight="1">
+      <c r="AD1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:38" ht="39" customHeight="1">
       <c r="A2" s="12" t="s">
         <v>31</v>
       </c>
@@ -2063,7 +5629,7 @@
       <c r="AA2" s="13"/>
       <c r="AB2" s="13"/>
       <c r="AD2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AE2">
         <v>4.62</v>
@@ -2071,19 +5637,19 @@
       <c r="AF2">
         <v>4.51</v>
       </c>
-      <c r="AH2">
-        <v>1</v>
-      </c>
-      <c r="AI2">
+      <c r="AJ2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AK2">
         <v>4.25</v>
       </c>
-      <c r="AJ2">
+      <c r="AL2">
         <v>4.18</v>
       </c>
     </row>
-    <row r="3" spans="1:36" s="8" customFormat="1" ht="7.5" customHeight="1">
+    <row r="3" spans="1:38" s="8" customFormat="1" ht="7.5" customHeight="1">
       <c r="AD3" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AE3" s="8">
         <v>4.38</v>
@@ -2091,17 +5657,17 @@
       <c r="AF3" s="8">
         <v>4.31</v>
       </c>
-      <c r="AH3" s="8">
-        <v>2</v>
-      </c>
-      <c r="AI3" s="8">
-        <v>4.29</v>
-      </c>
-      <c r="AJ3" s="8">
-        <v>4.215</v>
-      </c>
-    </row>
-    <row r="4" spans="1:36" ht="5.25" customHeight="1">
+      <c r="AJ3" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="AK3" s="8">
+        <v>4.32</v>
+      </c>
+      <c r="AL3" s="8">
+        <v>4.27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:38" ht="5.25" customHeight="1">
       <c r="A4" s="14"/>
       <c r="B4" s="14"/>
       <c r="C4" s="14"/>
@@ -2131,7 +5697,7 @@
       <c r="AA4" s="15"/>
       <c r="AB4" s="15"/>
       <c r="AD4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AE4">
         <v>4.71</v>
@@ -2139,17 +5705,17 @@
       <c r="AF4">
         <v>4.66</v>
       </c>
-      <c r="AH4">
-        <v>3</v>
-      </c>
-      <c r="AI4">
-        <v>4.33</v>
-      </c>
-      <c r="AJ4">
-        <v>4.25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:36" ht="27" customHeight="1">
+      <c r="AJ4" t="s">
+        <v>50</v>
+      </c>
+      <c r="AK4">
+        <v>4.39</v>
+      </c>
+      <c r="AL4">
+        <v>4.31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:38" ht="27" customHeight="1">
       <c r="A5" s="16" t="s">
         <v>37</v>
       </c>
@@ -2187,7 +5753,7 @@
       <c r="AA5" s="16"/>
       <c r="AB5" s="16"/>
       <c r="AD5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AE5">
         <v>4.55</v>
@@ -2195,17 +5761,17 @@
       <c r="AF5">
         <v>4.48</v>
       </c>
-      <c r="AH5">
-        <v>4</v>
-      </c>
-      <c r="AI5">
-        <v>4.37</v>
-      </c>
-      <c r="AJ5">
-        <v>4.285</v>
-      </c>
-    </row>
-    <row r="6" spans="1:36" ht="72" customHeight="1">
+      <c r="AJ5" t="s">
+        <v>51</v>
+      </c>
+      <c r="AK5">
+        <v>4.48</v>
+      </c>
+      <c r="AL5">
+        <v>4.38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:38" ht="72" customHeight="1">
       <c r="A6" s="17">
         <v>4.54</v>
       </c>
@@ -2242,56 +5808,26 @@
       <c r="Z6" s="17"/>
       <c r="AA6" s="17"/>
       <c r="AB6" s="17"/>
-      <c r="AH6">
-        <v>5</v>
-      </c>
-      <c r="AI6">
-        <v>4.41</v>
-      </c>
-      <c r="AJ6">
-        <v>4.319999999999999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:36" s="8" customFormat="1" ht="7.5" customHeight="1">
-      <c r="AH7" s="8">
-        <v>6</v>
-      </c>
-      <c r="AI7" s="8">
-        <v>4.45</v>
-      </c>
-      <c r="AJ7" s="8">
-        <v>4.355</v>
-      </c>
-    </row>
-    <row r="8" spans="1:36" s="8" customFormat="1" ht="16.5" customHeight="1">
-      <c r="AH8" s="8">
-        <v>7</v>
-      </c>
-      <c r="AI8" s="8">
-        <v>4.49</v>
-      </c>
-      <c r="AJ8" s="8">
-        <v>4.39</v>
-      </c>
-    </row>
-    <row r="9" spans="1:36" s="8" customFormat="1" ht="16.5" customHeight="1">
-      <c r="AH9" s="8">
-        <v>8</v>
-      </c>
-      <c r="AI9" s="8">
-        <v>4.53</v>
-      </c>
-      <c r="AJ9" s="8">
-        <v>4.425</v>
-      </c>
-    </row>
-    <row r="10" spans="1:36" s="8" customFormat="1" ht="16.5" customHeight="1"/>
-    <row r="11" spans="1:36" s="8" customFormat="1" ht="16.5" customHeight="1"/>
-    <row r="12" spans="1:36" s="8" customFormat="1" ht="16.5" customHeight="1"/>
-    <row r="13" spans="1:36" s="8" customFormat="1" ht="16.5" customHeight="1"/>
-    <row r="14" spans="1:36" s="8" customFormat="1" ht="16.5" customHeight="1"/>
-    <row r="15" spans="1:36" s="8" customFormat="1" ht="16.5" customHeight="1"/>
-    <row r="16" spans="1:36" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+      <c r="AJ6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK6">
+        <v>4.54</v>
+      </c>
+      <c r="AL6">
+        <v>4.42</v>
+      </c>
+    </row>
+    <row r="7" spans="1:38" s="8" customFormat="1" ht="7.5" customHeight="1"/>
+    <row r="8" spans="1:38" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="9" spans="1:38" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="10" spans="1:38" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="11" spans="1:38" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="12" spans="1:38" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="13" spans="1:38" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="14" spans="1:38" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="15" spans="1:38" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="16" spans="1:38" s="8" customFormat="1" ht="16.5" customHeight="1"/>
     <row r="17" spans="1:28" s="8" customFormat="1" ht="16.5" customHeight="1"/>
     <row r="18" spans="1:28" s="8" customFormat="1" ht="16.5" customHeight="1"/>
     <row r="19" spans="1:28" s="8" customFormat="1" ht="16.5" customHeight="1"/>
@@ -2300,7 +5836,7 @@
     <row r="22" spans="1:28" s="8" customFormat="1" ht="7.5" customHeight="1"/>
     <row r="23" spans="1:28" ht="25.5" customHeight="1">
       <c r="A23" s="19" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="B23" s="19"/>
       <c r="C23" s="19"/>
@@ -2325,7 +5861,7 @@
       <c r="C24" s="20"/>
       <c r="D24" s="20"/>
       <c r="E24" s="20" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="F24" s="20"/>
       <c r="G24" s="20"/>
@@ -2355,7 +5891,7 @@
       <c r="W24" s="20"/>
       <c r="X24" s="20"/>
       <c r="Y24" s="20" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="Z24" s="20"/>
       <c r="AA24" s="20"/>
@@ -2363,7 +5899,7 @@
     </row>
     <row r="25" spans="1:28" ht="19.5" customHeight="1">
       <c r="A25" s="21" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="B25" s="21"/>
       <c r="C25" s="21"/>
@@ -2407,7 +5943,7 @@
     </row>
     <row r="26" spans="1:28" ht="19.5" customHeight="1">
       <c r="A26" s="21" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="B26" s="21"/>
       <c r="C26" s="21"/>
@@ -2450,89 +5986,61 @@
       <c r="AB26" s="26"/>
     </row>
     <row r="27" spans="1:28" ht="19.5" customHeight="1">
-      <c r="A27" s="21" t="s">
-        <v>50</v>
-      </c>
+      <c r="A27" s="21"/>
       <c r="B27" s="21"/>
       <c r="C27" s="21"/>
       <c r="D27" s="21"/>
-      <c r="E27" s="22">
-        <v>11</v>
-      </c>
+      <c r="E27" s="22"/>
       <c r="F27" s="22"/>
       <c r="G27" s="22"/>
       <c r="H27" s="22"/>
-      <c r="I27" s="23">
-        <v>0.27</v>
-      </c>
+      <c r="I27" s="23"/>
       <c r="J27" s="23"/>
       <c r="K27" s="23"/>
       <c r="L27" s="23"/>
-      <c r="M27" s="24">
-        <v>4.38</v>
-      </c>
+      <c r="M27" s="24"/>
       <c r="N27" s="24"/>
       <c r="O27" s="24"/>
       <c r="P27" s="24"/>
-      <c r="Q27" s="24">
-        <v>4.31</v>
-      </c>
+      <c r="Q27" s="24"/>
       <c r="R27" s="24"/>
       <c r="S27" s="24"/>
       <c r="T27" s="24"/>
-      <c r="U27" s="25">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="V27" s="25"/>
-      <c r="W27" s="25"/>
-      <c r="X27" s="25"/>
-      <c r="Y27" s="26">
-        <v>1</v>
-      </c>
-      <c r="Z27" s="26"/>
-      <c r="AA27" s="26"/>
-      <c r="AB27" s="26"/>
+      <c r="U27" s="27"/>
+      <c r="V27" s="27"/>
+      <c r="W27" s="27"/>
+      <c r="X27" s="27"/>
+      <c r="Y27" s="28"/>
+      <c r="Z27" s="28"/>
+      <c r="AA27" s="28"/>
+      <c r="AB27" s="28"/>
     </row>
     <row r="28" spans="1:28" ht="19.5" customHeight="1">
-      <c r="A28" s="21" t="s">
-        <v>51</v>
-      </c>
+      <c r="A28" s="21"/>
       <c r="B28" s="21"/>
       <c r="C28" s="21"/>
       <c r="D28" s="21"/>
-      <c r="E28" s="22">
-        <v>9</v>
-      </c>
+      <c r="E28" s="22"/>
       <c r="F28" s="22"/>
       <c r="G28" s="22"/>
       <c r="H28" s="22"/>
-      <c r="I28" s="23">
-        <v>0.31</v>
-      </c>
+      <c r="I28" s="23"/>
       <c r="J28" s="23"/>
       <c r="K28" s="23"/>
       <c r="L28" s="23"/>
-      <c r="M28" s="24">
-        <v>4.71</v>
-      </c>
+      <c r="M28" s="24"/>
       <c r="N28" s="24"/>
       <c r="O28" s="24"/>
       <c r="P28" s="24"/>
-      <c r="Q28" s="24">
-        <v>4.66</v>
-      </c>
+      <c r="Q28" s="24"/>
       <c r="R28" s="24"/>
       <c r="S28" s="24"/>
       <c r="T28" s="24"/>
-      <c r="U28" s="25">
-        <v>0.05</v>
-      </c>
-      <c r="V28" s="25"/>
-      <c r="W28" s="25"/>
-      <c r="X28" s="25"/>
-      <c r="Y28" s="28">
-        <v>0</v>
-      </c>
+      <c r="U28" s="27"/>
+      <c r="V28" s="27"/>
+      <c r="W28" s="27"/>
+      <c r="X28" s="27"/>
+      <c r="Y28" s="28"/>
       <c r="Z28" s="28"/>
       <c r="AA28" s="28"/>
       <c r="AB28" s="28"/>
@@ -2753,6 +6261,7 @@
     <oddFooter>&amp;LPrepared by Anass ASSRI | WFM&amp;CDesign reference&amp;RConfidential</oddFooter>
   </headerFooter>
   <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -2760,357 +6269,739 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <tabColor rgb="FFD6A84B"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N25"/>
+  <dimension ref="A1:AL32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="14" width="12.7109375" customWidth="1"/>
+    <col min="1" max="28" width="7.42578125" style="8" customWidth="1"/>
+    <col min="30" max="38" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="34" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="2" t="s">
+    <row r="1" spans="1:38" ht="42" customHeight="1">
+      <c r="A1" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="9"/>
+      <c r="Q1" s="9"/>
+      <c r="R1" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="S1" s="10"/>
+      <c r="T1" s="10"/>
+      <c r="U1" s="10"/>
+      <c r="V1" s="10"/>
+      <c r="W1" s="10"/>
+      <c r="X1" s="10"/>
+      <c r="Y1" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z1" s="11"/>
+      <c r="AA1" s="11"/>
+      <c r="AB1" s="11"/>
+      <c r="AD1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>71</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="2" spans="1:38" ht="39" customHeight="1">
+      <c r="A2" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="B2" s="12"/>
+      <c r="C2" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="I2" s="12"/>
+      <c r="J2" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="K2" s="13"/>
+      <c r="L2" s="13"/>
+      <c r="M2" s="13"/>
+      <c r="N2" s="13"/>
+      <c r="O2" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="P2" s="12"/>
+      <c r="Q2" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="R2" s="13"/>
+      <c r="S2" s="13"/>
+      <c r="T2" s="13"/>
+      <c r="U2" s="13"/>
+      <c r="V2" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="W2" s="12"/>
+      <c r="X2" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="Y2" s="13"/>
+      <c r="Z2" s="13"/>
+      <c r="AA2" s="13"/>
+      <c r="AB2" s="13"/>
+      <c r="AD2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AE2">
+        <v>0.899</v>
+      </c>
+      <c r="AF2">
+        <v>0.8</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AK2">
+        <v>840</v>
+      </c>
+      <c r="AL2">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="3" spans="1:38" s="8" customFormat="1" ht="7.5" customHeight="1">
+      <c r="AD3" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE3" s="8">
+        <v>0.858</v>
+      </c>
+      <c r="AF3" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="AJ3" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="AK3" s="8">
+        <v>530</v>
+      </c>
+      <c r="AL3" s="8">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="4" spans="1:38" ht="5.25" customHeight="1">
+      <c r="A4" s="14"/>
+      <c r="B4" s="14"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="15"/>
+      <c r="I4" s="15"/>
+      <c r="J4" s="15"/>
+      <c r="K4" s="15"/>
+      <c r="L4" s="15"/>
+      <c r="M4" s="15"/>
+      <c r="N4" s="15"/>
+      <c r="O4" s="14"/>
+      <c r="P4" s="14"/>
+      <c r="Q4" s="14"/>
+      <c r="R4" s="14"/>
+      <c r="S4" s="14"/>
+      <c r="T4" s="14"/>
+      <c r="U4" s="14"/>
+      <c r="V4" s="15"/>
+      <c r="W4" s="15"/>
+      <c r="X4" s="15"/>
+      <c r="Y4" s="15"/>
+      <c r="Z4" s="15"/>
+      <c r="AA4" s="15"/>
+      <c r="AB4" s="15"/>
+      <c r="AD4" t="s">
+        <v>44</v>
+      </c>
+      <c r="AE4">
+        <v>0.973</v>
+      </c>
+      <c r="AF4">
+        <v>0.8</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK4">
+        <v>320</v>
+      </c>
+      <c r="AL4">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="5" spans="1:38" ht="27" customHeight="1">
+      <c r="A5" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="B5" s="16"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="I5" s="16"/>
+      <c r="J5" s="16"/>
+      <c r="K5" s="16"/>
+      <c r="L5" s="16"/>
+      <c r="M5" s="16"/>
+      <c r="N5" s="16"/>
+      <c r="O5" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="P5" s="16"/>
+      <c r="Q5" s="16"/>
+      <c r="R5" s="16"/>
+      <c r="S5" s="16"/>
+      <c r="T5" s="16"/>
+      <c r="U5" s="16"/>
+      <c r="V5" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="W5" s="16"/>
+      <c r="X5" s="16"/>
+      <c r="Y5" s="16"/>
+      <c r="Z5" s="16"/>
+      <c r="AA5" s="16"/>
+      <c r="AB5" s="16"/>
+      <c r="AD5" t="s">
+        <v>45</v>
+      </c>
+      <c r="AE5">
+        <v>0.949</v>
+      </c>
+      <c r="AF5">
+        <v>0.8</v>
+      </c>
+      <c r="AJ5" t="s">
+        <v>45</v>
+      </c>
+      <c r="AK5">
+        <v>410</v>
+      </c>
+      <c r="AL5">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="6" spans="1:38" ht="72" customHeight="1">
+      <c r="A6" s="29" t="s">
+        <v>67</v>
+      </c>
+      <c r="B6" s="29"/>
+      <c r="C6" s="29"/>
+      <c r="D6" s="29"/>
+      <c r="E6" s="29"/>
+      <c r="F6" s="29"/>
+      <c r="G6" s="29"/>
+      <c r="H6" s="30">
+        <v>84</v>
+      </c>
+      <c r="I6" s="30"/>
+      <c r="J6" s="30"/>
+      <c r="K6" s="30"/>
+      <c r="L6" s="30"/>
+      <c r="M6" s="30"/>
+      <c r="N6" s="30"/>
+      <c r="O6" s="30">
+        <v>6</v>
+      </c>
+      <c r="P6" s="30"/>
+      <c r="Q6" s="30"/>
+      <c r="R6" s="30"/>
+      <c r="S6" s="30"/>
+      <c r="T6" s="30"/>
+      <c r="U6" s="30"/>
+      <c r="V6" s="30">
+        <v>8</v>
+      </c>
+      <c r="W6" s="30"/>
+      <c r="X6" s="30"/>
+      <c r="Y6" s="30"/>
+      <c r="Z6" s="30"/>
+      <c r="AA6" s="30"/>
+      <c r="AB6" s="30"/>
+    </row>
+    <row r="7" spans="1:38" s="8" customFormat="1" ht="7.5" customHeight="1"/>
+    <row r="8" spans="1:38" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="9" spans="1:38" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="10" spans="1:38" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="11" spans="1:38" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="12" spans="1:38" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="13" spans="1:38" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="14" spans="1:38" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="15" spans="1:38" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="16" spans="1:38" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="17" spans="1:28" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="18" spans="1:28" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="19" spans="1:28" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="20" spans="1:28" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="21" spans="1:28" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="22" spans="1:28" s="8" customFormat="1" ht="7.5" customHeight="1"/>
+    <row r="23" spans="1:28" ht="25.5" customHeight="1">
+      <c r="A23" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="B23" s="19"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="19"/>
+      <c r="F23" s="19"/>
+      <c r="G23" s="19"/>
+      <c r="H23" s="19"/>
+      <c r="I23" s="19"/>
+      <c r="J23" s="19"/>
+      <c r="K23" s="19"/>
+      <c r="L23" s="19"/>
+      <c r="M23" s="19"/>
+      <c r="N23" s="19"/>
+      <c r="O23" s="19"/>
+    </row>
+    <row r="24" spans="1:28" ht="22.5" customHeight="1">
+      <c r="A24" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="B24" s="20"/>
+      <c r="C24" s="20"/>
+      <c r="D24" s="20"/>
+      <c r="E24" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="F24" s="20"/>
+      <c r="G24" s="20"/>
+      <c r="H24" s="20"/>
+      <c r="I24" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="J24" s="20"/>
+      <c r="K24" s="20"/>
+      <c r="L24" s="20"/>
+      <c r="M24" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="N24" s="20"/>
+      <c r="O24" s="20"/>
+      <c r="P24" s="20"/>
+      <c r="Q24" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="R24" s="20"/>
+      <c r="S24" s="20"/>
+      <c r="T24" s="20"/>
+      <c r="U24" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="V24" s="20"/>
+      <c r="W24" s="20"/>
+      <c r="X24" s="20"/>
+      <c r="Y24" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="Z24" s="20"/>
+      <c r="AA24" s="20"/>
+      <c r="AB24" s="20"/>
+    </row>
+    <row r="25" spans="1:28" ht="19.5" customHeight="1">
+      <c r="A25" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="B25" s="21"/>
+      <c r="C25" s="21"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="23">
+        <v>0.899</v>
+      </c>
+      <c r="F25" s="23"/>
+      <c r="G25" s="23"/>
+      <c r="H25" s="23"/>
+      <c r="I25" s="25">
+        <v>30</v>
+      </c>
+      <c r="J25" s="25"/>
+      <c r="K25" s="25"/>
+      <c r="L25" s="25"/>
+      <c r="M25" s="22">
+        <v>2</v>
+      </c>
+      <c r="N25" s="22"/>
+      <c r="O25" s="22"/>
+      <c r="P25" s="22"/>
+      <c r="Q25" s="22">
         <v>1</v>
       </c>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-    </row>
-    <row r="2" spans="1:14" ht="21" customHeight="1">
-      <c r="A2" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
-      <c r="N2" s="3"/>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" s="29" t="s">
-        <v>54</v>
-      </c>
-      <c r="B4" s="30" t="s">
-        <v>55</v>
-      </c>
-      <c r="C4" s="30"/>
-      <c r="D4" s="29" t="s">
-        <v>56</v>
-      </c>
-      <c r="E4" s="30" t="s">
-        <v>57</v>
-      </c>
-      <c r="F4" s="30"/>
-      <c r="G4" s="29" t="s">
-        <v>33</v>
-      </c>
-      <c r="H4" s="30" t="s">
-        <v>58</v>
-      </c>
-      <c r="I4" s="30"/>
-      <c r="J4" s="29" t="s">
-        <v>59</v>
-      </c>
-      <c r="K4" s="30" t="s">
-        <v>60</v>
-      </c>
-      <c r="L4" s="30"/>
-      <c r="M4" s="30"/>
-      <c r="N4" s="30"/>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="B6" s="31"/>
-      <c r="C6" s="31"/>
-      <c r="E6" s="31" t="s">
-        <v>64</v>
-      </c>
-      <c r="F6" s="31"/>
-      <c r="G6" s="31"/>
-      <c r="H6" s="31" t="s">
-        <v>67</v>
-      </c>
-      <c r="I6" s="31"/>
-      <c r="J6" s="31"/>
-      <c r="L6" s="31" t="s">
-        <v>70</v>
-      </c>
-      <c r="M6" s="31"/>
-      <c r="N6" s="31"/>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="A7" s="32" t="s">
-        <v>62</v>
-      </c>
-      <c r="B7" s="32"/>
-      <c r="C7" s="32"/>
-      <c r="E7" s="32" t="s">
-        <v>65</v>
-      </c>
-      <c r="F7" s="32"/>
-      <c r="G7" s="32"/>
-      <c r="H7" s="32" t="s">
-        <v>68</v>
-      </c>
-      <c r="I7" s="32"/>
-      <c r="J7" s="32"/>
-      <c r="L7" s="32" t="s">
-        <v>71</v>
-      </c>
-      <c r="M7" s="32"/>
-      <c r="N7" s="32"/>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" s="32"/>
-      <c r="B8" s="32"/>
-      <c r="C8" s="32"/>
-      <c r="E8" s="32"/>
-      <c r="F8" s="32"/>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
-      <c r="I8" s="32"/>
-      <c r="J8" s="32"/>
-      <c r="L8" s="32"/>
-      <c r="M8" s="32"/>
-      <c r="N8" s="32"/>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" s="33" t="s">
-        <v>63</v>
-      </c>
-      <c r="B9" s="33"/>
-      <c r="C9" s="33"/>
-      <c r="E9" s="33" t="s">
-        <v>66</v>
-      </c>
-      <c r="F9" s="33"/>
-      <c r="G9" s="33"/>
-      <c r="H9" s="33" t="s">
-        <v>69</v>
-      </c>
-      <c r="I9" s="33"/>
-      <c r="J9" s="33"/>
-      <c r="L9" s="33" t="s">
-        <v>72</v>
-      </c>
-      <c r="M9" s="33"/>
-      <c r="N9" s="33"/>
-    </row>
-    <row r="11" spans="1:14">
-      <c r="A11" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4"/>
-      <c r="J11" s="4"/>
-      <c r="K11" s="4"/>
-      <c r="L11" s="4"/>
-      <c r="M11" s="4"/>
-      <c r="N11" s="4"/>
-    </row>
-    <row r="13" spans="1:14">
-      <c r="A13" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="H13" s="5" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
-      <c r="A14" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="D14" s="6">
-        <v>840</v>
-      </c>
-      <c r="E14" s="6">
-        <v>810</v>
-      </c>
-      <c r="F14" s="6">
-        <v>30</v>
-      </c>
-      <c r="G14" s="6">
+      <c r="R25" s="22"/>
+      <c r="S25" s="22"/>
+      <c r="T25" s="22"/>
+      <c r="U25" s="22">
+        <v>0</v>
+      </c>
+      <c r="V25" s="22"/>
+      <c r="W25" s="22"/>
+      <c r="X25" s="22"/>
+      <c r="Y25" s="26">
         <v>2</v>
       </c>
-      <c r="H14" s="6">
+      <c r="Z25" s="26"/>
+      <c r="AA25" s="26"/>
+      <c r="AB25" s="26"/>
+    </row>
+    <row r="26" spans="1:28" ht="19.5" customHeight="1">
+      <c r="A26" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="B26" s="21"/>
+      <c r="C26" s="21"/>
+      <c r="D26" s="21"/>
+      <c r="E26" s="23">
+        <v>0.858</v>
+      </c>
+      <c r="F26" s="23"/>
+      <c r="G26" s="23"/>
+      <c r="H26" s="23"/>
+      <c r="I26" s="27">
+        <v>-22</v>
+      </c>
+      <c r="J26" s="27"/>
+      <c r="K26" s="27"/>
+      <c r="L26" s="27"/>
+      <c r="M26" s="22">
+        <v>1</v>
+      </c>
+      <c r="N26" s="22"/>
+      <c r="O26" s="22"/>
+      <c r="P26" s="22"/>
+      <c r="Q26" s="22">
         <v>2</v>
       </c>
-    </row>
-    <row r="15" spans="1:14">
-      <c r="A15" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="D15" s="6">
-        <v>530</v>
-      </c>
-      <c r="E15" s="6">
-        <v>552</v>
-      </c>
-      <c r="F15" s="6">
-        <v>-22</v>
-      </c>
-      <c r="G15" s="6">
+      <c r="R26" s="22"/>
+      <c r="S26" s="22"/>
+      <c r="T26" s="22"/>
+      <c r="U26" s="22">
         <v>1</v>
       </c>
-      <c r="H15" s="6">
+      <c r="V26" s="22"/>
+      <c r="W26" s="22"/>
+      <c r="X26" s="22"/>
+      <c r="Y26" s="26">
         <v>2</v>
       </c>
-    </row>
-    <row r="16" spans="1:14">
-      <c r="A16" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="D16" s="6">
-        <v>320</v>
-      </c>
-      <c r="E16" s="6">
-        <v>300</v>
-      </c>
-      <c r="F16" s="6">
-        <v>20</v>
-      </c>
-      <c r="G16" s="6">
-        <v>1</v>
-      </c>
-      <c r="H16" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14">
-      <c r="A17" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="D17" s="6">
-        <v>410</v>
-      </c>
-      <c r="E17" s="6">
-        <v>354</v>
-      </c>
-      <c r="F17" s="6">
-        <v>56</v>
-      </c>
-      <c r="G17" s="6">
-        <v>2</v>
-      </c>
-      <c r="H17" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14">
-      <c r="A25" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
-      <c r="G25" s="7"/>
-      <c r="H25" s="7"/>
-      <c r="I25" s="7"/>
-      <c r="J25" s="7"/>
-      <c r="K25" s="7"/>
-      <c r="L25" s="7"/>
-      <c r="M25" s="7"/>
-      <c r="N25" s="7"/>
+      <c r="Z26" s="26"/>
+      <c r="AA26" s="26"/>
+      <c r="AB26" s="26"/>
+    </row>
+    <row r="27" spans="1:28" ht="19.5" customHeight="1">
+      <c r="A27" s="21"/>
+      <c r="B27" s="21"/>
+      <c r="C27" s="21"/>
+      <c r="D27" s="21"/>
+      <c r="E27" s="23"/>
+      <c r="F27" s="23"/>
+      <c r="G27" s="23"/>
+      <c r="H27" s="23"/>
+      <c r="I27" s="27"/>
+      <c r="J27" s="27"/>
+      <c r="K27" s="27"/>
+      <c r="L27" s="27"/>
+      <c r="M27" s="22"/>
+      <c r="N27" s="22"/>
+      <c r="O27" s="22"/>
+      <c r="P27" s="22"/>
+      <c r="Q27" s="22"/>
+      <c r="R27" s="22"/>
+      <c r="S27" s="22"/>
+      <c r="T27" s="22"/>
+      <c r="U27" s="22"/>
+      <c r="V27" s="22"/>
+      <c r="W27" s="22"/>
+      <c r="X27" s="22"/>
+      <c r="Y27" s="28"/>
+      <c r="Z27" s="28"/>
+      <c r="AA27" s="28"/>
+      <c r="AB27" s="28"/>
+    </row>
+    <row r="28" spans="1:28" ht="19.5" customHeight="1">
+      <c r="A28" s="21"/>
+      <c r="B28" s="21"/>
+      <c r="C28" s="21"/>
+      <c r="D28" s="21"/>
+      <c r="E28" s="23"/>
+      <c r="F28" s="23"/>
+      <c r="G28" s="23"/>
+      <c r="H28" s="23"/>
+      <c r="I28" s="27"/>
+      <c r="J28" s="27"/>
+      <c r="K28" s="27"/>
+      <c r="L28" s="27"/>
+      <c r="M28" s="22"/>
+      <c r="N28" s="22"/>
+      <c r="O28" s="22"/>
+      <c r="P28" s="22"/>
+      <c r="Q28" s="22"/>
+      <c r="R28" s="22"/>
+      <c r="S28" s="22"/>
+      <c r="T28" s="22"/>
+      <c r="U28" s="22"/>
+      <c r="V28" s="22"/>
+      <c r="W28" s="22"/>
+      <c r="X28" s="22"/>
+      <c r="Y28" s="28"/>
+      <c r="Z28" s="28"/>
+      <c r="AA28" s="28"/>
+      <c r="AB28" s="28"/>
+    </row>
+    <row r="29" spans="1:28" ht="19.5" customHeight="1">
+      <c r="A29" s="21"/>
+      <c r="B29" s="21"/>
+      <c r="C29" s="21"/>
+      <c r="D29" s="21"/>
+      <c r="E29" s="23"/>
+      <c r="F29" s="23"/>
+      <c r="G29" s="23"/>
+      <c r="H29" s="23"/>
+      <c r="I29" s="27"/>
+      <c r="J29" s="27"/>
+      <c r="K29" s="27"/>
+      <c r="L29" s="27"/>
+      <c r="M29" s="22"/>
+      <c r="N29" s="22"/>
+      <c r="O29" s="22"/>
+      <c r="P29" s="22"/>
+      <c r="Q29" s="22"/>
+      <c r="R29" s="22"/>
+      <c r="S29" s="22"/>
+      <c r="T29" s="22"/>
+      <c r="U29" s="22"/>
+      <c r="V29" s="22"/>
+      <c r="W29" s="22"/>
+      <c r="X29" s="22"/>
+      <c r="Y29" s="28"/>
+      <c r="Z29" s="28"/>
+      <c r="AA29" s="28"/>
+      <c r="AB29" s="28"/>
+    </row>
+    <row r="30" spans="1:28" ht="19.5" customHeight="1">
+      <c r="A30" s="21"/>
+      <c r="B30" s="21"/>
+      <c r="C30" s="21"/>
+      <c r="D30" s="21"/>
+      <c r="E30" s="23"/>
+      <c r="F30" s="23"/>
+      <c r="G30" s="23"/>
+      <c r="H30" s="23"/>
+      <c r="I30" s="27"/>
+      <c r="J30" s="27"/>
+      <c r="K30" s="27"/>
+      <c r="L30" s="27"/>
+      <c r="M30" s="22"/>
+      <c r="N30" s="22"/>
+      <c r="O30" s="22"/>
+      <c r="P30" s="22"/>
+      <c r="Q30" s="22"/>
+      <c r="R30" s="22"/>
+      <c r="S30" s="22"/>
+      <c r="T30" s="22"/>
+      <c r="U30" s="22"/>
+      <c r="V30" s="22"/>
+      <c r="W30" s="22"/>
+      <c r="X30" s="22"/>
+      <c r="Y30" s="28"/>
+      <c r="Z30" s="28"/>
+      <c r="AA30" s="28"/>
+      <c r="AB30" s="28"/>
+    </row>
+    <row r="31" spans="1:28" ht="19.5" customHeight="1">
+      <c r="A31" s="21"/>
+      <c r="B31" s="21"/>
+      <c r="C31" s="21"/>
+      <c r="D31" s="21"/>
+      <c r="E31" s="23"/>
+      <c r="F31" s="23"/>
+      <c r="G31" s="23"/>
+      <c r="H31" s="23"/>
+      <c r="I31" s="27"/>
+      <c r="J31" s="27"/>
+      <c r="K31" s="27"/>
+      <c r="L31" s="27"/>
+      <c r="M31" s="22"/>
+      <c r="N31" s="22"/>
+      <c r="O31" s="22"/>
+      <c r="P31" s="22"/>
+      <c r="Q31" s="22"/>
+      <c r="R31" s="22"/>
+      <c r="S31" s="22"/>
+      <c r="T31" s="22"/>
+      <c r="U31" s="22"/>
+      <c r="V31" s="22"/>
+      <c r="W31" s="22"/>
+      <c r="X31" s="22"/>
+      <c r="Y31" s="28"/>
+      <c r="Z31" s="28"/>
+      <c r="AA31" s="28"/>
+      <c r="AB31" s="28"/>
+    </row>
+    <row r="32" spans="1:28" ht="19.5" customHeight="1">
+      <c r="A32" s="21"/>
+      <c r="B32" s="21"/>
+      <c r="C32" s="21"/>
+      <c r="D32" s="21"/>
+      <c r="E32" s="23"/>
+      <c r="F32" s="23"/>
+      <c r="G32" s="23"/>
+      <c r="H32" s="23"/>
+      <c r="I32" s="27"/>
+      <c r="J32" s="27"/>
+      <c r="K32" s="27"/>
+      <c r="L32" s="27"/>
+      <c r="M32" s="22"/>
+      <c r="N32" s="22"/>
+      <c r="O32" s="22"/>
+      <c r="P32" s="22"/>
+      <c r="Q32" s="22"/>
+      <c r="R32" s="22"/>
+      <c r="S32" s="22"/>
+      <c r="T32" s="22"/>
+      <c r="U32" s="22"/>
+      <c r="V32" s="22"/>
+      <c r="W32" s="22"/>
+      <c r="X32" s="22"/>
+      <c r="Y32" s="28"/>
+      <c r="Z32" s="28"/>
+      <c r="AA32" s="28"/>
+      <c r="AB32" s="28"/>
     </row>
   </sheetData>
-  <mergeCells count="21">
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="L1:N1"/>
-    <mergeCell ref="A2:N2"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="K4:N4"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A7:C8"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="E6:G6"/>
-    <mergeCell ref="E7:G8"/>
-    <mergeCell ref="E9:G9"/>
-    <mergeCell ref="H6:J6"/>
-    <mergeCell ref="H7:J8"/>
-    <mergeCell ref="H9:J9"/>
-    <mergeCell ref="L6:N6"/>
-    <mergeCell ref="L7:N8"/>
-    <mergeCell ref="L9:N9"/>
-    <mergeCell ref="A11:N11"/>
-    <mergeCell ref="A25:N25"/>
+  <mergeCells count="87">
+    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="R1:X1"/>
+    <mergeCell ref="Y1:AB1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="J2:N2"/>
+    <mergeCell ref="O2:P2"/>
+    <mergeCell ref="Q2:U2"/>
+    <mergeCell ref="V2:W2"/>
+    <mergeCell ref="X2:AB2"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="H4:N4"/>
+    <mergeCell ref="H5:N5"/>
+    <mergeCell ref="H6:N6"/>
+    <mergeCell ref="O4:U4"/>
+    <mergeCell ref="O5:U5"/>
+    <mergeCell ref="O6:U6"/>
+    <mergeCell ref="V4:AB4"/>
+    <mergeCell ref="V5:AB5"/>
+    <mergeCell ref="V6:AB6"/>
+    <mergeCell ref="A23:O23"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="E24:H24"/>
+    <mergeCell ref="I24:L24"/>
+    <mergeCell ref="M24:P24"/>
+    <mergeCell ref="Q24:T24"/>
+    <mergeCell ref="U24:X24"/>
+    <mergeCell ref="Y24:AB24"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="E25:H25"/>
+    <mergeCell ref="I25:L25"/>
+    <mergeCell ref="M25:P25"/>
+    <mergeCell ref="Q25:T25"/>
+    <mergeCell ref="U25:X25"/>
+    <mergeCell ref="Y25:AB25"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="E26:H26"/>
+    <mergeCell ref="I26:L26"/>
+    <mergeCell ref="M26:P26"/>
+    <mergeCell ref="Q26:T26"/>
+    <mergeCell ref="U26:X26"/>
+    <mergeCell ref="Y26:AB26"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="E27:H27"/>
+    <mergeCell ref="I27:L27"/>
+    <mergeCell ref="M27:P27"/>
+    <mergeCell ref="Q27:T27"/>
+    <mergeCell ref="U27:X27"/>
+    <mergeCell ref="Y27:AB27"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="E28:H28"/>
+    <mergeCell ref="I28:L28"/>
+    <mergeCell ref="M28:P28"/>
+    <mergeCell ref="Q28:T28"/>
+    <mergeCell ref="U28:X28"/>
+    <mergeCell ref="Y28:AB28"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="E29:H29"/>
+    <mergeCell ref="I29:L29"/>
+    <mergeCell ref="M29:P29"/>
+    <mergeCell ref="Q29:T29"/>
+    <mergeCell ref="U29:X29"/>
+    <mergeCell ref="Y29:AB29"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="E30:H30"/>
+    <mergeCell ref="I30:L30"/>
+    <mergeCell ref="M30:P30"/>
+    <mergeCell ref="Q30:T30"/>
+    <mergeCell ref="U30:X30"/>
+    <mergeCell ref="Y30:AB30"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="E31:H31"/>
+    <mergeCell ref="I31:L31"/>
+    <mergeCell ref="M31:P31"/>
+    <mergeCell ref="Q31:T31"/>
+    <mergeCell ref="U31:X31"/>
+    <mergeCell ref="Y31:AB31"/>
+    <mergeCell ref="A32:D32"/>
+    <mergeCell ref="E32:H32"/>
+    <mergeCell ref="I32:L32"/>
+    <mergeCell ref="M32:P32"/>
+    <mergeCell ref="Q32:T32"/>
+    <mergeCell ref="U32:X32"/>
+    <mergeCell ref="Y32:AB32"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.15" right="0.15" top="0.2" bottom="0.2" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape"/>
   <headerFooter>
     <oddFooter>&amp;LPrepared by Anass ASSRI | WFM&amp;CDesign reference&amp;RConfidential</oddFooter>
   </headerFooter>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -3118,354 +7009,3582 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <tabColor rgb="FFD6A84B"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N25"/>
+  <dimension ref="A1:AK32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="14" width="12.7109375" customWidth="1"/>
+    <col min="1" max="28" width="7.42578125" style="8" customWidth="1"/>
+    <col min="30" max="37" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="34" customHeight="1">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:37" ht="42" customHeight="1">
+      <c r="A1" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="9"/>
+      <c r="Q1" s="9"/>
+      <c r="R1" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="S1" s="10"/>
+      <c r="T1" s="10"/>
+      <c r="U1" s="10"/>
+      <c r="V1" s="10"/>
+      <c r="W1" s="10"/>
+      <c r="X1" s="10"/>
+      <c r="Y1" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z1" s="11"/>
+      <c r="AA1" s="11"/>
+      <c r="AB1" s="11"/>
+      <c r="AD1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>92</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="2" spans="1:37" ht="39" customHeight="1">
+      <c r="A2" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" s="12"/>
+      <c r="C2" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="I2" s="12"/>
+      <c r="J2" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="K2" s="13"/>
+      <c r="L2" s="13"/>
+      <c r="M2" s="13"/>
+      <c r="N2" s="13"/>
+      <c r="O2" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="P2" s="12"/>
+      <c r="Q2" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="R2" s="13"/>
+      <c r="S2" s="13"/>
+      <c r="T2" s="13"/>
+      <c r="U2" s="13"/>
+      <c r="V2" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="W2" s="12"/>
+      <c r="X2" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="2" t="s">
+      <c r="Y2" s="13"/>
+      <c r="Z2" s="13"/>
+      <c r="AA2" s="13"/>
+      <c r="AB2" s="13"/>
+      <c r="AD2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AE2">
+        <v>2.8</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>93</v>
+      </c>
+      <c r="AK2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:37" s="8" customFormat="1" ht="7.5" customHeight="1">
+      <c r="AD3" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE3" s="8">
+        <v>2.1</v>
+      </c>
+      <c r="AJ3" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="AK3" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:37" ht="5.25" customHeight="1">
+      <c r="A4" s="14"/>
+      <c r="B4" s="14"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="15"/>
+      <c r="I4" s="15"/>
+      <c r="J4" s="15"/>
+      <c r="K4" s="15"/>
+      <c r="L4" s="15"/>
+      <c r="M4" s="15"/>
+      <c r="N4" s="15"/>
+      <c r="O4" s="14"/>
+      <c r="P4" s="14"/>
+      <c r="Q4" s="14"/>
+      <c r="R4" s="14"/>
+      <c r="S4" s="14"/>
+      <c r="T4" s="14"/>
+      <c r="U4" s="14"/>
+      <c r="V4" s="15"/>
+      <c r="W4" s="15"/>
+      <c r="X4" s="15"/>
+      <c r="Y4" s="15"/>
+      <c r="Z4" s="15"/>
+      <c r="AA4" s="15"/>
+      <c r="AB4" s="15"/>
+      <c r="AD4" t="s">
+        <v>44</v>
+      </c>
+      <c r="AE4">
+        <v>1.6</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>95</v>
+      </c>
+      <c r="AK4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:37" ht="27" customHeight="1">
+      <c r="A5" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="B5" s="16"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="I5" s="16"/>
+      <c r="J5" s="16"/>
+      <c r="K5" s="16"/>
+      <c r="L5" s="16"/>
+      <c r="M5" s="16"/>
+      <c r="N5" s="16"/>
+      <c r="O5" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="P5" s="16"/>
+      <c r="Q5" s="16"/>
+      <c r="R5" s="16"/>
+      <c r="S5" s="16"/>
+      <c r="T5" s="16"/>
+      <c r="U5" s="16"/>
+      <c r="V5" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="W5" s="16"/>
+      <c r="X5" s="16"/>
+      <c r="Y5" s="16"/>
+      <c r="Z5" s="16"/>
+      <c r="AA5" s="16"/>
+      <c r="AB5" s="16"/>
+      <c r="AD5" t="s">
+        <v>45</v>
+      </c>
+      <c r="AE5">
+        <v>0.9</v>
+      </c>
+      <c r="AJ5" t="s">
+        <v>96</v>
+      </c>
+      <c r="AK5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:37" ht="72" customHeight="1">
+      <c r="A6" s="30">
+        <v>18</v>
+      </c>
+      <c r="B6" s="30"/>
+      <c r="C6" s="30"/>
+      <c r="D6" s="30"/>
+      <c r="E6" s="30"/>
+      <c r="F6" s="30"/>
+      <c r="G6" s="30"/>
+      <c r="H6" s="17">
+        <v>7.4</v>
+      </c>
+      <c r="I6" s="17"/>
+      <c r="J6" s="17"/>
+      <c r="K6" s="17"/>
+      <c r="L6" s="17"/>
+      <c r="M6" s="17"/>
+      <c r="N6" s="17"/>
+      <c r="O6" s="30">
+        <v>11</v>
+      </c>
+      <c r="P6" s="30"/>
+      <c r="Q6" s="30"/>
+      <c r="R6" s="30"/>
+      <c r="S6" s="30"/>
+      <c r="T6" s="30"/>
+      <c r="U6" s="30"/>
+      <c r="V6" s="30">
+        <v>2</v>
+      </c>
+      <c r="W6" s="30"/>
+      <c r="X6" s="30"/>
+      <c r="Y6" s="30"/>
+      <c r="Z6" s="30"/>
+      <c r="AA6" s="30"/>
+      <c r="AB6" s="30"/>
+    </row>
+    <row r="7" spans="1:37" s="8" customFormat="1" ht="7.5" customHeight="1"/>
+    <row r="8" spans="1:37" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="9" spans="1:37" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="10" spans="1:37" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="11" spans="1:37" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="12" spans="1:37" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="13" spans="1:37" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="14" spans="1:37" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="15" spans="1:37" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="16" spans="1:37" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="17" spans="1:28" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="18" spans="1:28" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="19" spans="1:28" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="20" spans="1:28" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="21" spans="1:28" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="22" spans="1:28" s="8" customFormat="1" ht="7.5" customHeight="1"/>
+    <row r="23" spans="1:28" ht="25.5" customHeight="1">
+      <c r="A23" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="B23" s="19"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="19"/>
+      <c r="F23" s="19"/>
+      <c r="G23" s="19"/>
+      <c r="H23" s="19"/>
+      <c r="I23" s="19"/>
+      <c r="J23" s="19"/>
+      <c r="K23" s="19"/>
+      <c r="L23" s="19"/>
+      <c r="M23" s="19"/>
+      <c r="N23" s="19"/>
+      <c r="O23" s="19"/>
+    </row>
+    <row r="24" spans="1:28" ht="22.5" customHeight="1">
+      <c r="A24" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="B24" s="20"/>
+      <c r="C24" s="20"/>
+      <c r="D24" s="20"/>
+      <c r="E24" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="F24" s="20"/>
+      <c r="G24" s="20"/>
+      <c r="H24" s="20"/>
+      <c r="I24" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="J24" s="20"/>
+      <c r="K24" s="20"/>
+      <c r="L24" s="20"/>
+      <c r="M24" s="20" t="s">
+        <v>100</v>
+      </c>
+      <c r="N24" s="20"/>
+      <c r="O24" s="20"/>
+      <c r="P24" s="20"/>
+      <c r="Q24" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="R24" s="20"/>
+      <c r="S24" s="20"/>
+      <c r="T24" s="20"/>
+      <c r="U24" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="V24" s="20"/>
+      <c r="W24" s="20"/>
+      <c r="X24" s="20"/>
+      <c r="Y24" s="20" t="s">
+        <v>103</v>
+      </c>
+      <c r="Z24" s="20"/>
+      <c r="AA24" s="20"/>
+      <c r="AB24" s="20"/>
+    </row>
+    <row r="25" spans="1:28" ht="19.5" customHeight="1">
+      <c r="A25" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="B25" s="21"/>
+      <c r="C25" s="21"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="22">
+        <v>6</v>
+      </c>
+      <c r="F25" s="22"/>
+      <c r="G25" s="22"/>
+      <c r="H25" s="22"/>
+      <c r="I25" s="24">
+        <v>2.8</v>
+      </c>
+      <c r="J25" s="24"/>
+      <c r="K25" s="24"/>
+      <c r="L25" s="24"/>
+      <c r="M25" s="22">
+        <v>4</v>
+      </c>
+      <c r="N25" s="22"/>
+      <c r="O25" s="22"/>
+      <c r="P25" s="22"/>
+      <c r="Q25" s="26">
+        <v>3</v>
+      </c>
+      <c r="R25" s="26"/>
+      <c r="S25" s="26"/>
+      <c r="T25" s="26"/>
+      <c r="U25" s="22">
+        <v>2</v>
+      </c>
+      <c r="V25" s="22"/>
+      <c r="W25" s="22"/>
+      <c r="X25" s="22"/>
+      <c r="Y25" s="22">
         <v>1</v>
       </c>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-    </row>
-    <row r="2" spans="1:14" ht="21" customHeight="1">
-      <c r="A2" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
-      <c r="N2" s="3"/>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="B4" s="30" t="s">
-        <v>89</v>
-      </c>
-      <c r="C4" s="30"/>
-      <c r="D4" s="29" t="s">
-        <v>90</v>
-      </c>
-      <c r="E4" s="30" t="s">
-        <v>91</v>
-      </c>
-      <c r="F4" s="30"/>
-      <c r="G4" s="29" t="s">
-        <v>92</v>
-      </c>
-      <c r="H4" s="30" t="s">
-        <v>93</v>
-      </c>
-      <c r="I4" s="30"/>
-      <c r="J4" s="29" t="s">
-        <v>94</v>
-      </c>
-      <c r="K4" s="30" t="s">
-        <v>95</v>
-      </c>
-      <c r="L4" s="30"/>
-      <c r="M4" s="30"/>
-      <c r="N4" s="30"/>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6" s="31" t="s">
-        <v>96</v>
-      </c>
-      <c r="B6" s="31"/>
-      <c r="C6" s="31"/>
-      <c r="E6" s="31" t="s">
-        <v>99</v>
-      </c>
-      <c r="F6" s="31"/>
-      <c r="G6" s="31"/>
-      <c r="H6" s="31" t="s">
-        <v>102</v>
-      </c>
-      <c r="I6" s="31"/>
-      <c r="J6" s="31"/>
-      <c r="L6" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="M6" s="31"/>
-      <c r="N6" s="31"/>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="A7" s="32" t="s">
-        <v>97</v>
-      </c>
-      <c r="B7" s="32"/>
-      <c r="C7" s="32"/>
-      <c r="E7" s="32" t="s">
-        <v>100</v>
-      </c>
-      <c r="F7" s="32"/>
-      <c r="G7" s="32"/>
-      <c r="H7" s="32" t="s">
-        <v>103</v>
-      </c>
-      <c r="I7" s="32"/>
-      <c r="J7" s="32"/>
-      <c r="L7" s="32" t="s">
-        <v>106</v>
-      </c>
-      <c r="M7" s="32"/>
-      <c r="N7" s="32"/>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" s="32"/>
-      <c r="B8" s="32"/>
-      <c r="C8" s="32"/>
-      <c r="E8" s="32"/>
-      <c r="F8" s="32"/>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
-      <c r="I8" s="32"/>
-      <c r="J8" s="32"/>
-      <c r="L8" s="32"/>
-      <c r="M8" s="32"/>
-      <c r="N8" s="32"/>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" s="33" t="s">
-        <v>98</v>
-      </c>
-      <c r="B9" s="33"/>
-      <c r="C9" s="33"/>
-      <c r="E9" s="33" t="s">
-        <v>101</v>
-      </c>
-      <c r="F9" s="33"/>
-      <c r="G9" s="33"/>
-      <c r="H9" s="33" t="s">
-        <v>104</v>
-      </c>
-      <c r="I9" s="33"/>
-      <c r="J9" s="33"/>
-      <c r="L9" s="33" t="s">
-        <v>107</v>
-      </c>
-      <c r="M9" s="33"/>
-      <c r="N9" s="33"/>
-    </row>
-    <row r="11" spans="1:14">
-      <c r="A11" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4"/>
-      <c r="J11" s="4"/>
-      <c r="K11" s="4"/>
-      <c r="L11" s="4"/>
-      <c r="M11" s="4"/>
-      <c r="N11" s="4"/>
-    </row>
-    <row r="13" spans="1:14">
-      <c r="A13" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
-      <c r="A14" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B14" s="6">
-        <v>6</v>
-      </c>
-      <c r="C14" s="6">
-        <v>2.8</v>
-      </c>
-      <c r="D14" s="6">
+      <c r="Z25" s="22"/>
+      <c r="AA25" s="22"/>
+      <c r="AB25" s="22"/>
+    </row>
+    <row r="26" spans="1:28" ht="19.5" customHeight="1">
+      <c r="A26" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="B26" s="21"/>
+      <c r="C26" s="21"/>
+      <c r="D26" s="21"/>
+      <c r="E26" s="22">
+        <v>5</v>
+      </c>
+      <c r="F26" s="22"/>
+      <c r="G26" s="22"/>
+      <c r="H26" s="22"/>
+      <c r="I26" s="24">
+        <v>2.1</v>
+      </c>
+      <c r="J26" s="24"/>
+      <c r="K26" s="24"/>
+      <c r="L26" s="24"/>
+      <c r="M26" s="22">
         <v>4</v>
       </c>
-      <c r="E14" s="6">
-        <v>3</v>
-      </c>
-      <c r="F14" s="6">
-        <v>2</v>
-      </c>
-      <c r="G14" s="6">
+      <c r="N26" s="22"/>
+      <c r="O26" s="22"/>
+      <c r="P26" s="22"/>
+      <c r="Q26" s="26">
+        <v>4</v>
+      </c>
+      <c r="R26" s="26"/>
+      <c r="S26" s="26"/>
+      <c r="T26" s="26"/>
+      <c r="U26" s="22">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="1:14">
-      <c r="A15" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B15" s="6">
-        <v>5</v>
-      </c>
-      <c r="C15" s="6">
-        <v>2.1</v>
-      </c>
-      <c r="D15" s="6">
-        <v>4</v>
-      </c>
-      <c r="E15" s="6">
-        <v>4</v>
-      </c>
-      <c r="F15" s="6">
-        <v>1</v>
-      </c>
-      <c r="G15" s="6">
+      <c r="V26" s="22"/>
+      <c r="W26" s="22"/>
+      <c r="X26" s="22"/>
+      <c r="Y26" s="22">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:14">
-      <c r="A16" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B16" s="6">
-        <v>4</v>
-      </c>
-      <c r="C16" s="6">
-        <v>1.6</v>
-      </c>
-      <c r="D16" s="6">
-        <v>3</v>
-      </c>
-      <c r="E16" s="6">
-        <v>2</v>
-      </c>
-      <c r="F16" s="6">
-        <v>1</v>
-      </c>
-      <c r="G16" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14">
-      <c r="A17" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="B17" s="6">
-        <v>3</v>
-      </c>
-      <c r="C17" s="6">
-        <v>0.9</v>
-      </c>
-      <c r="D17" s="6">
-        <v>2</v>
-      </c>
-      <c r="E17" s="6">
-        <v>2</v>
-      </c>
-      <c r="F17" s="6">
-        <v>1</v>
-      </c>
-      <c r="G17" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14">
-      <c r="A20" s="4" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14">
-      <c r="A21" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="B21" s="34" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14">
-      <c r="A25" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
-      <c r="G25" s="7"/>
-      <c r="H25" s="7"/>
-      <c r="I25" s="7"/>
-      <c r="J25" s="7"/>
-      <c r="K25" s="7"/>
-      <c r="L25" s="7"/>
-      <c r="M25" s="7"/>
-      <c r="N25" s="7"/>
+      <c r="Z26" s="22"/>
+      <c r="AA26" s="22"/>
+      <c r="AB26" s="22"/>
+    </row>
+    <row r="27" spans="1:28" ht="19.5" customHeight="1">
+      <c r="A27" s="21"/>
+      <c r="B27" s="21"/>
+      <c r="C27" s="21"/>
+      <c r="D27" s="21"/>
+      <c r="E27" s="22"/>
+      <c r="F27" s="22"/>
+      <c r="G27" s="22"/>
+      <c r="H27" s="22"/>
+      <c r="I27" s="24"/>
+      <c r="J27" s="24"/>
+      <c r="K27" s="24"/>
+      <c r="L27" s="24"/>
+      <c r="M27" s="22"/>
+      <c r="N27" s="22"/>
+      <c r="O27" s="22"/>
+      <c r="P27" s="22"/>
+      <c r="Q27" s="28"/>
+      <c r="R27" s="28"/>
+      <c r="S27" s="28"/>
+      <c r="T27" s="28"/>
+      <c r="U27" s="22"/>
+      <c r="V27" s="22"/>
+      <c r="W27" s="22"/>
+      <c r="X27" s="22"/>
+      <c r="Y27" s="22"/>
+      <c r="Z27" s="22"/>
+      <c r="AA27" s="22"/>
+      <c r="AB27" s="22"/>
+    </row>
+    <row r="28" spans="1:28" ht="19.5" customHeight="1">
+      <c r="A28" s="21"/>
+      <c r="B28" s="21"/>
+      <c r="C28" s="21"/>
+      <c r="D28" s="21"/>
+      <c r="E28" s="22"/>
+      <c r="F28" s="22"/>
+      <c r="G28" s="22"/>
+      <c r="H28" s="22"/>
+      <c r="I28" s="24"/>
+      <c r="J28" s="24"/>
+      <c r="K28" s="24"/>
+      <c r="L28" s="24"/>
+      <c r="M28" s="22"/>
+      <c r="N28" s="22"/>
+      <c r="O28" s="22"/>
+      <c r="P28" s="22"/>
+      <c r="Q28" s="28"/>
+      <c r="R28" s="28"/>
+      <c r="S28" s="28"/>
+      <c r="T28" s="28"/>
+      <c r="U28" s="22"/>
+      <c r="V28" s="22"/>
+      <c r="W28" s="22"/>
+      <c r="X28" s="22"/>
+      <c r="Y28" s="22"/>
+      <c r="Z28" s="22"/>
+      <c r="AA28" s="22"/>
+      <c r="AB28" s="22"/>
+    </row>
+    <row r="29" spans="1:28" ht="19.5" customHeight="1">
+      <c r="A29" s="21"/>
+      <c r="B29" s="21"/>
+      <c r="C29" s="21"/>
+      <c r="D29" s="21"/>
+      <c r="E29" s="22"/>
+      <c r="F29" s="22"/>
+      <c r="G29" s="22"/>
+      <c r="H29" s="22"/>
+      <c r="I29" s="24"/>
+      <c r="J29" s="24"/>
+      <c r="K29" s="24"/>
+      <c r="L29" s="24"/>
+      <c r="M29" s="22"/>
+      <c r="N29" s="22"/>
+      <c r="O29" s="22"/>
+      <c r="P29" s="22"/>
+      <c r="Q29" s="28"/>
+      <c r="R29" s="28"/>
+      <c r="S29" s="28"/>
+      <c r="T29" s="28"/>
+      <c r="U29" s="22"/>
+      <c r="V29" s="22"/>
+      <c r="W29" s="22"/>
+      <c r="X29" s="22"/>
+      <c r="Y29" s="22"/>
+      <c r="Z29" s="22"/>
+      <c r="AA29" s="22"/>
+      <c r="AB29" s="22"/>
+    </row>
+    <row r="30" spans="1:28" ht="19.5" customHeight="1">
+      <c r="A30" s="21"/>
+      <c r="B30" s="21"/>
+      <c r="C30" s="21"/>
+      <c r="D30" s="21"/>
+      <c r="E30" s="22"/>
+      <c r="F30" s="22"/>
+      <c r="G30" s="22"/>
+      <c r="H30" s="22"/>
+      <c r="I30" s="24"/>
+      <c r="J30" s="24"/>
+      <c r="K30" s="24"/>
+      <c r="L30" s="24"/>
+      <c r="M30" s="22"/>
+      <c r="N30" s="22"/>
+      <c r="O30" s="22"/>
+      <c r="P30" s="22"/>
+      <c r="Q30" s="28"/>
+      <c r="R30" s="28"/>
+      <c r="S30" s="28"/>
+      <c r="T30" s="28"/>
+      <c r="U30" s="22"/>
+      <c r="V30" s="22"/>
+      <c r="W30" s="22"/>
+      <c r="X30" s="22"/>
+      <c r="Y30" s="22"/>
+      <c r="Z30" s="22"/>
+      <c r="AA30" s="22"/>
+      <c r="AB30" s="22"/>
+    </row>
+    <row r="31" spans="1:28" ht="19.5" customHeight="1">
+      <c r="A31" s="21"/>
+      <c r="B31" s="21"/>
+      <c r="C31" s="21"/>
+      <c r="D31" s="21"/>
+      <c r="E31" s="22"/>
+      <c r="F31" s="22"/>
+      <c r="G31" s="22"/>
+      <c r="H31" s="22"/>
+      <c r="I31" s="24"/>
+      <c r="J31" s="24"/>
+      <c r="K31" s="24"/>
+      <c r="L31" s="24"/>
+      <c r="M31" s="22"/>
+      <c r="N31" s="22"/>
+      <c r="O31" s="22"/>
+      <c r="P31" s="22"/>
+      <c r="Q31" s="28"/>
+      <c r="R31" s="28"/>
+      <c r="S31" s="28"/>
+      <c r="T31" s="28"/>
+      <c r="U31" s="22"/>
+      <c r="V31" s="22"/>
+      <c r="W31" s="22"/>
+      <c r="X31" s="22"/>
+      <c r="Y31" s="22"/>
+      <c r="Z31" s="22"/>
+      <c r="AA31" s="22"/>
+      <c r="AB31" s="22"/>
+    </row>
+    <row r="32" spans="1:28" ht="19.5" customHeight="1">
+      <c r="A32" s="21"/>
+      <c r="B32" s="21"/>
+      <c r="C32" s="21"/>
+      <c r="D32" s="21"/>
+      <c r="E32" s="22"/>
+      <c r="F32" s="22"/>
+      <c r="G32" s="22"/>
+      <c r="H32" s="22"/>
+      <c r="I32" s="24"/>
+      <c r="J32" s="24"/>
+      <c r="K32" s="24"/>
+      <c r="L32" s="24"/>
+      <c r="M32" s="22"/>
+      <c r="N32" s="22"/>
+      <c r="O32" s="22"/>
+      <c r="P32" s="22"/>
+      <c r="Q32" s="28"/>
+      <c r="R32" s="28"/>
+      <c r="S32" s="28"/>
+      <c r="T32" s="28"/>
+      <c r="U32" s="22"/>
+      <c r="V32" s="22"/>
+      <c r="W32" s="22"/>
+      <c r="X32" s="22"/>
+      <c r="Y32" s="22"/>
+      <c r="Z32" s="22"/>
+      <c r="AA32" s="22"/>
+      <c r="AB32" s="22"/>
     </row>
   </sheetData>
-  <mergeCells count="21">
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="L1:N1"/>
-    <mergeCell ref="A2:N2"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="K4:N4"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A7:C8"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="E6:G6"/>
-    <mergeCell ref="E7:G8"/>
-    <mergeCell ref="E9:G9"/>
-    <mergeCell ref="H6:J6"/>
-    <mergeCell ref="H7:J8"/>
-    <mergeCell ref="H9:J9"/>
-    <mergeCell ref="L6:N6"/>
-    <mergeCell ref="L7:N8"/>
-    <mergeCell ref="L9:N9"/>
-    <mergeCell ref="A11:N11"/>
-    <mergeCell ref="A25:N25"/>
+  <mergeCells count="87">
+    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="R1:X1"/>
+    <mergeCell ref="Y1:AB1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="J2:N2"/>
+    <mergeCell ref="O2:P2"/>
+    <mergeCell ref="Q2:U2"/>
+    <mergeCell ref="V2:W2"/>
+    <mergeCell ref="X2:AB2"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="H4:N4"/>
+    <mergeCell ref="H5:N5"/>
+    <mergeCell ref="H6:N6"/>
+    <mergeCell ref="O4:U4"/>
+    <mergeCell ref="O5:U5"/>
+    <mergeCell ref="O6:U6"/>
+    <mergeCell ref="V4:AB4"/>
+    <mergeCell ref="V5:AB5"/>
+    <mergeCell ref="V6:AB6"/>
+    <mergeCell ref="A23:O23"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="E24:H24"/>
+    <mergeCell ref="I24:L24"/>
+    <mergeCell ref="M24:P24"/>
+    <mergeCell ref="Q24:T24"/>
+    <mergeCell ref="U24:X24"/>
+    <mergeCell ref="Y24:AB24"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="E25:H25"/>
+    <mergeCell ref="I25:L25"/>
+    <mergeCell ref="M25:P25"/>
+    <mergeCell ref="Q25:T25"/>
+    <mergeCell ref="U25:X25"/>
+    <mergeCell ref="Y25:AB25"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="E26:H26"/>
+    <mergeCell ref="I26:L26"/>
+    <mergeCell ref="M26:P26"/>
+    <mergeCell ref="Q26:T26"/>
+    <mergeCell ref="U26:X26"/>
+    <mergeCell ref="Y26:AB26"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="E27:H27"/>
+    <mergeCell ref="I27:L27"/>
+    <mergeCell ref="M27:P27"/>
+    <mergeCell ref="Q27:T27"/>
+    <mergeCell ref="U27:X27"/>
+    <mergeCell ref="Y27:AB27"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="E28:H28"/>
+    <mergeCell ref="I28:L28"/>
+    <mergeCell ref="M28:P28"/>
+    <mergeCell ref="Q28:T28"/>
+    <mergeCell ref="U28:X28"/>
+    <mergeCell ref="Y28:AB28"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="E29:H29"/>
+    <mergeCell ref="I29:L29"/>
+    <mergeCell ref="M29:P29"/>
+    <mergeCell ref="Q29:T29"/>
+    <mergeCell ref="U29:X29"/>
+    <mergeCell ref="Y29:AB29"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="E30:H30"/>
+    <mergeCell ref="I30:L30"/>
+    <mergeCell ref="M30:P30"/>
+    <mergeCell ref="Q30:T30"/>
+    <mergeCell ref="U30:X30"/>
+    <mergeCell ref="Y30:AB30"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="E31:H31"/>
+    <mergeCell ref="I31:L31"/>
+    <mergeCell ref="M31:P31"/>
+    <mergeCell ref="Q31:T31"/>
+    <mergeCell ref="U31:X31"/>
+    <mergeCell ref="Y31:AB31"/>
+    <mergeCell ref="A32:D32"/>
+    <mergeCell ref="E32:H32"/>
+    <mergeCell ref="I32:L32"/>
+    <mergeCell ref="M32:P32"/>
+    <mergeCell ref="Q32:T32"/>
+    <mergeCell ref="U32:X32"/>
+    <mergeCell ref="Y32:AB32"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.15" right="0.15" top="0.2" bottom="0.2" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape"/>
   <headerFooter>
     <oddFooter>&amp;LPrepared by Anass ASSRI | WFM&amp;CDesign reference&amp;RConfidential</oddFooter>
   </headerFooter>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <tabColor rgb="FFD6A84B"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:AK32"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="28" width="7.42578125" style="8" customWidth="1"/>
+    <col min="30" max="37" width="0" hidden="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:37" ht="42" customHeight="1">
+      <c r="A1" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="9"/>
+      <c r="Q1" s="9"/>
+      <c r="R1" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="S1" s="10"/>
+      <c r="T1" s="10"/>
+      <c r="U1" s="10"/>
+      <c r="V1" s="10"/>
+      <c r="W1" s="10"/>
+      <c r="X1" s="10"/>
+      <c r="Y1" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z1" s="11"/>
+      <c r="AA1" s="11"/>
+      <c r="AB1" s="11"/>
+      <c r="AD1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>113</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>114</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="2" spans="1:37" ht="39" customHeight="1">
+      <c r="A2" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" s="12"/>
+      <c r="C2" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="I2" s="12"/>
+      <c r="J2" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="K2" s="13"/>
+      <c r="L2" s="13"/>
+      <c r="M2" s="13"/>
+      <c r="N2" s="13"/>
+      <c r="O2" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="P2" s="12"/>
+      <c r="Q2" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="R2" s="13"/>
+      <c r="S2" s="13"/>
+      <c r="T2" s="13"/>
+      <c r="U2" s="13"/>
+      <c r="V2" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="W2" s="12"/>
+      <c r="X2" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y2" s="13"/>
+      <c r="Z2" s="13"/>
+      <c r="AA2" s="13"/>
+      <c r="AB2" s="13"/>
+      <c r="AD2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AE2">
+        <v>420</v>
+      </c>
+      <c r="AF2">
+        <v>401</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>115</v>
+      </c>
+      <c r="AK2">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:37" s="8" customFormat="1" ht="7.5" customHeight="1">
+      <c r="AD3" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE3" s="8">
+        <v>310</v>
+      </c>
+      <c r="AF3" s="8">
+        <v>298</v>
+      </c>
+      <c r="AJ3" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="AK3" s="8">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:37" ht="5.25" customHeight="1">
+      <c r="A4" s="14"/>
+      <c r="B4" s="14"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="15"/>
+      <c r="I4" s="15"/>
+      <c r="J4" s="15"/>
+      <c r="K4" s="15"/>
+      <c r="L4" s="15"/>
+      <c r="M4" s="15"/>
+      <c r="N4" s="15"/>
+      <c r="O4" s="14"/>
+      <c r="P4" s="14"/>
+      <c r="Q4" s="14"/>
+      <c r="R4" s="14"/>
+      <c r="S4" s="14"/>
+      <c r="T4" s="14"/>
+      <c r="U4" s="14"/>
+      <c r="V4" s="15"/>
+      <c r="W4" s="15"/>
+      <c r="X4" s="15"/>
+      <c r="Y4" s="15"/>
+      <c r="Z4" s="15"/>
+      <c r="AA4" s="15"/>
+      <c r="AB4" s="15"/>
+      <c r="AD4" t="s">
+        <v>44</v>
+      </c>
+      <c r="AE4">
+        <v>245</v>
+      </c>
+      <c r="AF4">
+        <v>251</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>117</v>
+      </c>
+      <c r="AK4">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:37" ht="27" customHeight="1">
+      <c r="A5" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="B5" s="16"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="I5" s="16"/>
+      <c r="J5" s="16"/>
+      <c r="K5" s="16"/>
+      <c r="L5" s="16"/>
+      <c r="M5" s="16"/>
+      <c r="N5" s="16"/>
+      <c r="O5" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="P5" s="16"/>
+      <c r="Q5" s="16"/>
+      <c r="R5" s="16"/>
+      <c r="S5" s="16"/>
+      <c r="T5" s="16"/>
+      <c r="U5" s="16"/>
+      <c r="V5" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="W5" s="16"/>
+      <c r="X5" s="16"/>
+      <c r="Y5" s="16"/>
+      <c r="Z5" s="16"/>
+      <c r="AA5" s="16"/>
+      <c r="AB5" s="16"/>
+      <c r="AD5" t="s">
+        <v>45</v>
+      </c>
+      <c r="AE5">
+        <v>280</v>
+      </c>
+      <c r="AF5">
+        <v>260</v>
+      </c>
+      <c r="AJ5" t="s">
+        <v>118</v>
+      </c>
+      <c r="AK5">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:37" ht="72" customHeight="1">
+      <c r="A6" s="17">
+        <v>4.5</v>
+      </c>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="17">
+        <v>36.8</v>
+      </c>
+      <c r="I6" s="17"/>
+      <c r="J6" s="17"/>
+      <c r="K6" s="17"/>
+      <c r="L6" s="17"/>
+      <c r="M6" s="17"/>
+      <c r="N6" s="17"/>
+      <c r="O6" s="18">
+        <v>0.9429999999999999</v>
+      </c>
+      <c r="P6" s="18"/>
+      <c r="Q6" s="18"/>
+      <c r="R6" s="18"/>
+      <c r="S6" s="18"/>
+      <c r="T6" s="18"/>
+      <c r="U6" s="18"/>
+      <c r="V6" s="17">
+        <v>61</v>
+      </c>
+      <c r="W6" s="17"/>
+      <c r="X6" s="17"/>
+      <c r="Y6" s="17"/>
+      <c r="Z6" s="17"/>
+      <c r="AA6" s="17"/>
+      <c r="AB6" s="17"/>
+      <c r="AJ6" t="s">
+        <v>119</v>
+      </c>
+      <c r="AK6">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:37" s="8" customFormat="1" ht="7.5" customHeight="1"/>
+    <row r="8" spans="1:37" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="9" spans="1:37" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="10" spans="1:37" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="11" spans="1:37" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="12" spans="1:37" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="13" spans="1:37" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="14" spans="1:37" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="15" spans="1:37" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="16" spans="1:37" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="17" spans="1:28" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="18" spans="1:28" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="19" spans="1:28" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="20" spans="1:28" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="21" spans="1:28" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="22" spans="1:28" s="8" customFormat="1" ht="7.5" customHeight="1"/>
+    <row r="23" spans="1:28" ht="25.5" customHeight="1">
+      <c r="A23" s="19" t="s">
+        <v>121</v>
+      </c>
+      <c r="B23" s="19"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="19"/>
+      <c r="F23" s="19"/>
+      <c r="G23" s="19"/>
+      <c r="H23" s="19"/>
+      <c r="I23" s="19"/>
+      <c r="J23" s="19"/>
+      <c r="K23" s="19"/>
+      <c r="L23" s="19"/>
+      <c r="M23" s="19"/>
+      <c r="N23" s="19"/>
+      <c r="O23" s="19"/>
+    </row>
+    <row r="24" spans="1:28" ht="22.5" customHeight="1">
+      <c r="A24" s="20" t="s">
+        <v>122</v>
+      </c>
+      <c r="B24" s="20"/>
+      <c r="C24" s="20"/>
+      <c r="D24" s="20"/>
+      <c r="E24" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="F24" s="20"/>
+      <c r="G24" s="20"/>
+      <c r="H24" s="20"/>
+      <c r="I24" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="J24" s="20"/>
+      <c r="K24" s="20"/>
+      <c r="L24" s="20"/>
+      <c r="M24" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="N24" s="20"/>
+      <c r="O24" s="20"/>
+      <c r="P24" s="20"/>
+      <c r="Q24" s="20" t="s">
+        <v>125</v>
+      </c>
+      <c r="R24" s="20"/>
+      <c r="S24" s="20"/>
+      <c r="T24" s="20"/>
+      <c r="U24" s="20" t="s">
+        <v>126</v>
+      </c>
+      <c r="V24" s="20"/>
+      <c r="W24" s="20"/>
+      <c r="X24" s="20"/>
+      <c r="Y24" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="Z24" s="20"/>
+      <c r="AA24" s="20"/>
+      <c r="AB24" s="20"/>
+    </row>
+    <row r="25" spans="1:28" ht="19.5" customHeight="1">
+      <c r="A25" s="21" t="s">
+        <v>128</v>
+      </c>
+      <c r="B25" s="21"/>
+      <c r="C25" s="21"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="21" t="s">
+        <v>129</v>
+      </c>
+      <c r="F25" s="21"/>
+      <c r="G25" s="21"/>
+      <c r="H25" s="21"/>
+      <c r="I25" s="21" t="s">
+        <v>130</v>
+      </c>
+      <c r="J25" s="21"/>
+      <c r="K25" s="21"/>
+      <c r="L25" s="21"/>
+      <c r="M25" s="24">
+        <v>22.5</v>
+      </c>
+      <c r="N25" s="24"/>
+      <c r="O25" s="24"/>
+      <c r="P25" s="24"/>
+      <c r="Q25" s="24">
+        <v>18</v>
+      </c>
+      <c r="R25" s="24"/>
+      <c r="S25" s="24"/>
+      <c r="T25" s="24"/>
+      <c r="U25" s="24">
+        <v>4.5</v>
+      </c>
+      <c r="V25" s="24"/>
+      <c r="W25" s="24"/>
+      <c r="X25" s="24"/>
+      <c r="Y25" s="26" t="s">
+        <v>131</v>
+      </c>
+      <c r="Z25" s="26"/>
+      <c r="AA25" s="26"/>
+      <c r="AB25" s="26"/>
+    </row>
+    <row r="26" spans="1:28" ht="19.5" customHeight="1">
+      <c r="A26" s="21"/>
+      <c r="B26" s="21"/>
+      <c r="C26" s="21"/>
+      <c r="D26" s="21"/>
+      <c r="E26" s="21"/>
+      <c r="F26" s="21"/>
+      <c r="G26" s="21"/>
+      <c r="H26" s="21"/>
+      <c r="I26" s="21"/>
+      <c r="J26" s="21"/>
+      <c r="K26" s="21"/>
+      <c r="L26" s="21"/>
+      <c r="M26" s="24"/>
+      <c r="N26" s="24"/>
+      <c r="O26" s="24"/>
+      <c r="P26" s="24"/>
+      <c r="Q26" s="24"/>
+      <c r="R26" s="24"/>
+      <c r="S26" s="24"/>
+      <c r="T26" s="24"/>
+      <c r="U26" s="24"/>
+      <c r="V26" s="24"/>
+      <c r="W26" s="24"/>
+      <c r="X26" s="24"/>
+      <c r="Y26" s="28"/>
+      <c r="Z26" s="28"/>
+      <c r="AA26" s="28"/>
+      <c r="AB26" s="28"/>
+    </row>
+    <row r="27" spans="1:28" ht="19.5" customHeight="1">
+      <c r="A27" s="21"/>
+      <c r="B27" s="21"/>
+      <c r="C27" s="21"/>
+      <c r="D27" s="21"/>
+      <c r="E27" s="21"/>
+      <c r="F27" s="21"/>
+      <c r="G27" s="21"/>
+      <c r="H27" s="21"/>
+      <c r="I27" s="21"/>
+      <c r="J27" s="21"/>
+      <c r="K27" s="21"/>
+      <c r="L27" s="21"/>
+      <c r="M27" s="24"/>
+      <c r="N27" s="24"/>
+      <c r="O27" s="24"/>
+      <c r="P27" s="24"/>
+      <c r="Q27" s="24"/>
+      <c r="R27" s="24"/>
+      <c r="S27" s="24"/>
+      <c r="T27" s="24"/>
+      <c r="U27" s="24"/>
+      <c r="V27" s="24"/>
+      <c r="W27" s="24"/>
+      <c r="X27" s="24"/>
+      <c r="Y27" s="28"/>
+      <c r="Z27" s="28"/>
+      <c r="AA27" s="28"/>
+      <c r="AB27" s="28"/>
+    </row>
+    <row r="28" spans="1:28" ht="19.5" customHeight="1">
+      <c r="A28" s="21"/>
+      <c r="B28" s="21"/>
+      <c r="C28" s="21"/>
+      <c r="D28" s="21"/>
+      <c r="E28" s="21"/>
+      <c r="F28" s="21"/>
+      <c r="G28" s="21"/>
+      <c r="H28" s="21"/>
+      <c r="I28" s="21"/>
+      <c r="J28" s="21"/>
+      <c r="K28" s="21"/>
+      <c r="L28" s="21"/>
+      <c r="M28" s="24"/>
+      <c r="N28" s="24"/>
+      <c r="O28" s="24"/>
+      <c r="P28" s="24"/>
+      <c r="Q28" s="24"/>
+      <c r="R28" s="24"/>
+      <c r="S28" s="24"/>
+      <c r="T28" s="24"/>
+      <c r="U28" s="24"/>
+      <c r="V28" s="24"/>
+      <c r="W28" s="24"/>
+      <c r="X28" s="24"/>
+      <c r="Y28" s="28"/>
+      <c r="Z28" s="28"/>
+      <c r="AA28" s="28"/>
+      <c r="AB28" s="28"/>
+    </row>
+    <row r="29" spans="1:28" ht="19.5" customHeight="1">
+      <c r="A29" s="21"/>
+      <c r="B29" s="21"/>
+      <c r="C29" s="21"/>
+      <c r="D29" s="21"/>
+      <c r="E29" s="21"/>
+      <c r="F29" s="21"/>
+      <c r="G29" s="21"/>
+      <c r="H29" s="21"/>
+      <c r="I29" s="21"/>
+      <c r="J29" s="21"/>
+      <c r="K29" s="21"/>
+      <c r="L29" s="21"/>
+      <c r="M29" s="24"/>
+      <c r="N29" s="24"/>
+      <c r="O29" s="24"/>
+      <c r="P29" s="24"/>
+      <c r="Q29" s="24"/>
+      <c r="R29" s="24"/>
+      <c r="S29" s="24"/>
+      <c r="T29" s="24"/>
+      <c r="U29" s="24"/>
+      <c r="V29" s="24"/>
+      <c r="W29" s="24"/>
+      <c r="X29" s="24"/>
+      <c r="Y29" s="28"/>
+      <c r="Z29" s="28"/>
+      <c r="AA29" s="28"/>
+      <c r="AB29" s="28"/>
+    </row>
+    <row r="30" spans="1:28" ht="19.5" customHeight="1">
+      <c r="A30" s="21"/>
+      <c r="B30" s="21"/>
+      <c r="C30" s="21"/>
+      <c r="D30" s="21"/>
+      <c r="E30" s="21"/>
+      <c r="F30" s="21"/>
+      <c r="G30" s="21"/>
+      <c r="H30" s="21"/>
+      <c r="I30" s="21"/>
+      <c r="J30" s="21"/>
+      <c r="K30" s="21"/>
+      <c r="L30" s="21"/>
+      <c r="M30" s="24"/>
+      <c r="N30" s="24"/>
+      <c r="O30" s="24"/>
+      <c r="P30" s="24"/>
+      <c r="Q30" s="24"/>
+      <c r="R30" s="24"/>
+      <c r="S30" s="24"/>
+      <c r="T30" s="24"/>
+      <c r="U30" s="24"/>
+      <c r="V30" s="24"/>
+      <c r="W30" s="24"/>
+      <c r="X30" s="24"/>
+      <c r="Y30" s="28"/>
+      <c r="Z30" s="28"/>
+      <c r="AA30" s="28"/>
+      <c r="AB30" s="28"/>
+    </row>
+    <row r="31" spans="1:28" ht="19.5" customHeight="1">
+      <c r="A31" s="21"/>
+      <c r="B31" s="21"/>
+      <c r="C31" s="21"/>
+      <c r="D31" s="21"/>
+      <c r="E31" s="21"/>
+      <c r="F31" s="21"/>
+      <c r="G31" s="21"/>
+      <c r="H31" s="21"/>
+      <c r="I31" s="21"/>
+      <c r="J31" s="21"/>
+      <c r="K31" s="21"/>
+      <c r="L31" s="21"/>
+      <c r="M31" s="24"/>
+      <c r="N31" s="24"/>
+      <c r="O31" s="24"/>
+      <c r="P31" s="24"/>
+      <c r="Q31" s="24"/>
+      <c r="R31" s="24"/>
+      <c r="S31" s="24"/>
+      <c r="T31" s="24"/>
+      <c r="U31" s="24"/>
+      <c r="V31" s="24"/>
+      <c r="W31" s="24"/>
+      <c r="X31" s="24"/>
+      <c r="Y31" s="28"/>
+      <c r="Z31" s="28"/>
+      <c r="AA31" s="28"/>
+      <c r="AB31" s="28"/>
+    </row>
+    <row r="32" spans="1:28" ht="19.5" customHeight="1">
+      <c r="A32" s="21"/>
+      <c r="B32" s="21"/>
+      <c r="C32" s="21"/>
+      <c r="D32" s="21"/>
+      <c r="E32" s="21"/>
+      <c r="F32" s="21"/>
+      <c r="G32" s="21"/>
+      <c r="H32" s="21"/>
+      <c r="I32" s="21"/>
+      <c r="J32" s="21"/>
+      <c r="K32" s="21"/>
+      <c r="L32" s="21"/>
+      <c r="M32" s="24"/>
+      <c r="N32" s="24"/>
+      <c r="O32" s="24"/>
+      <c r="P32" s="24"/>
+      <c r="Q32" s="24"/>
+      <c r="R32" s="24"/>
+      <c r="S32" s="24"/>
+      <c r="T32" s="24"/>
+      <c r="U32" s="24"/>
+      <c r="V32" s="24"/>
+      <c r="W32" s="24"/>
+      <c r="X32" s="24"/>
+      <c r="Y32" s="28"/>
+      <c r="Z32" s="28"/>
+      <c r="AA32" s="28"/>
+      <c r="AB32" s="28"/>
+    </row>
+  </sheetData>
+  <mergeCells count="87">
+    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="R1:X1"/>
+    <mergeCell ref="Y1:AB1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="J2:N2"/>
+    <mergeCell ref="O2:P2"/>
+    <mergeCell ref="Q2:U2"/>
+    <mergeCell ref="V2:W2"/>
+    <mergeCell ref="X2:AB2"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="H4:N4"/>
+    <mergeCell ref="H5:N5"/>
+    <mergeCell ref="H6:N6"/>
+    <mergeCell ref="O4:U4"/>
+    <mergeCell ref="O5:U5"/>
+    <mergeCell ref="O6:U6"/>
+    <mergeCell ref="V4:AB4"/>
+    <mergeCell ref="V5:AB5"/>
+    <mergeCell ref="V6:AB6"/>
+    <mergeCell ref="A23:O23"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="E24:H24"/>
+    <mergeCell ref="I24:L24"/>
+    <mergeCell ref="M24:P24"/>
+    <mergeCell ref="Q24:T24"/>
+    <mergeCell ref="U24:X24"/>
+    <mergeCell ref="Y24:AB24"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="E25:H25"/>
+    <mergeCell ref="I25:L25"/>
+    <mergeCell ref="M25:P25"/>
+    <mergeCell ref="Q25:T25"/>
+    <mergeCell ref="U25:X25"/>
+    <mergeCell ref="Y25:AB25"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="E26:H26"/>
+    <mergeCell ref="I26:L26"/>
+    <mergeCell ref="M26:P26"/>
+    <mergeCell ref="Q26:T26"/>
+    <mergeCell ref="U26:X26"/>
+    <mergeCell ref="Y26:AB26"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="E27:H27"/>
+    <mergeCell ref="I27:L27"/>
+    <mergeCell ref="M27:P27"/>
+    <mergeCell ref="Q27:T27"/>
+    <mergeCell ref="U27:X27"/>
+    <mergeCell ref="Y27:AB27"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="E28:H28"/>
+    <mergeCell ref="I28:L28"/>
+    <mergeCell ref="M28:P28"/>
+    <mergeCell ref="Q28:T28"/>
+    <mergeCell ref="U28:X28"/>
+    <mergeCell ref="Y28:AB28"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="E29:H29"/>
+    <mergeCell ref="I29:L29"/>
+    <mergeCell ref="M29:P29"/>
+    <mergeCell ref="Q29:T29"/>
+    <mergeCell ref="U29:X29"/>
+    <mergeCell ref="Y29:AB29"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="E30:H30"/>
+    <mergeCell ref="I30:L30"/>
+    <mergeCell ref="M30:P30"/>
+    <mergeCell ref="Q30:T30"/>
+    <mergeCell ref="U30:X30"/>
+    <mergeCell ref="Y30:AB30"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="E31:H31"/>
+    <mergeCell ref="I31:L31"/>
+    <mergeCell ref="M31:P31"/>
+    <mergeCell ref="Q31:T31"/>
+    <mergeCell ref="U31:X31"/>
+    <mergeCell ref="Y31:AB31"/>
+    <mergeCell ref="A32:D32"/>
+    <mergeCell ref="E32:H32"/>
+    <mergeCell ref="I32:L32"/>
+    <mergeCell ref="M32:P32"/>
+    <mergeCell ref="Q32:T32"/>
+    <mergeCell ref="U32:X32"/>
+    <mergeCell ref="Y32:AB32"/>
+  </mergeCells>
+  <pageMargins left="0.15" right="0.15" top="0.2" bottom="0.2" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape"/>
+  <headerFooter>
+    <oddFooter>&amp;LPrepared by Anass ASSRI | WFM&amp;CDesign reference&amp;RConfidential</oddFooter>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <tabColor rgb="FFD6A84B"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:AL32"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="28" width="7.42578125" style="8" customWidth="1"/>
+    <col min="30" max="38" width="0" hidden="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:38" ht="42" customHeight="1">
+      <c r="A1" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="9"/>
+      <c r="Q1" s="9"/>
+      <c r="R1" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="S1" s="10"/>
+      <c r="T1" s="10"/>
+      <c r="U1" s="10"/>
+      <c r="V1" s="10"/>
+      <c r="W1" s="10"/>
+      <c r="X1" s="10"/>
+      <c r="Y1" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z1" s="11"/>
+      <c r="AA1" s="11"/>
+      <c r="AB1" s="11"/>
+      <c r="AD1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>74</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>142</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2" spans="1:38" ht="39" customHeight="1">
+      <c r="A2" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" s="12"/>
+      <c r="C2" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="I2" s="12"/>
+      <c r="J2" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="K2" s="13"/>
+      <c r="L2" s="13"/>
+      <c r="M2" s="13"/>
+      <c r="N2" s="13"/>
+      <c r="O2" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="P2" s="12"/>
+      <c r="Q2" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="R2" s="13"/>
+      <c r="S2" s="13"/>
+      <c r="T2" s="13"/>
+      <c r="U2" s="13"/>
+      <c r="V2" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="W2" s="12"/>
+      <c r="X2" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="Y2" s="13"/>
+      <c r="Z2" s="13"/>
+      <c r="AA2" s="13"/>
+      <c r="AB2" s="13"/>
+      <c r="AD2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AE2">
+        <v>18400</v>
+      </c>
+      <c r="AF2">
+        <v>17950</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AK2">
+        <v>0.899</v>
+      </c>
+      <c r="AL2">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:38" s="8" customFormat="1" ht="7.5" customHeight="1">
+      <c r="AD3" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE3" s="8">
+        <v>12150</v>
+      </c>
+      <c r="AF3" s="8">
+        <v>12600</v>
+      </c>
+      <c r="AJ3" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="AK3" s="8">
+        <v>0.858</v>
+      </c>
+      <c r="AL3" s="8">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:38" ht="5.25" customHeight="1">
+      <c r="A4" s="14"/>
+      <c r="B4" s="14"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="15"/>
+      <c r="I4" s="15"/>
+      <c r="J4" s="15"/>
+      <c r="K4" s="15"/>
+      <c r="L4" s="15"/>
+      <c r="M4" s="15"/>
+      <c r="N4" s="15"/>
+      <c r="O4" s="14"/>
+      <c r="P4" s="14"/>
+      <c r="Q4" s="14"/>
+      <c r="R4" s="14"/>
+      <c r="S4" s="14"/>
+      <c r="T4" s="14"/>
+      <c r="U4" s="14"/>
+      <c r="V4" s="15"/>
+      <c r="W4" s="15"/>
+      <c r="X4" s="15"/>
+      <c r="Y4" s="15"/>
+      <c r="Z4" s="15"/>
+      <c r="AA4" s="15"/>
+      <c r="AB4" s="15"/>
+      <c r="AD4" t="s">
+        <v>44</v>
+      </c>
+      <c r="AE4">
+        <v>8830</v>
+      </c>
+      <c r="AF4">
+        <v>8460</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK4">
+        <v>0.973</v>
+      </c>
+      <c r="AL4">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:38" ht="27" customHeight="1">
+      <c r="A5" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="B5" s="16"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="I5" s="16"/>
+      <c r="J5" s="16"/>
+      <c r="K5" s="16"/>
+      <c r="L5" s="16"/>
+      <c r="M5" s="16"/>
+      <c r="N5" s="16"/>
+      <c r="O5" s="16" t="s">
+        <v>140</v>
+      </c>
+      <c r="P5" s="16"/>
+      <c r="Q5" s="16"/>
+      <c r="R5" s="16"/>
+      <c r="S5" s="16"/>
+      <c r="T5" s="16"/>
+      <c r="U5" s="16"/>
+      <c r="V5" s="16" t="s">
+        <v>141</v>
+      </c>
+      <c r="W5" s="16"/>
+      <c r="X5" s="16"/>
+      <c r="Y5" s="16"/>
+      <c r="Z5" s="16"/>
+      <c r="AA5" s="16"/>
+      <c r="AB5" s="16"/>
+      <c r="AD5" t="s">
+        <v>45</v>
+      </c>
+      <c r="AE5">
+        <v>10240</v>
+      </c>
+      <c r="AF5">
+        <v>9980</v>
+      </c>
+      <c r="AJ5" t="s">
+        <v>45</v>
+      </c>
+      <c r="AK5">
+        <v>0.949</v>
+      </c>
+      <c r="AL5">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:38" ht="72" customHeight="1">
+      <c r="A6" s="30">
+        <v>49620</v>
+      </c>
+      <c r="B6" s="30"/>
+      <c r="C6" s="30"/>
+      <c r="D6" s="30"/>
+      <c r="E6" s="30"/>
+      <c r="F6" s="30"/>
+      <c r="G6" s="30"/>
+      <c r="H6" s="18">
+        <v>1.012</v>
+      </c>
+      <c r="I6" s="18"/>
+      <c r="J6" s="18"/>
+      <c r="K6" s="18"/>
+      <c r="L6" s="18"/>
+      <c r="M6" s="18"/>
+      <c r="N6" s="18"/>
+      <c r="O6" s="18">
+        <v>0.958</v>
+      </c>
+      <c r="P6" s="18"/>
+      <c r="Q6" s="18"/>
+      <c r="R6" s="18"/>
+      <c r="S6" s="18"/>
+      <c r="T6" s="18"/>
+      <c r="U6" s="18"/>
+      <c r="V6" s="17">
+        <v>294</v>
+      </c>
+      <c r="W6" s="17"/>
+      <c r="X6" s="17"/>
+      <c r="Y6" s="17"/>
+      <c r="Z6" s="17"/>
+      <c r="AA6" s="17"/>
+      <c r="AB6" s="17"/>
+    </row>
+    <row r="7" spans="1:38" s="8" customFormat="1" ht="7.5" customHeight="1"/>
+    <row r="8" spans="1:38" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="9" spans="1:38" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="10" spans="1:38" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="11" spans="1:38" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="12" spans="1:38" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="13" spans="1:38" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="14" spans="1:38" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="15" spans="1:38" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="16" spans="1:38" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="17" spans="1:28" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="18" spans="1:28" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="19" spans="1:28" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="20" spans="1:28" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="21" spans="1:28" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="22" spans="1:28" s="8" customFormat="1" ht="7.5" customHeight="1"/>
+    <row r="23" spans="1:28" ht="25.5" customHeight="1">
+      <c r="A23" s="19" t="s">
+        <v>143</v>
+      </c>
+      <c r="B23" s="19"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="19"/>
+      <c r="F23" s="19"/>
+      <c r="G23" s="19"/>
+      <c r="H23" s="19"/>
+      <c r="I23" s="19"/>
+      <c r="J23" s="19"/>
+      <c r="K23" s="19"/>
+      <c r="L23" s="19"/>
+      <c r="M23" s="19"/>
+      <c r="N23" s="19"/>
+      <c r="O23" s="19"/>
+    </row>
+    <row r="24" spans="1:28" ht="22.5" customHeight="1">
+      <c r="A24" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="B24" s="20"/>
+      <c r="C24" s="20"/>
+      <c r="D24" s="20"/>
+      <c r="E24" s="20" t="s">
+        <v>144</v>
+      </c>
+      <c r="F24" s="20"/>
+      <c r="G24" s="20"/>
+      <c r="H24" s="20"/>
+      <c r="I24" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="J24" s="20"/>
+      <c r="K24" s="20"/>
+      <c r="L24" s="20"/>
+      <c r="M24" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="N24" s="20"/>
+      <c r="O24" s="20"/>
+      <c r="P24" s="20"/>
+      <c r="Q24" s="20" t="s">
+        <v>147</v>
+      </c>
+      <c r="R24" s="20"/>
+      <c r="S24" s="20"/>
+      <c r="T24" s="20"/>
+      <c r="U24" s="20" t="s">
+        <v>148</v>
+      </c>
+      <c r="V24" s="20"/>
+      <c r="W24" s="20"/>
+      <c r="X24" s="20"/>
+      <c r="Y24" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="Z24" s="20"/>
+      <c r="AA24" s="20"/>
+      <c r="AB24" s="20"/>
+    </row>
+    <row r="25" spans="1:28" ht="19.5" customHeight="1">
+      <c r="A25" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="B25" s="21"/>
+      <c r="C25" s="21"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="22">
+        <v>18400</v>
+      </c>
+      <c r="F25" s="22"/>
+      <c r="G25" s="22"/>
+      <c r="H25" s="22"/>
+      <c r="I25" s="22">
+        <v>17950</v>
+      </c>
+      <c r="J25" s="22"/>
+      <c r="K25" s="22"/>
+      <c r="L25" s="22"/>
+      <c r="M25" s="23">
+        <v>1.025</v>
+      </c>
+      <c r="N25" s="23"/>
+      <c r="O25" s="23"/>
+      <c r="P25" s="23"/>
+      <c r="Q25" s="23">
+        <v>0.899</v>
+      </c>
+      <c r="R25" s="23"/>
+      <c r="S25" s="23"/>
+      <c r="T25" s="23"/>
+      <c r="U25" s="23">
+        <v>0.041</v>
+      </c>
+      <c r="V25" s="23"/>
+      <c r="W25" s="23"/>
+      <c r="X25" s="23"/>
+      <c r="Y25" s="28" t="s">
+        <v>149</v>
+      </c>
+      <c r="Z25" s="28"/>
+      <c r="AA25" s="28"/>
+      <c r="AB25" s="28"/>
+    </row>
+    <row r="26" spans="1:28" ht="19.5" customHeight="1">
+      <c r="A26" s="21"/>
+      <c r="B26" s="21"/>
+      <c r="C26" s="21"/>
+      <c r="D26" s="21"/>
+      <c r="E26" s="22"/>
+      <c r="F26" s="22"/>
+      <c r="G26" s="22"/>
+      <c r="H26" s="22"/>
+      <c r="I26" s="22"/>
+      <c r="J26" s="22"/>
+      <c r="K26" s="22"/>
+      <c r="L26" s="22"/>
+      <c r="M26" s="23"/>
+      <c r="N26" s="23"/>
+      <c r="O26" s="23"/>
+      <c r="P26" s="23"/>
+      <c r="Q26" s="23"/>
+      <c r="R26" s="23"/>
+      <c r="S26" s="23"/>
+      <c r="T26" s="23"/>
+      <c r="U26" s="23"/>
+      <c r="V26" s="23"/>
+      <c r="W26" s="23"/>
+      <c r="X26" s="23"/>
+      <c r="Y26" s="28"/>
+      <c r="Z26" s="28"/>
+      <c r="AA26" s="28"/>
+      <c r="AB26" s="28"/>
+    </row>
+    <row r="27" spans="1:28" ht="19.5" customHeight="1">
+      <c r="A27" s="21"/>
+      <c r="B27" s="21"/>
+      <c r="C27" s="21"/>
+      <c r="D27" s="21"/>
+      <c r="E27" s="22"/>
+      <c r="F27" s="22"/>
+      <c r="G27" s="22"/>
+      <c r="H27" s="22"/>
+      <c r="I27" s="22"/>
+      <c r="J27" s="22"/>
+      <c r="K27" s="22"/>
+      <c r="L27" s="22"/>
+      <c r="M27" s="23"/>
+      <c r="N27" s="23"/>
+      <c r="O27" s="23"/>
+      <c r="P27" s="23"/>
+      <c r="Q27" s="23"/>
+      <c r="R27" s="23"/>
+      <c r="S27" s="23"/>
+      <c r="T27" s="23"/>
+      <c r="U27" s="23"/>
+      <c r="V27" s="23"/>
+      <c r="W27" s="23"/>
+      <c r="X27" s="23"/>
+      <c r="Y27" s="28"/>
+      <c r="Z27" s="28"/>
+      <c r="AA27" s="28"/>
+      <c r="AB27" s="28"/>
+    </row>
+    <row r="28" spans="1:28" ht="19.5" customHeight="1">
+      <c r="A28" s="21"/>
+      <c r="B28" s="21"/>
+      <c r="C28" s="21"/>
+      <c r="D28" s="21"/>
+      <c r="E28" s="22"/>
+      <c r="F28" s="22"/>
+      <c r="G28" s="22"/>
+      <c r="H28" s="22"/>
+      <c r="I28" s="22"/>
+      <c r="J28" s="22"/>
+      <c r="K28" s="22"/>
+      <c r="L28" s="22"/>
+      <c r="M28" s="23"/>
+      <c r="N28" s="23"/>
+      <c r="O28" s="23"/>
+      <c r="P28" s="23"/>
+      <c r="Q28" s="23"/>
+      <c r="R28" s="23"/>
+      <c r="S28" s="23"/>
+      <c r="T28" s="23"/>
+      <c r="U28" s="23"/>
+      <c r="V28" s="23"/>
+      <c r="W28" s="23"/>
+      <c r="X28" s="23"/>
+      <c r="Y28" s="28"/>
+      <c r="Z28" s="28"/>
+      <c r="AA28" s="28"/>
+      <c r="AB28" s="28"/>
+    </row>
+    <row r="29" spans="1:28" ht="19.5" customHeight="1">
+      <c r="A29" s="21"/>
+      <c r="B29" s="21"/>
+      <c r="C29" s="21"/>
+      <c r="D29" s="21"/>
+      <c r="E29" s="22"/>
+      <c r="F29" s="22"/>
+      <c r="G29" s="22"/>
+      <c r="H29" s="22"/>
+      <c r="I29" s="22"/>
+      <c r="J29" s="22"/>
+      <c r="K29" s="22"/>
+      <c r="L29" s="22"/>
+      <c r="M29" s="23"/>
+      <c r="N29" s="23"/>
+      <c r="O29" s="23"/>
+      <c r="P29" s="23"/>
+      <c r="Q29" s="23"/>
+      <c r="R29" s="23"/>
+      <c r="S29" s="23"/>
+      <c r="T29" s="23"/>
+      <c r="U29" s="23"/>
+      <c r="V29" s="23"/>
+      <c r="W29" s="23"/>
+      <c r="X29" s="23"/>
+      <c r="Y29" s="28"/>
+      <c r="Z29" s="28"/>
+      <c r="AA29" s="28"/>
+      <c r="AB29" s="28"/>
+    </row>
+    <row r="30" spans="1:28" ht="19.5" customHeight="1">
+      <c r="A30" s="21"/>
+      <c r="B30" s="21"/>
+      <c r="C30" s="21"/>
+      <c r="D30" s="21"/>
+      <c r="E30" s="22"/>
+      <c r="F30" s="22"/>
+      <c r="G30" s="22"/>
+      <c r="H30" s="22"/>
+      <c r="I30" s="22"/>
+      <c r="J30" s="22"/>
+      <c r="K30" s="22"/>
+      <c r="L30" s="22"/>
+      <c r="M30" s="23"/>
+      <c r="N30" s="23"/>
+      <c r="O30" s="23"/>
+      <c r="P30" s="23"/>
+      <c r="Q30" s="23"/>
+      <c r="R30" s="23"/>
+      <c r="S30" s="23"/>
+      <c r="T30" s="23"/>
+      <c r="U30" s="23"/>
+      <c r="V30" s="23"/>
+      <c r="W30" s="23"/>
+      <c r="X30" s="23"/>
+      <c r="Y30" s="28"/>
+      <c r="Z30" s="28"/>
+      <c r="AA30" s="28"/>
+      <c r="AB30" s="28"/>
+    </row>
+    <row r="31" spans="1:28" ht="19.5" customHeight="1">
+      <c r="A31" s="21"/>
+      <c r="B31" s="21"/>
+      <c r="C31" s="21"/>
+      <c r="D31" s="21"/>
+      <c r="E31" s="22"/>
+      <c r="F31" s="22"/>
+      <c r="G31" s="22"/>
+      <c r="H31" s="22"/>
+      <c r="I31" s="22"/>
+      <c r="J31" s="22"/>
+      <c r="K31" s="22"/>
+      <c r="L31" s="22"/>
+      <c r="M31" s="23"/>
+      <c r="N31" s="23"/>
+      <c r="O31" s="23"/>
+      <c r="P31" s="23"/>
+      <c r="Q31" s="23"/>
+      <c r="R31" s="23"/>
+      <c r="S31" s="23"/>
+      <c r="T31" s="23"/>
+      <c r="U31" s="23"/>
+      <c r="V31" s="23"/>
+      <c r="W31" s="23"/>
+      <c r="X31" s="23"/>
+      <c r="Y31" s="28"/>
+      <c r="Z31" s="28"/>
+      <c r="AA31" s="28"/>
+      <c r="AB31" s="28"/>
+    </row>
+    <row r="32" spans="1:28" ht="19.5" customHeight="1">
+      <c r="A32" s="21"/>
+      <c r="B32" s="21"/>
+      <c r="C32" s="21"/>
+      <c r="D32" s="21"/>
+      <c r="E32" s="22"/>
+      <c r="F32" s="22"/>
+      <c r="G32" s="22"/>
+      <c r="H32" s="22"/>
+      <c r="I32" s="22"/>
+      <c r="J32" s="22"/>
+      <c r="K32" s="22"/>
+      <c r="L32" s="22"/>
+      <c r="M32" s="23"/>
+      <c r="N32" s="23"/>
+      <c r="O32" s="23"/>
+      <c r="P32" s="23"/>
+      <c r="Q32" s="23"/>
+      <c r="R32" s="23"/>
+      <c r="S32" s="23"/>
+      <c r="T32" s="23"/>
+      <c r="U32" s="23"/>
+      <c r="V32" s="23"/>
+      <c r="W32" s="23"/>
+      <c r="X32" s="23"/>
+      <c r="Y32" s="28"/>
+      <c r="Z32" s="28"/>
+      <c r="AA32" s="28"/>
+      <c r="AB32" s="28"/>
+    </row>
+  </sheetData>
+  <mergeCells count="87">
+    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="R1:X1"/>
+    <mergeCell ref="Y1:AB1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="J2:N2"/>
+    <mergeCell ref="O2:P2"/>
+    <mergeCell ref="Q2:U2"/>
+    <mergeCell ref="V2:W2"/>
+    <mergeCell ref="X2:AB2"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="H4:N4"/>
+    <mergeCell ref="H5:N5"/>
+    <mergeCell ref="H6:N6"/>
+    <mergeCell ref="O4:U4"/>
+    <mergeCell ref="O5:U5"/>
+    <mergeCell ref="O6:U6"/>
+    <mergeCell ref="V4:AB4"/>
+    <mergeCell ref="V5:AB5"/>
+    <mergeCell ref="V6:AB6"/>
+    <mergeCell ref="A23:O23"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="E24:H24"/>
+    <mergeCell ref="I24:L24"/>
+    <mergeCell ref="M24:P24"/>
+    <mergeCell ref="Q24:T24"/>
+    <mergeCell ref="U24:X24"/>
+    <mergeCell ref="Y24:AB24"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="E25:H25"/>
+    <mergeCell ref="I25:L25"/>
+    <mergeCell ref="M25:P25"/>
+    <mergeCell ref="Q25:T25"/>
+    <mergeCell ref="U25:X25"/>
+    <mergeCell ref="Y25:AB25"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="E26:H26"/>
+    <mergeCell ref="I26:L26"/>
+    <mergeCell ref="M26:P26"/>
+    <mergeCell ref="Q26:T26"/>
+    <mergeCell ref="U26:X26"/>
+    <mergeCell ref="Y26:AB26"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="E27:H27"/>
+    <mergeCell ref="I27:L27"/>
+    <mergeCell ref="M27:P27"/>
+    <mergeCell ref="Q27:T27"/>
+    <mergeCell ref="U27:X27"/>
+    <mergeCell ref="Y27:AB27"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="E28:H28"/>
+    <mergeCell ref="I28:L28"/>
+    <mergeCell ref="M28:P28"/>
+    <mergeCell ref="Q28:T28"/>
+    <mergeCell ref="U28:X28"/>
+    <mergeCell ref="Y28:AB28"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="E29:H29"/>
+    <mergeCell ref="I29:L29"/>
+    <mergeCell ref="M29:P29"/>
+    <mergeCell ref="Q29:T29"/>
+    <mergeCell ref="U29:X29"/>
+    <mergeCell ref="Y29:AB29"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="E30:H30"/>
+    <mergeCell ref="I30:L30"/>
+    <mergeCell ref="M30:P30"/>
+    <mergeCell ref="Q30:T30"/>
+    <mergeCell ref="U30:X30"/>
+    <mergeCell ref="Y30:AB30"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="E31:H31"/>
+    <mergeCell ref="I31:L31"/>
+    <mergeCell ref="M31:P31"/>
+    <mergeCell ref="Q31:T31"/>
+    <mergeCell ref="U31:X31"/>
+    <mergeCell ref="Y31:AB31"/>
+    <mergeCell ref="A32:D32"/>
+    <mergeCell ref="E32:H32"/>
+    <mergeCell ref="I32:L32"/>
+    <mergeCell ref="M32:P32"/>
+    <mergeCell ref="Q32:T32"/>
+    <mergeCell ref="U32:X32"/>
+    <mergeCell ref="Y32:AB32"/>
+  </mergeCells>
+  <pageMargins left="0.15" right="0.15" top="0.2" bottom="0.2" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape"/>
+  <headerFooter>
+    <oddFooter>&amp;LPrepared by Anass ASSRI | WFM&amp;CDesign reference&amp;RConfidential</oddFooter>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <tabColor rgb="FFD6A84B"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:AL32"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="28" width="7.42578125" style="8" customWidth="1"/>
+    <col min="30" max="38" width="0" hidden="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:38" ht="42" customHeight="1">
+      <c r="A1" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="9"/>
+      <c r="Q1" s="9"/>
+      <c r="R1" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="S1" s="10"/>
+      <c r="T1" s="10"/>
+      <c r="U1" s="10"/>
+      <c r="V1" s="10"/>
+      <c r="W1" s="10"/>
+      <c r="X1" s="10"/>
+      <c r="Y1" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z1" s="11"/>
+      <c r="AA1" s="11"/>
+      <c r="AB1" s="11"/>
+      <c r="AD1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>155</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>156</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>155</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="2" spans="1:38" ht="39" customHeight="1">
+      <c r="A2" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" s="12"/>
+      <c r="C2" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="I2" s="12"/>
+      <c r="J2" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="K2" s="13"/>
+      <c r="L2" s="13"/>
+      <c r="M2" s="13"/>
+      <c r="N2" s="13"/>
+      <c r="O2" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="P2" s="12"/>
+      <c r="Q2" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="R2" s="13"/>
+      <c r="S2" s="13"/>
+      <c r="T2" s="13"/>
+      <c r="U2" s="13"/>
+      <c r="V2" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="W2" s="12"/>
+      <c r="X2" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y2" s="13"/>
+      <c r="Z2" s="13"/>
+      <c r="AA2" s="13"/>
+      <c r="AB2" s="13"/>
+      <c r="AD2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AE2">
+        <v>0.041</v>
+      </c>
+      <c r="AF2">
+        <v>0.118</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AK2">
+        <v>31</v>
+      </c>
+      <c r="AL2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="3" spans="1:38" s="8" customFormat="1" ht="7.5" customHeight="1">
+      <c r="AD3" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE3" s="8">
+        <v>0.052</v>
+      </c>
+      <c r="AF3" s="8">
+        <v>0.129</v>
+      </c>
+      <c r="AJ3" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="AK3" s="8">
+        <v>27</v>
+      </c>
+      <c r="AL3" s="8">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="4" spans="1:38" ht="5.25" customHeight="1">
+      <c r="A4" s="14"/>
+      <c r="B4" s="14"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="15"/>
+      <c r="I4" s="15"/>
+      <c r="J4" s="15"/>
+      <c r="K4" s="15"/>
+      <c r="L4" s="15"/>
+      <c r="M4" s="15"/>
+      <c r="N4" s="15"/>
+      <c r="O4" s="14"/>
+      <c r="P4" s="14"/>
+      <c r="Q4" s="14"/>
+      <c r="R4" s="14"/>
+      <c r="S4" s="14"/>
+      <c r="T4" s="14"/>
+      <c r="U4" s="14"/>
+      <c r="V4" s="15"/>
+      <c r="W4" s="15"/>
+      <c r="X4" s="15"/>
+      <c r="Y4" s="15"/>
+      <c r="Z4" s="15"/>
+      <c r="AA4" s="15"/>
+      <c r="AB4" s="15"/>
+      <c r="AD4" t="s">
+        <v>44</v>
+      </c>
+      <c r="AE4">
+        <v>0.033</v>
+      </c>
+      <c r="AF4">
+        <v>0.104</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>50</v>
+      </c>
+      <c r="AK4">
+        <v>38</v>
+      </c>
+      <c r="AL4">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="5" spans="1:38" ht="27" customHeight="1">
+      <c r="A5" s="16" t="s">
+        <v>151</v>
+      </c>
+      <c r="B5" s="16"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="16" t="s">
+        <v>152</v>
+      </c>
+      <c r="I5" s="16"/>
+      <c r="J5" s="16"/>
+      <c r="K5" s="16"/>
+      <c r="L5" s="16"/>
+      <c r="M5" s="16"/>
+      <c r="N5" s="16"/>
+      <c r="O5" s="16" t="s">
+        <v>153</v>
+      </c>
+      <c r="P5" s="16"/>
+      <c r="Q5" s="16"/>
+      <c r="R5" s="16"/>
+      <c r="S5" s="16"/>
+      <c r="T5" s="16"/>
+      <c r="U5" s="16"/>
+      <c r="V5" s="16" t="s">
+        <v>154</v>
+      </c>
+      <c r="W5" s="16"/>
+      <c r="X5" s="16"/>
+      <c r="Y5" s="16"/>
+      <c r="Z5" s="16"/>
+      <c r="AA5" s="16"/>
+      <c r="AB5" s="16"/>
+      <c r="AD5" t="s">
+        <v>45</v>
+      </c>
+      <c r="AE5">
+        <v>0.046</v>
+      </c>
+      <c r="AF5">
+        <v>0.123</v>
+      </c>
+      <c r="AJ5" t="s">
+        <v>51</v>
+      </c>
+      <c r="AK5">
+        <v>42</v>
+      </c>
+      <c r="AL5">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="6" spans="1:38" ht="72" customHeight="1">
+      <c r="A6" s="18">
+        <v>0.043</v>
+      </c>
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="18"/>
+      <c r="H6" s="18">
+        <v>0.118</v>
+      </c>
+      <c r="I6" s="18"/>
+      <c r="J6" s="18"/>
+      <c r="K6" s="18"/>
+      <c r="L6" s="18"/>
+      <c r="M6" s="18"/>
+      <c r="N6" s="18"/>
+      <c r="O6" s="18">
+        <v>0.988</v>
+      </c>
+      <c r="P6" s="18"/>
+      <c r="Q6" s="18"/>
+      <c r="R6" s="18"/>
+      <c r="S6" s="18"/>
+      <c r="T6" s="18"/>
+      <c r="U6" s="18"/>
+      <c r="V6" s="30">
+        <v>7</v>
+      </c>
+      <c r="W6" s="30"/>
+      <c r="X6" s="30"/>
+      <c r="Y6" s="30"/>
+      <c r="Z6" s="30"/>
+      <c r="AA6" s="30"/>
+      <c r="AB6" s="30"/>
+      <c r="AJ6" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK6">
+        <v>35</v>
+      </c>
+      <c r="AL6">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="7" spans="1:38" s="8" customFormat="1" ht="7.5" customHeight="1"/>
+    <row r="8" spans="1:38" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="9" spans="1:38" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="10" spans="1:38" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="11" spans="1:38" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="12" spans="1:38" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="13" spans="1:38" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="14" spans="1:38" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="15" spans="1:38" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="16" spans="1:38" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="17" spans="1:28" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="18" spans="1:28" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="19" spans="1:28" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="20" spans="1:28" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="21" spans="1:28" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="22" spans="1:28" s="8" customFormat="1" ht="7.5" customHeight="1"/>
+    <row r="23" spans="1:28" ht="25.5" customHeight="1">
+      <c r="A23" s="19" t="s">
+        <v>157</v>
+      </c>
+      <c r="B23" s="19"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="19"/>
+      <c r="F23" s="19"/>
+      <c r="G23" s="19"/>
+      <c r="H23" s="19"/>
+      <c r="I23" s="19"/>
+      <c r="J23" s="19"/>
+      <c r="K23" s="19"/>
+      <c r="L23" s="19"/>
+      <c r="M23" s="19"/>
+      <c r="N23" s="19"/>
+      <c r="O23" s="19"/>
+    </row>
+    <row r="24" spans="1:28" ht="22.5" customHeight="1">
+      <c r="A24" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="B24" s="20"/>
+      <c r="C24" s="20"/>
+      <c r="D24" s="20"/>
+      <c r="E24" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="F24" s="20"/>
+      <c r="G24" s="20"/>
+      <c r="H24" s="20"/>
+      <c r="I24" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="J24" s="20"/>
+      <c r="K24" s="20"/>
+      <c r="L24" s="20"/>
+      <c r="M24" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="N24" s="20"/>
+      <c r="O24" s="20"/>
+      <c r="P24" s="20"/>
+      <c r="Q24" s="20" t="s">
+        <v>158</v>
+      </c>
+      <c r="R24" s="20"/>
+      <c r="S24" s="20"/>
+      <c r="T24" s="20"/>
+      <c r="U24" s="20" t="s">
+        <v>159</v>
+      </c>
+      <c r="V24" s="20"/>
+      <c r="W24" s="20"/>
+      <c r="X24" s="20"/>
+      <c r="Y24" s="20" t="s">
+        <v>160</v>
+      </c>
+      <c r="Z24" s="20"/>
+      <c r="AA24" s="20"/>
+      <c r="AB24" s="20"/>
+    </row>
+    <row r="25" spans="1:28" ht="19.5" customHeight="1">
+      <c r="A25" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="B25" s="21"/>
+      <c r="C25" s="21"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="21" t="s">
+        <v>162</v>
+      </c>
+      <c r="F25" s="21"/>
+      <c r="G25" s="21"/>
+      <c r="H25" s="21"/>
+      <c r="I25" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="J25" s="21"/>
+      <c r="K25" s="21"/>
+      <c r="L25" s="21"/>
+      <c r="M25" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="N25" s="21"/>
+      <c r="O25" s="21"/>
+      <c r="P25" s="21"/>
+      <c r="Q25" s="21" t="s">
+        <v>163</v>
+      </c>
+      <c r="R25" s="21"/>
+      <c r="S25" s="21"/>
+      <c r="T25" s="21"/>
+      <c r="U25" s="24">
+        <v>8</v>
+      </c>
+      <c r="V25" s="24"/>
+      <c r="W25" s="24"/>
+      <c r="X25" s="24"/>
+      <c r="Y25" s="26" t="s">
+        <v>164</v>
+      </c>
+      <c r="Z25" s="26"/>
+      <c r="AA25" s="26"/>
+      <c r="AB25" s="26"/>
+    </row>
+    <row r="26" spans="1:28" ht="19.5" customHeight="1">
+      <c r="A26" s="21"/>
+      <c r="B26" s="21"/>
+      <c r="C26" s="21"/>
+      <c r="D26" s="21"/>
+      <c r="E26" s="21"/>
+      <c r="F26" s="21"/>
+      <c r="G26" s="21"/>
+      <c r="H26" s="21"/>
+      <c r="I26" s="21"/>
+      <c r="J26" s="21"/>
+      <c r="K26" s="21"/>
+      <c r="L26" s="21"/>
+      <c r="M26" s="21"/>
+      <c r="N26" s="21"/>
+      <c r="O26" s="21"/>
+      <c r="P26" s="21"/>
+      <c r="Q26" s="21"/>
+      <c r="R26" s="21"/>
+      <c r="S26" s="21"/>
+      <c r="T26" s="21"/>
+      <c r="U26" s="24"/>
+      <c r="V26" s="24"/>
+      <c r="W26" s="24"/>
+      <c r="X26" s="24"/>
+      <c r="Y26" s="28"/>
+      <c r="Z26" s="28"/>
+      <c r="AA26" s="28"/>
+      <c r="AB26" s="28"/>
+    </row>
+    <row r="27" spans="1:28" ht="19.5" customHeight="1">
+      <c r="A27" s="21"/>
+      <c r="B27" s="21"/>
+      <c r="C27" s="21"/>
+      <c r="D27" s="21"/>
+      <c r="E27" s="21"/>
+      <c r="F27" s="21"/>
+      <c r="G27" s="21"/>
+      <c r="H27" s="21"/>
+      <c r="I27" s="21"/>
+      <c r="J27" s="21"/>
+      <c r="K27" s="21"/>
+      <c r="L27" s="21"/>
+      <c r="M27" s="21"/>
+      <c r="N27" s="21"/>
+      <c r="O27" s="21"/>
+      <c r="P27" s="21"/>
+      <c r="Q27" s="21"/>
+      <c r="R27" s="21"/>
+      <c r="S27" s="21"/>
+      <c r="T27" s="21"/>
+      <c r="U27" s="24"/>
+      <c r="V27" s="24"/>
+      <c r="W27" s="24"/>
+      <c r="X27" s="24"/>
+      <c r="Y27" s="28"/>
+      <c r="Z27" s="28"/>
+      <c r="AA27" s="28"/>
+      <c r="AB27" s="28"/>
+    </row>
+    <row r="28" spans="1:28" ht="19.5" customHeight="1">
+      <c r="A28" s="21"/>
+      <c r="B28" s="21"/>
+      <c r="C28" s="21"/>
+      <c r="D28" s="21"/>
+      <c r="E28" s="21"/>
+      <c r="F28" s="21"/>
+      <c r="G28" s="21"/>
+      <c r="H28" s="21"/>
+      <c r="I28" s="21"/>
+      <c r="J28" s="21"/>
+      <c r="K28" s="21"/>
+      <c r="L28" s="21"/>
+      <c r="M28" s="21"/>
+      <c r="N28" s="21"/>
+      <c r="O28" s="21"/>
+      <c r="P28" s="21"/>
+      <c r="Q28" s="21"/>
+      <c r="R28" s="21"/>
+      <c r="S28" s="21"/>
+      <c r="T28" s="21"/>
+      <c r="U28" s="24"/>
+      <c r="V28" s="24"/>
+      <c r="W28" s="24"/>
+      <c r="X28" s="24"/>
+      <c r="Y28" s="28"/>
+      <c r="Z28" s="28"/>
+      <c r="AA28" s="28"/>
+      <c r="AB28" s="28"/>
+    </row>
+    <row r="29" spans="1:28" ht="19.5" customHeight="1">
+      <c r="A29" s="21"/>
+      <c r="B29" s="21"/>
+      <c r="C29" s="21"/>
+      <c r="D29" s="21"/>
+      <c r="E29" s="21"/>
+      <c r="F29" s="21"/>
+      <c r="G29" s="21"/>
+      <c r="H29" s="21"/>
+      <c r="I29" s="21"/>
+      <c r="J29" s="21"/>
+      <c r="K29" s="21"/>
+      <c r="L29" s="21"/>
+      <c r="M29" s="21"/>
+      <c r="N29" s="21"/>
+      <c r="O29" s="21"/>
+      <c r="P29" s="21"/>
+      <c r="Q29" s="21"/>
+      <c r="R29" s="21"/>
+      <c r="S29" s="21"/>
+      <c r="T29" s="21"/>
+      <c r="U29" s="24"/>
+      <c r="V29" s="24"/>
+      <c r="W29" s="24"/>
+      <c r="X29" s="24"/>
+      <c r="Y29" s="28"/>
+      <c r="Z29" s="28"/>
+      <c r="AA29" s="28"/>
+      <c r="AB29" s="28"/>
+    </row>
+    <row r="30" spans="1:28" ht="19.5" customHeight="1">
+      <c r="A30" s="21"/>
+      <c r="B30" s="21"/>
+      <c r="C30" s="21"/>
+      <c r="D30" s="21"/>
+      <c r="E30" s="21"/>
+      <c r="F30" s="21"/>
+      <c r="G30" s="21"/>
+      <c r="H30" s="21"/>
+      <c r="I30" s="21"/>
+      <c r="J30" s="21"/>
+      <c r="K30" s="21"/>
+      <c r="L30" s="21"/>
+      <c r="M30" s="21"/>
+      <c r="N30" s="21"/>
+      <c r="O30" s="21"/>
+      <c r="P30" s="21"/>
+      <c r="Q30" s="21"/>
+      <c r="R30" s="21"/>
+      <c r="S30" s="21"/>
+      <c r="T30" s="21"/>
+      <c r="U30" s="24"/>
+      <c r="V30" s="24"/>
+      <c r="W30" s="24"/>
+      <c r="X30" s="24"/>
+      <c r="Y30" s="28"/>
+      <c r="Z30" s="28"/>
+      <c r="AA30" s="28"/>
+      <c r="AB30" s="28"/>
+    </row>
+    <row r="31" spans="1:28" ht="19.5" customHeight="1">
+      <c r="A31" s="21"/>
+      <c r="B31" s="21"/>
+      <c r="C31" s="21"/>
+      <c r="D31" s="21"/>
+      <c r="E31" s="21"/>
+      <c r="F31" s="21"/>
+      <c r="G31" s="21"/>
+      <c r="H31" s="21"/>
+      <c r="I31" s="21"/>
+      <c r="J31" s="21"/>
+      <c r="K31" s="21"/>
+      <c r="L31" s="21"/>
+      <c r="M31" s="21"/>
+      <c r="N31" s="21"/>
+      <c r="O31" s="21"/>
+      <c r="P31" s="21"/>
+      <c r="Q31" s="21"/>
+      <c r="R31" s="21"/>
+      <c r="S31" s="21"/>
+      <c r="T31" s="21"/>
+      <c r="U31" s="24"/>
+      <c r="V31" s="24"/>
+      <c r="W31" s="24"/>
+      <c r="X31" s="24"/>
+      <c r="Y31" s="28"/>
+      <c r="Z31" s="28"/>
+      <c r="AA31" s="28"/>
+      <c r="AB31" s="28"/>
+    </row>
+    <row r="32" spans="1:28" ht="19.5" customHeight="1">
+      <c r="A32" s="21"/>
+      <c r="B32" s="21"/>
+      <c r="C32" s="21"/>
+      <c r="D32" s="21"/>
+      <c r="E32" s="21"/>
+      <c r="F32" s="21"/>
+      <c r="G32" s="21"/>
+      <c r="H32" s="21"/>
+      <c r="I32" s="21"/>
+      <c r="J32" s="21"/>
+      <c r="K32" s="21"/>
+      <c r="L32" s="21"/>
+      <c r="M32" s="21"/>
+      <c r="N32" s="21"/>
+      <c r="O32" s="21"/>
+      <c r="P32" s="21"/>
+      <c r="Q32" s="21"/>
+      <c r="R32" s="21"/>
+      <c r="S32" s="21"/>
+      <c r="T32" s="21"/>
+      <c r="U32" s="24"/>
+      <c r="V32" s="24"/>
+      <c r="W32" s="24"/>
+      <c r="X32" s="24"/>
+      <c r="Y32" s="28"/>
+      <c r="Z32" s="28"/>
+      <c r="AA32" s="28"/>
+      <c r="AB32" s="28"/>
+    </row>
+  </sheetData>
+  <mergeCells count="87">
+    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="R1:X1"/>
+    <mergeCell ref="Y1:AB1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="J2:N2"/>
+    <mergeCell ref="O2:P2"/>
+    <mergeCell ref="Q2:U2"/>
+    <mergeCell ref="V2:W2"/>
+    <mergeCell ref="X2:AB2"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="H4:N4"/>
+    <mergeCell ref="H5:N5"/>
+    <mergeCell ref="H6:N6"/>
+    <mergeCell ref="O4:U4"/>
+    <mergeCell ref="O5:U5"/>
+    <mergeCell ref="O6:U6"/>
+    <mergeCell ref="V4:AB4"/>
+    <mergeCell ref="V5:AB5"/>
+    <mergeCell ref="V6:AB6"/>
+    <mergeCell ref="A23:O23"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="E24:H24"/>
+    <mergeCell ref="I24:L24"/>
+    <mergeCell ref="M24:P24"/>
+    <mergeCell ref="Q24:T24"/>
+    <mergeCell ref="U24:X24"/>
+    <mergeCell ref="Y24:AB24"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="E25:H25"/>
+    <mergeCell ref="I25:L25"/>
+    <mergeCell ref="M25:P25"/>
+    <mergeCell ref="Q25:T25"/>
+    <mergeCell ref="U25:X25"/>
+    <mergeCell ref="Y25:AB25"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="E26:H26"/>
+    <mergeCell ref="I26:L26"/>
+    <mergeCell ref="M26:P26"/>
+    <mergeCell ref="Q26:T26"/>
+    <mergeCell ref="U26:X26"/>
+    <mergeCell ref="Y26:AB26"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="E27:H27"/>
+    <mergeCell ref="I27:L27"/>
+    <mergeCell ref="M27:P27"/>
+    <mergeCell ref="Q27:T27"/>
+    <mergeCell ref="U27:X27"/>
+    <mergeCell ref="Y27:AB27"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="E28:H28"/>
+    <mergeCell ref="I28:L28"/>
+    <mergeCell ref="M28:P28"/>
+    <mergeCell ref="Q28:T28"/>
+    <mergeCell ref="U28:X28"/>
+    <mergeCell ref="Y28:AB28"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="E29:H29"/>
+    <mergeCell ref="I29:L29"/>
+    <mergeCell ref="M29:P29"/>
+    <mergeCell ref="Q29:T29"/>
+    <mergeCell ref="U29:X29"/>
+    <mergeCell ref="Y29:AB29"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="E30:H30"/>
+    <mergeCell ref="I30:L30"/>
+    <mergeCell ref="M30:P30"/>
+    <mergeCell ref="Q30:T30"/>
+    <mergeCell ref="U30:X30"/>
+    <mergeCell ref="Y30:AB30"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="E31:H31"/>
+    <mergeCell ref="I31:L31"/>
+    <mergeCell ref="M31:P31"/>
+    <mergeCell ref="Q31:T31"/>
+    <mergeCell ref="U31:X31"/>
+    <mergeCell ref="Y31:AB31"/>
+    <mergeCell ref="A32:D32"/>
+    <mergeCell ref="E32:H32"/>
+    <mergeCell ref="I32:L32"/>
+    <mergeCell ref="M32:P32"/>
+    <mergeCell ref="Q32:T32"/>
+    <mergeCell ref="U32:X32"/>
+    <mergeCell ref="Y32:AB32"/>
+  </mergeCells>
+  <pageMargins left="0.15" right="0.15" top="0.2" bottom="0.2" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape"/>
+  <headerFooter>
+    <oddFooter>&amp;LPrepared by Anass ASSRI | WFM&amp;CDesign reference&amp;RConfidential</oddFooter>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <tabColor rgb="FFD6A84B"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:AK32"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="28" width="7.42578125" style="8" customWidth="1"/>
+    <col min="30" max="37" width="0" hidden="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:37" ht="42" customHeight="1">
+      <c r="A1" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="9"/>
+      <c r="Q1" s="9"/>
+      <c r="R1" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="S1" s="10"/>
+      <c r="T1" s="10"/>
+      <c r="U1" s="10"/>
+      <c r="V1" s="10"/>
+      <c r="W1" s="10"/>
+      <c r="X1" s="10"/>
+      <c r="Y1" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z1" s="11"/>
+      <c r="AA1" s="11"/>
+      <c r="AB1" s="11"/>
+      <c r="AD1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>175</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="2" spans="1:37" ht="39" customHeight="1">
+      <c r="A2" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" s="12"/>
+      <c r="C2" s="13" t="s">
+        <v>166</v>
+      </c>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="I2" s="12"/>
+      <c r="J2" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="K2" s="13"/>
+      <c r="L2" s="13"/>
+      <c r="M2" s="13"/>
+      <c r="N2" s="13"/>
+      <c r="O2" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="P2" s="12"/>
+      <c r="Q2" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="R2" s="13"/>
+      <c r="S2" s="13"/>
+      <c r="T2" s="13"/>
+      <c r="U2" s="13"/>
+      <c r="V2" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="W2" s="12"/>
+      <c r="X2" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y2" s="13"/>
+      <c r="Z2" s="13"/>
+      <c r="AA2" s="13"/>
+      <c r="AB2" s="13"/>
+      <c r="AD2" t="s">
+        <v>173</v>
+      </c>
+      <c r="AE2">
+        <v>92100</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>176</v>
+      </c>
+      <c r="AK2">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="3" spans="1:37" s="8" customFormat="1" ht="7.5" customHeight="1">
+      <c r="AD3" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="AE3" s="8">
+        <v>54120</v>
+      </c>
+      <c r="AJ3" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="AK3" s="8">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="4" spans="1:37" ht="5.25" customHeight="1">
+      <c r="A4" s="14"/>
+      <c r="B4" s="14"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="15"/>
+      <c r="I4" s="15"/>
+      <c r="J4" s="15"/>
+      <c r="K4" s="15"/>
+      <c r="L4" s="15"/>
+      <c r="M4" s="15"/>
+      <c r="N4" s="15"/>
+      <c r="O4" s="14"/>
+      <c r="P4" s="14"/>
+      <c r="Q4" s="14"/>
+      <c r="R4" s="14"/>
+      <c r="S4" s="14"/>
+      <c r="T4" s="14"/>
+      <c r="U4" s="14"/>
+      <c r="V4" s="15"/>
+      <c r="W4" s="15"/>
+      <c r="X4" s="15"/>
+      <c r="Y4" s="15"/>
+      <c r="Z4" s="15"/>
+      <c r="AA4" s="15"/>
+      <c r="AB4" s="15"/>
+      <c r="AD4" t="s">
+        <v>45</v>
+      </c>
+      <c r="AE4">
+        <v>38300</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>178</v>
+      </c>
+      <c r="AK4">
+        <v>0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:37" ht="27" customHeight="1">
+      <c r="A5" s="16" t="s">
+        <v>169</v>
+      </c>
+      <c r="B5" s="16"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="16" t="s">
+        <v>170</v>
+      </c>
+      <c r="I5" s="16"/>
+      <c r="J5" s="16"/>
+      <c r="K5" s="16"/>
+      <c r="L5" s="16"/>
+      <c r="M5" s="16"/>
+      <c r="N5" s="16"/>
+      <c r="O5" s="16" t="s">
+        <v>171</v>
+      </c>
+      <c r="P5" s="16"/>
+      <c r="Q5" s="16"/>
+      <c r="R5" s="16"/>
+      <c r="S5" s="16"/>
+      <c r="T5" s="16"/>
+      <c r="U5" s="16"/>
+      <c r="V5" s="16" t="s">
+        <v>172</v>
+      </c>
+      <c r="W5" s="16"/>
+      <c r="X5" s="16"/>
+      <c r="Y5" s="16"/>
+      <c r="Z5" s="16"/>
+      <c r="AA5" s="16"/>
+      <c r="AB5" s="16"/>
+      <c r="AJ5" t="s">
+        <v>179</v>
+      </c>
+      <c r="AK5">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="6" spans="1:37" ht="72" customHeight="1">
+      <c r="A6" s="31">
+        <v>184520</v>
+      </c>
+      <c r="B6" s="31"/>
+      <c r="C6" s="31"/>
+      <c r="D6" s="31"/>
+      <c r="E6" s="31"/>
+      <c r="F6" s="31"/>
+      <c r="G6" s="31"/>
+      <c r="H6" s="30">
+        <v>84</v>
+      </c>
+      <c r="I6" s="30"/>
+      <c r="J6" s="30"/>
+      <c r="K6" s="30"/>
+      <c r="L6" s="30"/>
+      <c r="M6" s="30"/>
+      <c r="N6" s="30"/>
+      <c r="O6" s="31">
+        <v>2196.67</v>
+      </c>
+      <c r="P6" s="31"/>
+      <c r="Q6" s="31"/>
+      <c r="R6" s="31"/>
+      <c r="S6" s="31"/>
+      <c r="T6" s="31"/>
+      <c r="U6" s="31"/>
+      <c r="V6" s="30">
+        <v>6</v>
+      </c>
+      <c r="W6" s="30"/>
+      <c r="X6" s="30"/>
+      <c r="Y6" s="30"/>
+      <c r="Z6" s="30"/>
+      <c r="AA6" s="30"/>
+      <c r="AB6" s="30"/>
+      <c r="AJ6" t="s">
+        <v>180</v>
+      </c>
+      <c r="AK6">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="7" spans="1:37" s="8" customFormat="1" ht="7.5" customHeight="1"/>
+    <row r="8" spans="1:37" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="9" spans="1:37" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="10" spans="1:37" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="11" spans="1:37" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="12" spans="1:37" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="13" spans="1:37" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="14" spans="1:37" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="15" spans="1:37" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="16" spans="1:37" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="17" spans="1:28" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="18" spans="1:28" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="19" spans="1:28" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="20" spans="1:28" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="21" spans="1:28" s="8" customFormat="1" ht="16.5" customHeight="1"/>
+    <row r="22" spans="1:28" s="8" customFormat="1" ht="7.5" customHeight="1"/>
+    <row r="23" spans="1:28" ht="25.5" customHeight="1">
+      <c r="A23" s="19" t="s">
+        <v>182</v>
+      </c>
+      <c r="B23" s="19"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="19"/>
+      <c r="F23" s="19"/>
+      <c r="G23" s="19"/>
+      <c r="H23" s="19"/>
+      <c r="I23" s="19"/>
+      <c r="J23" s="19"/>
+      <c r="K23" s="19"/>
+      <c r="L23" s="19"/>
+      <c r="M23" s="19"/>
+      <c r="N23" s="19"/>
+      <c r="O23" s="19"/>
+    </row>
+    <row r="24" spans="1:28" ht="22.5" customHeight="1">
+      <c r="A24" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="B24" s="20"/>
+      <c r="C24" s="20"/>
+      <c r="D24" s="20"/>
+      <c r="E24" s="20" t="s">
+        <v>100</v>
+      </c>
+      <c r="F24" s="20"/>
+      <c r="G24" s="20"/>
+      <c r="H24" s="20"/>
+      <c r="I24" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="J24" s="20"/>
+      <c r="K24" s="20"/>
+      <c r="L24" s="20"/>
+      <c r="M24" s="20" t="s">
+        <v>183</v>
+      </c>
+      <c r="N24" s="20"/>
+      <c r="O24" s="20"/>
+      <c r="P24" s="20"/>
+      <c r="Q24" s="20" t="s">
+        <v>169</v>
+      </c>
+      <c r="R24" s="20"/>
+      <c r="S24" s="20"/>
+      <c r="T24" s="20"/>
+      <c r="U24" s="20" t="s">
+        <v>184</v>
+      </c>
+      <c r="V24" s="20"/>
+      <c r="W24" s="20"/>
+      <c r="X24" s="20"/>
+      <c r="Y24" s="20" t="s">
+        <v>185</v>
+      </c>
+      <c r="Z24" s="20"/>
+      <c r="AA24" s="20"/>
+      <c r="AB24" s="20"/>
+    </row>
+    <row r="25" spans="1:28" ht="19.5" customHeight="1">
+      <c r="A25" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="B25" s="21"/>
+      <c r="C25" s="21"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="22">
+        <v>48</v>
+      </c>
+      <c r="F25" s="22"/>
+      <c r="G25" s="22"/>
+      <c r="H25" s="22"/>
+      <c r="I25" s="22">
+        <v>44</v>
+      </c>
+      <c r="J25" s="22"/>
+      <c r="K25" s="22"/>
+      <c r="L25" s="22"/>
+      <c r="M25" s="23">
+        <v>0.917</v>
+      </c>
+      <c r="N25" s="23"/>
+      <c r="O25" s="23"/>
+      <c r="P25" s="23"/>
+      <c r="Q25" s="32">
+        <v>92100</v>
+      </c>
+      <c r="R25" s="32"/>
+      <c r="S25" s="32"/>
+      <c r="T25" s="32"/>
+      <c r="U25" s="23">
+        <v>1.06</v>
+      </c>
+      <c r="V25" s="23"/>
+      <c r="W25" s="23"/>
+      <c r="X25" s="23"/>
+      <c r="Y25" s="26">
+        <v>2</v>
+      </c>
+      <c r="Z25" s="26"/>
+      <c r="AA25" s="26"/>
+      <c r="AB25" s="26"/>
+    </row>
+    <row r="26" spans="1:28" ht="19.5" customHeight="1">
+      <c r="A26" s="21"/>
+      <c r="B26" s="21"/>
+      <c r="C26" s="21"/>
+      <c r="D26" s="21"/>
+      <c r="E26" s="22"/>
+      <c r="F26" s="22"/>
+      <c r="G26" s="22"/>
+      <c r="H26" s="22"/>
+      <c r="I26" s="22"/>
+      <c r="J26" s="22"/>
+      <c r="K26" s="22"/>
+      <c r="L26" s="22"/>
+      <c r="M26" s="23"/>
+      <c r="N26" s="23"/>
+      <c r="O26" s="23"/>
+      <c r="P26" s="23"/>
+      <c r="Q26" s="32"/>
+      <c r="R26" s="32"/>
+      <c r="S26" s="32"/>
+      <c r="T26" s="32"/>
+      <c r="U26" s="23"/>
+      <c r="V26" s="23"/>
+      <c r="W26" s="23"/>
+      <c r="X26" s="23"/>
+      <c r="Y26" s="28"/>
+      <c r="Z26" s="28"/>
+      <c r="AA26" s="28"/>
+      <c r="AB26" s="28"/>
+    </row>
+    <row r="27" spans="1:28" ht="19.5" customHeight="1">
+      <c r="A27" s="21"/>
+      <c r="B27" s="21"/>
+      <c r="C27" s="21"/>
+      <c r="D27" s="21"/>
+      <c r="E27" s="22"/>
+      <c r="F27" s="22"/>
+      <c r="G27" s="22"/>
+      <c r="H27" s="22"/>
+      <c r="I27" s="22"/>
+      <c r="J27" s="22"/>
+      <c r="K27" s="22"/>
+      <c r="L27" s="22"/>
+      <c r="M27" s="23"/>
+      <c r="N27" s="23"/>
+      <c r="O27" s="23"/>
+      <c r="P27" s="23"/>
+      <c r="Q27" s="32"/>
+      <c r="R27" s="32"/>
+      <c r="S27" s="32"/>
+      <c r="T27" s="32"/>
+      <c r="U27" s="23"/>
+      <c r="V27" s="23"/>
+      <c r="W27" s="23"/>
+      <c r="X27" s="23"/>
+      <c r="Y27" s="28"/>
+      <c r="Z27" s="28"/>
+      <c r="AA27" s="28"/>
+      <c r="AB27" s="28"/>
+    </row>
+    <row r="28" spans="1:28" ht="19.5" customHeight="1">
+      <c r="A28" s="21"/>
+      <c r="B28" s="21"/>
+      <c r="C28" s="21"/>
+      <c r="D28" s="21"/>
+      <c r="E28" s="22"/>
+      <c r="F28" s="22"/>
+      <c r="G28" s="22"/>
+      <c r="H28" s="22"/>
+      <c r="I28" s="22"/>
+      <c r="J28" s="22"/>
+      <c r="K28" s="22"/>
+      <c r="L28" s="22"/>
+      <c r="M28" s="23"/>
+      <c r="N28" s="23"/>
+      <c r="O28" s="23"/>
+      <c r="P28" s="23"/>
+      <c r="Q28" s="32"/>
+      <c r="R28" s="32"/>
+      <c r="S28" s="32"/>
+      <c r="T28" s="32"/>
+      <c r="U28" s="23"/>
+      <c r="V28" s="23"/>
+      <c r="W28" s="23"/>
+      <c r="X28" s="23"/>
+      <c r="Y28" s="28"/>
+      <c r="Z28" s="28"/>
+      <c r="AA28" s="28"/>
+      <c r="AB28" s="28"/>
+    </row>
+    <row r="29" spans="1:28" ht="19.5" customHeight="1">
+      <c r="A29" s="21"/>
+      <c r="B29" s="21"/>
+      <c r="C29" s="21"/>
+      <c r="D29" s="21"/>
+      <c r="E29" s="22"/>
+      <c r="F29" s="22"/>
+      <c r="G29" s="22"/>
+      <c r="H29" s="22"/>
+      <c r="I29" s="22"/>
+      <c r="J29" s="22"/>
+      <c r="K29" s="22"/>
+      <c r="L29" s="22"/>
+      <c r="M29" s="23"/>
+      <c r="N29" s="23"/>
+      <c r="O29" s="23"/>
+      <c r="P29" s="23"/>
+      <c r="Q29" s="32"/>
+      <c r="R29" s="32"/>
+      <c r="S29" s="32"/>
+      <c r="T29" s="32"/>
+      <c r="U29" s="23"/>
+      <c r="V29" s="23"/>
+      <c r="W29" s="23"/>
+      <c r="X29" s="23"/>
+      <c r="Y29" s="28"/>
+      <c r="Z29" s="28"/>
+      <c r="AA29" s="28"/>
+      <c r="AB29" s="28"/>
+    </row>
+    <row r="30" spans="1:28" ht="19.5" customHeight="1">
+      <c r="A30" s="21"/>
+      <c r="B30" s="21"/>
+      <c r="C30" s="21"/>
+      <c r="D30" s="21"/>
+      <c r="E30" s="22"/>
+      <c r="F30" s="22"/>
+      <c r="G30" s="22"/>
+      <c r="H30" s="22"/>
+      <c r="I30" s="22"/>
+      <c r="J30" s="22"/>
+      <c r="K30" s="22"/>
+      <c r="L30" s="22"/>
+      <c r="M30" s="23"/>
+      <c r="N30" s="23"/>
+      <c r="O30" s="23"/>
+      <c r="P30" s="23"/>
+      <c r="Q30" s="32"/>
+      <c r="R30" s="32"/>
+      <c r="S30" s="32"/>
+      <c r="T30" s="32"/>
+      <c r="U30" s="23"/>
+      <c r="V30" s="23"/>
+      <c r="W30" s="23"/>
+      <c r="X30" s="23"/>
+      <c r="Y30" s="28"/>
+      <c r="Z30" s="28"/>
+      <c r="AA30" s="28"/>
+      <c r="AB30" s="28"/>
+    </row>
+    <row r="31" spans="1:28" ht="19.5" customHeight="1">
+      <c r="A31" s="21"/>
+      <c r="B31" s="21"/>
+      <c r="C31" s="21"/>
+      <c r="D31" s="21"/>
+      <c r="E31" s="22"/>
+      <c r="F31" s="22"/>
+      <c r="G31" s="22"/>
+      <c r="H31" s="22"/>
+      <c r="I31" s="22"/>
+      <c r="J31" s="22"/>
+      <c r="K31" s="22"/>
+      <c r="L31" s="22"/>
+      <c r="M31" s="23"/>
+      <c r="N31" s="23"/>
+      <c r="O31" s="23"/>
+      <c r="P31" s="23"/>
+      <c r="Q31" s="32"/>
+      <c r="R31" s="32"/>
+      <c r="S31" s="32"/>
+      <c r="T31" s="32"/>
+      <c r="U31" s="23"/>
+      <c r="V31" s="23"/>
+      <c r="W31" s="23"/>
+      <c r="X31" s="23"/>
+      <c r="Y31" s="28"/>
+      <c r="Z31" s="28"/>
+      <c r="AA31" s="28"/>
+      <c r="AB31" s="28"/>
+    </row>
+    <row r="32" spans="1:28" ht="19.5" customHeight="1">
+      <c r="A32" s="21"/>
+      <c r="B32" s="21"/>
+      <c r="C32" s="21"/>
+      <c r="D32" s="21"/>
+      <c r="E32" s="22"/>
+      <c r="F32" s="22"/>
+      <c r="G32" s="22"/>
+      <c r="H32" s="22"/>
+      <c r="I32" s="22"/>
+      <c r="J32" s="22"/>
+      <c r="K32" s="22"/>
+      <c r="L32" s="22"/>
+      <c r="M32" s="23"/>
+      <c r="N32" s="23"/>
+      <c r="O32" s="23"/>
+      <c r="P32" s="23"/>
+      <c r="Q32" s="32"/>
+      <c r="R32" s="32"/>
+      <c r="S32" s="32"/>
+      <c r="T32" s="32"/>
+      <c r="U32" s="23"/>
+      <c r="V32" s="23"/>
+      <c r="W32" s="23"/>
+      <c r="X32" s="23"/>
+      <c r="Y32" s="28"/>
+      <c r="Z32" s="28"/>
+      <c r="AA32" s="28"/>
+      <c r="AB32" s="28"/>
+    </row>
+  </sheetData>
+  <mergeCells count="87">
+    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="R1:X1"/>
+    <mergeCell ref="Y1:AB1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="J2:N2"/>
+    <mergeCell ref="O2:P2"/>
+    <mergeCell ref="Q2:U2"/>
+    <mergeCell ref="V2:W2"/>
+    <mergeCell ref="X2:AB2"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="H4:N4"/>
+    <mergeCell ref="H5:N5"/>
+    <mergeCell ref="H6:N6"/>
+    <mergeCell ref="O4:U4"/>
+    <mergeCell ref="O5:U5"/>
+    <mergeCell ref="O6:U6"/>
+    <mergeCell ref="V4:AB4"/>
+    <mergeCell ref="V5:AB5"/>
+    <mergeCell ref="V6:AB6"/>
+    <mergeCell ref="A23:O23"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="E24:H24"/>
+    <mergeCell ref="I24:L24"/>
+    <mergeCell ref="M24:P24"/>
+    <mergeCell ref="Q24:T24"/>
+    <mergeCell ref="U24:X24"/>
+    <mergeCell ref="Y24:AB24"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="E25:H25"/>
+    <mergeCell ref="I25:L25"/>
+    <mergeCell ref="M25:P25"/>
+    <mergeCell ref="Q25:T25"/>
+    <mergeCell ref="U25:X25"/>
+    <mergeCell ref="Y25:AB25"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="E26:H26"/>
+    <mergeCell ref="I26:L26"/>
+    <mergeCell ref="M26:P26"/>
+    <mergeCell ref="Q26:T26"/>
+    <mergeCell ref="U26:X26"/>
+    <mergeCell ref="Y26:AB26"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="E27:H27"/>
+    <mergeCell ref="I27:L27"/>
+    <mergeCell ref="M27:P27"/>
+    <mergeCell ref="Q27:T27"/>
+    <mergeCell ref="U27:X27"/>
+    <mergeCell ref="Y27:AB27"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="E28:H28"/>
+    <mergeCell ref="I28:L28"/>
+    <mergeCell ref="M28:P28"/>
+    <mergeCell ref="Q28:T28"/>
+    <mergeCell ref="U28:X28"/>
+    <mergeCell ref="Y28:AB28"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="E29:H29"/>
+    <mergeCell ref="I29:L29"/>
+    <mergeCell ref="M29:P29"/>
+    <mergeCell ref="Q29:T29"/>
+    <mergeCell ref="U29:X29"/>
+    <mergeCell ref="Y29:AB29"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="E30:H30"/>
+    <mergeCell ref="I30:L30"/>
+    <mergeCell ref="M30:P30"/>
+    <mergeCell ref="Q30:T30"/>
+    <mergeCell ref="U30:X30"/>
+    <mergeCell ref="Y30:AB30"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="E31:H31"/>
+    <mergeCell ref="I31:L31"/>
+    <mergeCell ref="M31:P31"/>
+    <mergeCell ref="Q31:T31"/>
+    <mergeCell ref="U31:X31"/>
+    <mergeCell ref="Y31:AB31"/>
+    <mergeCell ref="A32:D32"/>
+    <mergeCell ref="E32:H32"/>
+    <mergeCell ref="I32:L32"/>
+    <mergeCell ref="M32:P32"/>
+    <mergeCell ref="Q32:T32"/>
+    <mergeCell ref="U32:X32"/>
+    <mergeCell ref="Y32:AB32"/>
+  </mergeCells>
+  <pageMargins left="0.15" right="0.15" top="0.2" bottom="0.2" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape"/>
+  <headerFooter>
+    <oddFooter>&amp;LPrepared by Anass ASSRI | WFM&amp;CDesign reference&amp;RConfidential</oddFooter>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/docs/WFMHub Report Design Reference.xlsx
+++ b/docs/WFMHub Report Design Reference.xlsx
@@ -190,7 +190,7 @@
     <t>UPDATED</t>
   </si>
   <si>
-    <t>WFMHUB-DESIGN 2.1.0 · approved visual contract</t>
+    <t>WFMHUB-DESIGN 2.2.0 · approved visual contract</t>
   </si>
   <si>
     <t>TOKENS</t>

--- a/docs/WFMHub Report Design Reference.xlsx
+++ b/docs/WFMHub Report Design Reference.xlsx
@@ -190,7 +190,7 @@
     <t>UPDATED</t>
   </si>
   <si>
-    <t>WFMHUB-DESIGN 2.2.0 · approved visual contract</t>
+    <t>WFMHUB-DESIGN 2.3.0 · approved visual contract</t>
   </si>
   <si>
     <t>TOKENS</t>

--- a/docs/WFMHub Report Design Reference.xlsx
+++ b/docs/WFMHub Report Design Reference.xlsx
@@ -190,7 +190,7 @@
     <t>UPDATED</t>
   </si>
   <si>
-    <t>WFMHUB-DESIGN 2.3.0 · approved visual contract</t>
+    <t>WFMHUB-DESIGN 2.3.1 · approved visual contract</t>
   </si>
   <si>
     <t>TOKENS</t>

--- a/docs/WFMHub Report Design Reference.xlsx
+++ b/docs/WFMHub Report Design Reference.xlsx
@@ -190,7 +190,7 @@
     <t>UPDATED</t>
   </si>
   <si>
-    <t>WFMHUB-DESIGN 2.3.1 · approved visual contract</t>
+    <t>WFMHUB-DESIGN 3.0.0 · approved visual contract</t>
   </si>
   <si>
     <t>TOKENS</t>

--- a/docs/WFMHub Report Design Reference.xlsx
+++ b/docs/WFMHub Report Design Reference.xlsx
@@ -190,7 +190,7 @@
     <t>UPDATED</t>
   </si>
   <si>
-    <t>WFMHUB-DESIGN 3.0.0 · approved visual contract</t>
+    <t>WFMHUB-DESIGN 3.0.1 · approved visual contract</t>
   </si>
   <si>
     <t>TOKENS</t>

--- a/docs/WFMHub Report Design Reference.xlsx
+++ b/docs/WFMHub Report Design Reference.xlsx
@@ -190,7 +190,7 @@
     <t>UPDATED</t>
   </si>
   <si>
-    <t>WFMHUB-DESIGN 3.0.1 · approved visual contract</t>
+    <t>WFMHUB-DESIGN 3.1.0 · approved visual contract</t>
   </si>
   <si>
     <t>TOKENS</t>

--- a/docs/WFMHub Report Design Reference.xlsx
+++ b/docs/WFMHub Report Design Reference.xlsx
@@ -190,7 +190,7 @@
     <t>UPDATED</t>
   </si>
   <si>
-    <t>WFMHUB-DESIGN 3.1.0 · approved visual contract</t>
+    <t>WFMHUB-DESIGN 3.2.0 · approved visual contract</t>
   </si>
   <si>
     <t>TOKENS</t>
